--- a/data/final_governance.xlsx
+++ b/data/final_governance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_MONASH_UNI\_Y3S1\FIT3179\DV2_repo\FIT3179_DV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133D83CB-50FE-485F-B34E-65AC0CD970A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4627EF45-B25E-491E-ADD0-CE192EC514D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A96843CF-6E57-494F-B5A3-EF4DBD7CFBBF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="10">
   <si>
     <t>Governance</t>
   </si>
@@ -75,7 +75,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0000"/>
+  </numFmts>
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,16 +89,340 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -100,15 +430,4835 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2346">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="10"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2346">
+    <cellStyle name="20% - Accent1" xfId="17" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1 10" xfId="308" xr:uid="{716E9EB7-F42F-4400-85F2-08B14BBED818}"/>
+    <cellStyle name="20% - Accent1 10 2" xfId="1354" xr:uid="{CE41FA1E-254F-4B07-AFF2-F7D5A87622F3}"/>
+    <cellStyle name="20% - Accent1 10 3" xfId="1675" xr:uid="{A1404C48-7D99-4D9B-883E-CC70168B1273}"/>
+    <cellStyle name="20% - Accent1 11" xfId="108" xr:uid="{5C3C74EE-EDE2-4F0E-A596-E4760B200DEC}"/>
+    <cellStyle name="20% - Accent1 11 2" xfId="1367" xr:uid="{78768E64-8629-413C-A523-FFAC788764F7}"/>
+    <cellStyle name="20% - Accent1 11 3" xfId="1477" xr:uid="{E8580737-CF9D-4536-B540-9ED3C4F6F3C1}"/>
+    <cellStyle name="20% - Accent1 12" xfId="941" xr:uid="{5376AA7D-7FE2-4A64-B525-7F3BF9E7371F}"/>
+    <cellStyle name="20% - Accent1 12 2" xfId="1380" xr:uid="{12EDBDE4-FC9C-4093-A0DC-EBD50C902E2B}"/>
+    <cellStyle name="20% - Accent1 12 3" xfId="2297" xr:uid="{F9B5E467-2328-4F09-BB1F-E8840DDA9131}"/>
+    <cellStyle name="20% - Accent1 13" xfId="955" xr:uid="{FBEE050E-E56D-42E4-B181-172B54A226BD}"/>
+    <cellStyle name="20% - Accent1 13 2" xfId="1394" xr:uid="{C0C5161E-6848-4119-8E35-BA4A858A297E}"/>
+    <cellStyle name="20% - Accent1 13 3" xfId="2311" xr:uid="{6765EED9-8E34-4155-BCFC-F66BEDBE18AE}"/>
+    <cellStyle name="20% - Accent1 14" xfId="969" xr:uid="{3B68D2D0-2ECF-4E21-9626-496900AAC2EA}"/>
+    <cellStyle name="20% - Accent1 14 2" xfId="2325" xr:uid="{AC9896B3-F295-49B0-8D1E-9F63AAF1E2B5}"/>
+    <cellStyle name="20% - Accent1 15" xfId="985" xr:uid="{DBE5E576-F786-499A-A00A-882A98546FEA}"/>
+    <cellStyle name="20% - Accent1 16" xfId="998" xr:uid="{92C1567D-4617-420E-9E8F-885F5ABCEE7D}"/>
+    <cellStyle name="20% - Accent1 17" xfId="1407" xr:uid="{A95F01D8-8A12-43BB-9F51-B506F614E1C1}"/>
+    <cellStyle name="20% - Accent1 2" xfId="49" xr:uid="{5213F60A-B7B3-40BE-AEF3-7F3B29B01F3D}"/>
+    <cellStyle name="20% - Accent1 2 2" xfId="254" xr:uid="{1D06E5A0-98B9-40FC-B9CF-F8A2DE09A2B7}"/>
+    <cellStyle name="20% - Accent1 2 2 2" xfId="517" xr:uid="{F9FA930F-01E6-4BDA-8D74-9B591DDD8722}"/>
+    <cellStyle name="20% - Accent1 2 2 2 2" xfId="899" xr:uid="{D8527882-B933-4666-A510-E814E23B12E7}"/>
+    <cellStyle name="20% - Accent1 2 2 2 2 2" xfId="2255" xr:uid="{C908E07C-512E-41A3-9C2E-18AD59503788}"/>
+    <cellStyle name="20% - Accent1 2 2 2 3" xfId="1284" xr:uid="{D5DFD9EF-3502-4598-88D9-D5816011DAAF}"/>
+    <cellStyle name="20% - Accent1 2 2 2 4" xfId="1875" xr:uid="{196BE454-DEFC-4B6A-BF0C-864EDD92A7C3}"/>
+    <cellStyle name="20% - Accent1 2 2 3" xfId="629" xr:uid="{7F31D9FC-B582-4D1C-B516-4C2666DBBE9D}"/>
+    <cellStyle name="20% - Accent1 2 2 3 2" xfId="1987" xr:uid="{2BE55882-DD34-4267-9027-442B3BAB0F31}"/>
+    <cellStyle name="20% - Accent1 2 2 4" xfId="771" xr:uid="{8395B516-857C-49CE-959B-1CB58487E14E}"/>
+    <cellStyle name="20% - Accent1 2 2 4 2" xfId="2129" xr:uid="{3F479CAC-E78E-4033-B973-5DDCA2D165F5}"/>
+    <cellStyle name="20% - Accent1 2 2 5" xfId="382" xr:uid="{C7FC037A-988A-407C-9C2B-E932F16B3FCE}"/>
+    <cellStyle name="20% - Accent1 2 2 5 2" xfId="1749" xr:uid="{34468AE9-FA94-400D-A0C7-217D299B3DDD}"/>
+    <cellStyle name="20% - Accent1 2 2 6" xfId="1140" xr:uid="{CC5CE486-26D7-4430-8A5D-E274CD8F0B27}"/>
+    <cellStyle name="20% - Accent1 2 2 7" xfId="1621" xr:uid="{250C5F00-B629-4CE3-9F9A-F13F2D99CF75}"/>
+    <cellStyle name="20% - Accent1 2 3" xfId="194" xr:uid="{C5B7FE42-84C8-430A-B288-575BF6F1A65C}"/>
+    <cellStyle name="20% - Accent1 2 3 2" xfId="842" xr:uid="{5DCC4928-1919-4D6F-937C-3F8B1AD10378}"/>
+    <cellStyle name="20% - Accent1 2 3 2 2" xfId="2199" xr:uid="{0E18FFD5-560B-431E-B25F-907DF5587B8E}"/>
+    <cellStyle name="20% - Accent1 2 3 3" xfId="454" xr:uid="{C8505C54-A322-4478-AFB0-6B769D48DA9D}"/>
+    <cellStyle name="20% - Accent1 2 3 3 2" xfId="1819" xr:uid="{21FC0E82-3852-4DB9-A328-FA30E25C0C66}"/>
+    <cellStyle name="20% - Accent1 2 3 4" xfId="1084" xr:uid="{510A2C7F-FFDD-4B94-830F-E75877CECCBD}"/>
+    <cellStyle name="20% - Accent1 2 3 5" xfId="1563" xr:uid="{E0CFEF09-F27D-48E8-9482-C85058ADDFCB}"/>
+    <cellStyle name="20% - Accent1 2 4" xfId="573" xr:uid="{C72A2021-AC46-4F72-B830-7EB01BC576AF}"/>
+    <cellStyle name="20% - Accent1 2 4 2" xfId="1213" xr:uid="{1FD320E3-0C01-40D5-BFAF-FC18B3BF18FE}"/>
+    <cellStyle name="20% - Accent1 2 4 3" xfId="1931" xr:uid="{62FB44A8-47ED-448A-9444-7505D999E514}"/>
+    <cellStyle name="20% - Accent1 2 5" xfId="713" xr:uid="{C49C676E-463D-4DDD-A044-60C5EEA633F0}"/>
+    <cellStyle name="20% - Accent1 2 5 2" xfId="2071" xr:uid="{BA668BF2-A1BD-4FBF-A3E9-007E780A9480}"/>
+    <cellStyle name="20% - Accent1 2 6" xfId="324" xr:uid="{FA2F3784-5DFB-4D67-B216-915F4950D867}"/>
+    <cellStyle name="20% - Accent1 2 6 2" xfId="1691" xr:uid="{CC0A03D5-147C-44C2-84E4-6F052C6D433A}"/>
+    <cellStyle name="20% - Accent1 2 7" xfId="124" xr:uid="{0A4AEBA3-DE76-44D8-B76D-A53613BCB535}"/>
+    <cellStyle name="20% - Accent1 2 7 2" xfId="1493" xr:uid="{1CDBC459-8316-440F-9D4E-35130C1A6F3D}"/>
+    <cellStyle name="20% - Accent1 2 8" xfId="1014" xr:uid="{B017ED67-3FC9-4A43-B1E1-DE0FEDE8167F}"/>
+    <cellStyle name="20% - Accent1 2 9" xfId="1423" xr:uid="{4679FC6E-BE39-4D3A-814A-99BF5E7D8230}"/>
+    <cellStyle name="20% - Accent1 3" xfId="67" xr:uid="{BF7EF1A8-57FF-465A-8CD6-4515A6378F94}"/>
+    <cellStyle name="20% - Accent1 3 2" xfId="268" xr:uid="{FAA69354-01BC-46DD-AE44-7893F728D420}"/>
+    <cellStyle name="20% - Accent1 3 2 2" xfId="531" xr:uid="{730C96A4-489D-42FB-B79E-5A80B1791DA9}"/>
+    <cellStyle name="20% - Accent1 3 2 2 2" xfId="913" xr:uid="{E7CB5FF2-76DD-4FCF-88B8-D998739CFA01}"/>
+    <cellStyle name="20% - Accent1 3 2 2 2 2" xfId="2269" xr:uid="{46ADC9DB-F27D-4379-8D85-E03A0F35C60A}"/>
+    <cellStyle name="20% - Accent1 3 2 2 3" xfId="1298" xr:uid="{C99E358B-6DE2-402D-83D8-DD85BE855F34}"/>
+    <cellStyle name="20% - Accent1 3 2 2 4" xfId="1889" xr:uid="{196098B9-65C8-49E9-8361-AADB8B64FD14}"/>
+    <cellStyle name="20% - Accent1 3 2 3" xfId="643" xr:uid="{30852D34-31FB-4A89-BFE4-B6CE85CEC238}"/>
+    <cellStyle name="20% - Accent1 3 2 3 2" xfId="2001" xr:uid="{169F6034-0218-4FF1-8090-D4651E620D8B}"/>
+    <cellStyle name="20% - Accent1 3 2 4" xfId="785" xr:uid="{B54F6D76-EDC4-4203-B924-0B16472C6585}"/>
+    <cellStyle name="20% - Accent1 3 2 4 2" xfId="2143" xr:uid="{0B366622-8EA5-493B-B3E9-5572347E447A}"/>
+    <cellStyle name="20% - Accent1 3 2 5" xfId="396" xr:uid="{7D84B257-B332-42F7-BB9A-A00486419774}"/>
+    <cellStyle name="20% - Accent1 3 2 5 2" xfId="1763" xr:uid="{FFEA86BF-ED04-46C7-BDF5-B7A0DF625D18}"/>
+    <cellStyle name="20% - Accent1 3 2 6" xfId="1154" xr:uid="{8B34E117-6CF0-41BA-A41D-05E1F5352A3B}"/>
+    <cellStyle name="20% - Accent1 3 2 7" xfId="1635" xr:uid="{975CDE3F-14E0-4504-9C8D-DC2C6A620BED}"/>
+    <cellStyle name="20% - Accent1 3 3" xfId="208" xr:uid="{A6945010-7658-43F5-A917-EC7B1E4AFB56}"/>
+    <cellStyle name="20% - Accent1 3 3 2" xfId="856" xr:uid="{DB0EFAED-22AF-4C13-878B-290729089099}"/>
+    <cellStyle name="20% - Accent1 3 3 2 2" xfId="2213" xr:uid="{228F2FCC-9006-47EA-95ED-E91C5BDDC3DA}"/>
+    <cellStyle name="20% - Accent1 3 3 3" xfId="468" xr:uid="{1B19B4DA-4392-4661-A8EF-C74F83FCE8DA}"/>
+    <cellStyle name="20% - Accent1 3 3 3 2" xfId="1833" xr:uid="{25E7C698-CAC0-4A6D-9EAE-32F52ABD4191}"/>
+    <cellStyle name="20% - Accent1 3 3 4" xfId="1098" xr:uid="{50D17E04-A8A0-43FB-B555-1EFFB4095142}"/>
+    <cellStyle name="20% - Accent1 3 3 5" xfId="1577" xr:uid="{72ABBB44-74B0-43E3-AB09-F829BA29FB59}"/>
+    <cellStyle name="20% - Accent1 3 4" xfId="587" xr:uid="{8B778C08-A938-40C7-9F26-A2AF8CDB09BE}"/>
+    <cellStyle name="20% - Accent1 3 4 2" xfId="1227" xr:uid="{CAD3463A-9F70-4DD9-9CB2-BC275C1E1A1A}"/>
+    <cellStyle name="20% - Accent1 3 4 3" xfId="1945" xr:uid="{3280E00B-4E21-4F6A-A0DD-FF48A1F868D8}"/>
+    <cellStyle name="20% - Accent1 3 5" xfId="727" xr:uid="{CF9DECAF-BAD9-4CFE-93B5-35E8CB7F75EF}"/>
+    <cellStyle name="20% - Accent1 3 5 2" xfId="2085" xr:uid="{C3859F75-72B7-4AE9-8BE7-DAED15B265D6}"/>
+    <cellStyle name="20% - Accent1 3 6" xfId="338" xr:uid="{566EFB23-A09F-4CA2-B942-436DB12BC9E6}"/>
+    <cellStyle name="20% - Accent1 3 6 2" xfId="1705" xr:uid="{C63CC68A-E1EF-4317-99FE-DC8B2EB7A9F2}"/>
+    <cellStyle name="20% - Accent1 3 7" xfId="138" xr:uid="{953D342D-8D79-484D-8F72-6CD5FFE02925}"/>
+    <cellStyle name="20% - Accent1 3 7 2" xfId="1507" xr:uid="{3BCDDBFD-15E3-484D-8A53-8D5BC817174D}"/>
+    <cellStyle name="20% - Accent1 3 8" xfId="1028" xr:uid="{D415FAB9-B8F1-48C4-92B6-872B2BCC67C8}"/>
+    <cellStyle name="20% - Accent1 3 9" xfId="1437" xr:uid="{444EFB06-FAC2-47AB-8BD5-B162BF1CB340}"/>
+    <cellStyle name="20% - Accent1 4" xfId="81" xr:uid="{0219508E-3FFC-44D1-8D27-7AA03FB4DE0E}"/>
+    <cellStyle name="20% - Accent1 4 2" xfId="281" xr:uid="{007E1B36-18CA-48D3-A670-57DAD869A3C5}"/>
+    <cellStyle name="20% - Accent1 4 2 2" xfId="545" xr:uid="{5FCE6AEB-A443-47DF-96FC-1EE790C8FB10}"/>
+    <cellStyle name="20% - Accent1 4 2 2 2" xfId="927" xr:uid="{752489FB-D99E-4736-B442-AFCFF0E24EA3}"/>
+    <cellStyle name="20% - Accent1 4 2 2 2 2" xfId="2283" xr:uid="{24F29411-61D6-488A-A0CF-75644E2CB369}"/>
+    <cellStyle name="20% - Accent1 4 2 2 3" xfId="1312" xr:uid="{D87875BE-EE8E-4636-A82D-3C84352ED59A}"/>
+    <cellStyle name="20% - Accent1 4 2 2 4" xfId="1903" xr:uid="{6FA38856-F1B5-4A08-9CB5-862BF075C266}"/>
+    <cellStyle name="20% - Accent1 4 2 3" xfId="657" xr:uid="{2A12EBCA-EF7A-4BC2-9032-46ABD4DB45FA}"/>
+    <cellStyle name="20% - Accent1 4 2 3 2" xfId="2015" xr:uid="{17D20580-4108-41D7-BE65-96243B0FD2E5}"/>
+    <cellStyle name="20% - Accent1 4 2 4" xfId="798" xr:uid="{FCD56FA1-9B32-4D86-83B4-0D41C97511BD}"/>
+    <cellStyle name="20% - Accent1 4 2 4 2" xfId="2156" xr:uid="{45B01B01-D7C3-4369-B00F-AE791D5EA812}"/>
+    <cellStyle name="20% - Accent1 4 2 5" xfId="409" xr:uid="{FFAC391F-F303-4F70-BE1D-647D73BCB180}"/>
+    <cellStyle name="20% - Accent1 4 2 5 2" xfId="1776" xr:uid="{DB4EA64B-D42C-49DD-BF8E-3273B6B5CDEE}"/>
+    <cellStyle name="20% - Accent1 4 2 6" xfId="1168" xr:uid="{DD2CCB4C-BABA-4A99-BA61-3530513D1605}"/>
+    <cellStyle name="20% - Accent1 4 2 7" xfId="1648" xr:uid="{F73B88F3-43B9-478C-9338-950067BDA23D}"/>
+    <cellStyle name="20% - Accent1 4 3" xfId="222" xr:uid="{C9449209-F8DD-4B8C-A307-69AE511E70FF}"/>
+    <cellStyle name="20% - Accent1 4 3 2" xfId="870" xr:uid="{5D3FE7EF-7CB8-49B1-B5D3-8BD8A1411AC9}"/>
+    <cellStyle name="20% - Accent1 4 3 2 2" xfId="2227" xr:uid="{542FC56F-5A91-4660-9043-E90785009A09}"/>
+    <cellStyle name="20% - Accent1 4 3 3" xfId="482" xr:uid="{CF83ED2A-1914-499B-9512-3B138A5D8640}"/>
+    <cellStyle name="20% - Accent1 4 3 3 2" xfId="1847" xr:uid="{26A75A44-712E-4297-B47E-81A7A582C4E3}"/>
+    <cellStyle name="20% - Accent1 4 3 4" xfId="1112" xr:uid="{50D5C437-2A1C-466D-BAA7-9C6389EF6B28}"/>
+    <cellStyle name="20% - Accent1 4 3 5" xfId="1591" xr:uid="{20250F21-3D16-42DB-835F-AAE88CD5E7B6}"/>
+    <cellStyle name="20% - Accent1 4 4" xfId="601" xr:uid="{FC29C18C-E00F-4BDD-8DB7-BF8FE1672335}"/>
+    <cellStyle name="20% - Accent1 4 4 2" xfId="1241" xr:uid="{11D0A8CB-B056-4DC8-821E-317C0EA158ED}"/>
+    <cellStyle name="20% - Accent1 4 4 3" xfId="1959" xr:uid="{790AFE7F-6EA5-4CE5-9B1A-C4062D9DDC25}"/>
+    <cellStyle name="20% - Accent1 4 5" xfId="741" xr:uid="{10B094FC-8753-47E4-8067-17774CD4106D}"/>
+    <cellStyle name="20% - Accent1 4 5 2" xfId="2099" xr:uid="{3E88F433-99EC-47BA-B615-E9D7452701A4}"/>
+    <cellStyle name="20% - Accent1 4 6" xfId="352" xr:uid="{59E78011-DA55-4DC5-A075-A0726C68A17A}"/>
+    <cellStyle name="20% - Accent1 4 6 2" xfId="1719" xr:uid="{A3535337-35A4-4E7D-A4AD-1E4B147B5F83}"/>
+    <cellStyle name="20% - Accent1 4 7" xfId="152" xr:uid="{C0FE1AFE-1A67-4BBC-AED2-6C4AFE437C1B}"/>
+    <cellStyle name="20% - Accent1 4 7 2" xfId="1521" xr:uid="{9DC6DD73-6758-4E26-8854-0BEAE99A4F61}"/>
+    <cellStyle name="20% - Accent1 4 8" xfId="1042" xr:uid="{1EEAB798-F7A2-4E54-B3DF-CE7165DF485A}"/>
+    <cellStyle name="20% - Accent1 4 9" xfId="1451" xr:uid="{DEAF4808-B920-4DB4-BC90-3B86F597D839}"/>
+    <cellStyle name="20% - Accent1 5" xfId="95" xr:uid="{E044531D-6C70-4936-A443-7CF88516CD8C}"/>
+    <cellStyle name="20% - Accent1 5 2" xfId="238" xr:uid="{57AD92CC-D257-4119-91C1-A4C818ECEDB6}"/>
+    <cellStyle name="20% - Accent1 5 2 2" xfId="883" xr:uid="{21C51FCA-5020-46A9-86F0-6E58B9FB8E9A}"/>
+    <cellStyle name="20% - Accent1 5 2 2 2" xfId="2239" xr:uid="{15099BB4-7A3C-4A0D-95C7-3ECA0E708BFB}"/>
+    <cellStyle name="20% - Accent1 5 2 3" xfId="498" xr:uid="{48C20AF6-F872-449B-B809-AD589FA50F0C}"/>
+    <cellStyle name="20% - Accent1 5 2 3 2" xfId="1859" xr:uid="{C8CA1F59-B5FA-48E2-8557-EB9FBFA1D0EB}"/>
+    <cellStyle name="20% - Accent1 5 2 4" xfId="1124" xr:uid="{C4CC81B6-DF05-4FFE-A021-32129D7A446B}"/>
+    <cellStyle name="20% - Accent1 5 2 5" xfId="1605" xr:uid="{AF22A54D-5729-48EC-AED1-573E45BD25DF}"/>
+    <cellStyle name="20% - Accent1 5 3" xfId="671" xr:uid="{32350251-117C-47A4-8F5B-B7C7B3B3D620}"/>
+    <cellStyle name="20% - Accent1 5 3 2" xfId="1255" xr:uid="{D078BAFB-FF34-4188-9EEB-EF392274C51D}"/>
+    <cellStyle name="20% - Accent1 5 3 3" xfId="2029" xr:uid="{82BA778D-62F3-4113-A627-C8E979339831}"/>
+    <cellStyle name="20% - Accent1 5 4" xfId="755" xr:uid="{601024F9-6997-4302-B8A3-0B84DFA5921D}"/>
+    <cellStyle name="20% - Accent1 5 4 2" xfId="2113" xr:uid="{B099758F-1FEB-4F3F-96CA-9BCA861E0312}"/>
+    <cellStyle name="20% - Accent1 5 5" xfId="366" xr:uid="{0643C6E1-DB94-465A-8E6C-08F2489456B8}"/>
+    <cellStyle name="20% - Accent1 5 5 2" xfId="1733" xr:uid="{DB2F92C7-629E-4744-B700-21AAA58C2B3F}"/>
+    <cellStyle name="20% - Accent1 5 6" xfId="166" xr:uid="{5B09A1C6-A69A-4E72-9FD6-3F82BFFC079F}"/>
+    <cellStyle name="20% - Accent1 5 6 2" xfId="1535" xr:uid="{3E5680AB-2764-449A-A52E-B22F3AF23C82}"/>
+    <cellStyle name="20% - Accent1 5 7" xfId="1056" xr:uid="{AA4CB1DC-A7A8-42B6-9C4C-28F1125028FC}"/>
+    <cellStyle name="20% - Accent1 5 8" xfId="1465" xr:uid="{4F425AE8-9858-4679-897C-2498313B90BD}"/>
+    <cellStyle name="20% - Accent1 6" xfId="178" xr:uid="{7A4E6358-477D-4A1B-81E4-70A735D41510}"/>
+    <cellStyle name="20% - Accent1 6 2" xfId="613" xr:uid="{BAC4B7D1-0565-484F-88CA-572D126E21DD}"/>
+    <cellStyle name="20% - Accent1 6 2 2" xfId="1268" xr:uid="{9EBD1A4E-1CCA-4E85-AE38-7240B03ACA71}"/>
+    <cellStyle name="20% - Accent1 6 2 3" xfId="1971" xr:uid="{C5D638BB-D4C4-4723-A0C1-29BABD32606A}"/>
+    <cellStyle name="20% - Accent1 6 3" xfId="813" xr:uid="{3C8B67C2-D675-4EAB-8253-46D8905D2F0D}"/>
+    <cellStyle name="20% - Accent1 6 3 2" xfId="2171" xr:uid="{46D24FC6-D98F-42A0-BB14-82C3ECC9AE57}"/>
+    <cellStyle name="20% - Accent1 6 4" xfId="424" xr:uid="{52EBDC20-D32F-4153-972B-7DA9AD12DA84}"/>
+    <cellStyle name="20% - Accent1 6 4 2" xfId="1791" xr:uid="{9D932BB2-3F08-407B-AC61-8E65E84452C9}"/>
+    <cellStyle name="20% - Accent1 6 5" xfId="1068" xr:uid="{B8B8CDBC-0D3C-4EEC-B964-2455C08FEC77}"/>
+    <cellStyle name="20% - Accent1 6 6" xfId="1547" xr:uid="{F47992E9-F10D-42F2-9CDC-390D74434BD0}"/>
+    <cellStyle name="20% - Accent1 7" xfId="296" xr:uid="{B43BB96C-D8B2-403B-AE18-AC6CFEB8CFCA}"/>
+    <cellStyle name="20% - Accent1 7 2" xfId="685" xr:uid="{231EFBA0-03DC-49A3-B5E6-40BBC51BC742}"/>
+    <cellStyle name="20% - Accent1 7 2 2" xfId="1326" xr:uid="{7DFEDBA3-F3D3-4ED3-BD20-B55E4628517C}"/>
+    <cellStyle name="20% - Accent1 7 2 3" xfId="2043" xr:uid="{83949915-0CFA-4E1E-90AF-F934C37302D0}"/>
+    <cellStyle name="20% - Accent1 7 3" xfId="826" xr:uid="{D78DC90C-E0F5-42E7-90B4-41B63F7BAD48}"/>
+    <cellStyle name="20% - Accent1 7 3 2" xfId="2183" xr:uid="{D881AE54-B944-42F9-ADEF-F3ADAABE29F3}"/>
+    <cellStyle name="20% - Accent1 7 4" xfId="438" xr:uid="{C441963E-6651-4FDB-8277-FBB4752B6ECC}"/>
+    <cellStyle name="20% - Accent1 7 4 2" xfId="1803" xr:uid="{82AF33C7-1EE1-4E02-9050-3CFDA84947C7}"/>
+    <cellStyle name="20% - Accent1 7 5" xfId="1182" xr:uid="{5E6D4919-7DBB-43B3-A29C-93033E50BD9C}"/>
+    <cellStyle name="20% - Accent1 7 6" xfId="1663" xr:uid="{CEB61D81-5227-4223-8B25-DCAD5B4E0DD1}"/>
+    <cellStyle name="20% - Accent1 8" xfId="557" xr:uid="{C2301E5B-18BD-480B-99FF-59630879171E}"/>
+    <cellStyle name="20% - Accent1 8 2" xfId="1196" xr:uid="{D1751C19-E3BC-4FB3-95B7-648CDB3CBE77}"/>
+    <cellStyle name="20% - Accent1 8 3" xfId="1915" xr:uid="{7DE7F015-7114-499A-8F6F-7720373BB34F}"/>
+    <cellStyle name="20% - Accent1 9" xfId="697" xr:uid="{08862FF7-A12E-45CE-B4BB-1093474D89CB}"/>
+    <cellStyle name="20% - Accent1 9 2" xfId="1340" xr:uid="{EFD9BF07-69C3-4032-A4EE-AB0DDDDCEC5A}"/>
+    <cellStyle name="20% - Accent1 9 3" xfId="2055" xr:uid="{1D0638FD-FDE0-47C6-9EA0-AB41AC145FFE}"/>
+    <cellStyle name="20% - Accent2" xfId="20" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2 10" xfId="310" xr:uid="{E9CC954A-0433-47DE-BF87-B92D960337E6}"/>
+    <cellStyle name="20% - Accent2 10 2" xfId="1356" xr:uid="{70DA96FA-E0E8-41D0-A6FF-6FBE1BC5453E}"/>
+    <cellStyle name="20% - Accent2 10 3" xfId="1677" xr:uid="{274EC662-0C28-4B1D-A040-48BCA2839CEE}"/>
+    <cellStyle name="20% - Accent2 11" xfId="110" xr:uid="{EFFA9A2D-087F-46E6-94E8-88B5BD89AB4A}"/>
+    <cellStyle name="20% - Accent2 11 2" xfId="1369" xr:uid="{A1BC7562-C994-483E-B28F-7364F83F1A3E}"/>
+    <cellStyle name="20% - Accent2 11 3" xfId="1479" xr:uid="{C340D187-4451-4CB4-9F4B-3AA8C62117D1}"/>
+    <cellStyle name="20% - Accent2 12" xfId="943" xr:uid="{CFFA0B2C-1A31-4EE1-8198-2FA586120EC5}"/>
+    <cellStyle name="20% - Accent2 12 2" xfId="1382" xr:uid="{C49F3BAA-6D14-4F5D-815C-95EA28C0770B}"/>
+    <cellStyle name="20% - Accent2 12 3" xfId="2299" xr:uid="{E90C81AD-01D7-406C-8A6F-B072A291788B}"/>
+    <cellStyle name="20% - Accent2 13" xfId="957" xr:uid="{D9F25AA1-88E2-4F3E-A70D-A8394DC04629}"/>
+    <cellStyle name="20% - Accent2 13 2" xfId="1396" xr:uid="{6FEA7E73-9380-4DAB-97EE-B1E5DB3E9D04}"/>
+    <cellStyle name="20% - Accent2 13 3" xfId="2313" xr:uid="{CC877124-CD2C-4748-8D77-0553051C9265}"/>
+    <cellStyle name="20% - Accent2 14" xfId="971" xr:uid="{CF9FBD89-86C9-4CB6-8B5C-1855E8CAF910}"/>
+    <cellStyle name="20% - Accent2 14 2" xfId="2327" xr:uid="{8F886CA6-7BD6-46E5-A65F-BA94A7553D94}"/>
+    <cellStyle name="20% - Accent2 15" xfId="987" xr:uid="{1F21C27B-8FE8-45D5-8B50-506AD60C7D2C}"/>
+    <cellStyle name="20% - Accent2 16" xfId="1000" xr:uid="{F5700006-EAC7-4C03-9E0A-3EAB4CB27804}"/>
+    <cellStyle name="20% - Accent2 17" xfId="1409" xr:uid="{DC35AC1C-6E7C-4349-8E3B-1E3B230AC41A}"/>
+    <cellStyle name="20% - Accent2 2" xfId="51" xr:uid="{81121AD0-5A31-4FF3-AA2B-A896AF3E4017}"/>
+    <cellStyle name="20% - Accent2 2 2" xfId="256" xr:uid="{ADBFFB7F-1B33-46E7-818B-9A0CC8688015}"/>
+    <cellStyle name="20% - Accent2 2 2 2" xfId="519" xr:uid="{69BF654A-F853-4922-AEE9-9C419ACF41CD}"/>
+    <cellStyle name="20% - Accent2 2 2 2 2" xfId="901" xr:uid="{6537FF73-81C8-4232-9C9E-F3DE3E7A952C}"/>
+    <cellStyle name="20% - Accent2 2 2 2 2 2" xfId="2257" xr:uid="{1FF86FBC-D25F-4F42-9522-98752ED6A064}"/>
+    <cellStyle name="20% - Accent2 2 2 2 3" xfId="1286" xr:uid="{C7CF40C7-4944-472F-B0A6-0C3E671ADADD}"/>
+    <cellStyle name="20% - Accent2 2 2 2 4" xfId="1877" xr:uid="{0BB7D7D9-AF6F-4C3B-96D1-C485999409D5}"/>
+    <cellStyle name="20% - Accent2 2 2 3" xfId="631" xr:uid="{E74D0BE1-8E02-4A6C-B621-D8F4450870D2}"/>
+    <cellStyle name="20% - Accent2 2 2 3 2" xfId="1989" xr:uid="{38A1B5DD-4AB6-4471-B342-D7E58D5EBE72}"/>
+    <cellStyle name="20% - Accent2 2 2 4" xfId="773" xr:uid="{4C00F389-8E70-41F1-B64B-B5FA926574DA}"/>
+    <cellStyle name="20% - Accent2 2 2 4 2" xfId="2131" xr:uid="{DFDC1E20-71D0-461A-A2E5-DF3198A22A40}"/>
+    <cellStyle name="20% - Accent2 2 2 5" xfId="384" xr:uid="{BF9CBE21-B7B5-40A9-932A-43A7A8F4941A}"/>
+    <cellStyle name="20% - Accent2 2 2 5 2" xfId="1751" xr:uid="{57D4980A-6B16-403F-979B-B2E89999135D}"/>
+    <cellStyle name="20% - Accent2 2 2 6" xfId="1142" xr:uid="{5BEAAC37-7785-49B6-976B-F6A1C99602D5}"/>
+    <cellStyle name="20% - Accent2 2 2 7" xfId="1623" xr:uid="{98C93BF7-B244-4046-B40D-9ED3D8EEE94E}"/>
+    <cellStyle name="20% - Accent2 2 3" xfId="196" xr:uid="{DAA743C6-112B-4D70-A3A9-C34BF6273E4D}"/>
+    <cellStyle name="20% - Accent2 2 3 2" xfId="844" xr:uid="{5F6BE3D5-FB51-41DF-82EC-198BD5AB0E00}"/>
+    <cellStyle name="20% - Accent2 2 3 2 2" xfId="2201" xr:uid="{840FDBC7-AB44-4C9A-98E3-7E0922985C19}"/>
+    <cellStyle name="20% - Accent2 2 3 3" xfId="456" xr:uid="{2B5ED1BB-BE06-4BFD-8641-4504F10D6AD7}"/>
+    <cellStyle name="20% - Accent2 2 3 3 2" xfId="1821" xr:uid="{F2B2014E-003E-4B72-8444-DED592011DAB}"/>
+    <cellStyle name="20% - Accent2 2 3 4" xfId="1086" xr:uid="{13546510-968D-48CB-9A5F-A742D8970548}"/>
+    <cellStyle name="20% - Accent2 2 3 5" xfId="1565" xr:uid="{3B414127-7173-4A43-B369-F64872563BD9}"/>
+    <cellStyle name="20% - Accent2 2 4" xfId="575" xr:uid="{A1E492B8-D4CB-471C-B60A-5322C62220FF}"/>
+    <cellStyle name="20% - Accent2 2 4 2" xfId="1215" xr:uid="{4CAC1D1E-EDEA-49DE-B8FB-BE5DEE920896}"/>
+    <cellStyle name="20% - Accent2 2 4 3" xfId="1933" xr:uid="{7E1D888D-D217-416B-9322-2EAE617ED85F}"/>
+    <cellStyle name="20% - Accent2 2 5" xfId="715" xr:uid="{2C3FC7D3-2E7C-40A8-AE1F-A8CF02356340}"/>
+    <cellStyle name="20% - Accent2 2 5 2" xfId="2073" xr:uid="{09ABE321-BB6B-4308-8717-A03BD26B70A0}"/>
+    <cellStyle name="20% - Accent2 2 6" xfId="326" xr:uid="{A556BEA0-3077-4244-958A-36EECBB3A9EB}"/>
+    <cellStyle name="20% - Accent2 2 6 2" xfId="1693" xr:uid="{4B96D23B-5AF4-4D75-A0D8-3B76F6B8CAFB}"/>
+    <cellStyle name="20% - Accent2 2 7" xfId="126" xr:uid="{A921838F-9C67-4702-A42E-43C82AD24C28}"/>
+    <cellStyle name="20% - Accent2 2 7 2" xfId="1495" xr:uid="{993D5A87-2CC1-4906-9144-46DFF4B9C52B}"/>
+    <cellStyle name="20% - Accent2 2 8" xfId="1016" xr:uid="{AFE3E298-A121-44F8-A497-6E6EAFC445FF}"/>
+    <cellStyle name="20% - Accent2 2 9" xfId="1425" xr:uid="{1C689315-6A36-4B33-A76F-A974F8AA02C6}"/>
+    <cellStyle name="20% - Accent2 3" xfId="69" xr:uid="{A3716E0A-5AAB-4FE5-95EE-F2991253A681}"/>
+    <cellStyle name="20% - Accent2 3 2" xfId="270" xr:uid="{16F722E4-2A31-4CF3-A1E3-476E9B0DE4E5}"/>
+    <cellStyle name="20% - Accent2 3 2 2" xfId="533" xr:uid="{D8294D43-4153-4E54-86AE-C56368D77903}"/>
+    <cellStyle name="20% - Accent2 3 2 2 2" xfId="915" xr:uid="{C522CCAB-4D37-46AE-86B7-C34A4D49BE68}"/>
+    <cellStyle name="20% - Accent2 3 2 2 2 2" xfId="2271" xr:uid="{D61B7840-E9D5-4D73-B42D-41F28F993D83}"/>
+    <cellStyle name="20% - Accent2 3 2 2 3" xfId="1300" xr:uid="{81B0CB90-B8F4-4928-92EF-55CF0D0250B6}"/>
+    <cellStyle name="20% - Accent2 3 2 2 4" xfId="1891" xr:uid="{B322C713-6ACE-4BF1-9120-8F2ABA2B435C}"/>
+    <cellStyle name="20% - Accent2 3 2 3" xfId="645" xr:uid="{116B123F-91D7-4ADE-A235-4658F43E8C9B}"/>
+    <cellStyle name="20% - Accent2 3 2 3 2" xfId="2003" xr:uid="{677FA714-1EC3-4F77-8D7E-7D3253771612}"/>
+    <cellStyle name="20% - Accent2 3 2 4" xfId="787" xr:uid="{8EA99EFF-1229-4AD3-95ED-BFCCCD0F72E1}"/>
+    <cellStyle name="20% - Accent2 3 2 4 2" xfId="2145" xr:uid="{DC35AEC0-2D65-46E9-B265-A861A3935D8A}"/>
+    <cellStyle name="20% - Accent2 3 2 5" xfId="398" xr:uid="{644AF8FD-0027-417D-A39D-B4002B5B428D}"/>
+    <cellStyle name="20% - Accent2 3 2 5 2" xfId="1765" xr:uid="{8E482D71-46A0-4D4C-AC5F-CE15195A492E}"/>
+    <cellStyle name="20% - Accent2 3 2 6" xfId="1156" xr:uid="{5955C327-D24C-4F25-B440-E1B5C92C4DB5}"/>
+    <cellStyle name="20% - Accent2 3 2 7" xfId="1637" xr:uid="{FFA9C197-BF7F-414F-B940-4D60C07E3678}"/>
+    <cellStyle name="20% - Accent2 3 3" xfId="210" xr:uid="{016223EB-EA0F-4294-BCA5-65FCF693E2D6}"/>
+    <cellStyle name="20% - Accent2 3 3 2" xfId="858" xr:uid="{7962C391-DB26-47D4-B506-C3DBDA787626}"/>
+    <cellStyle name="20% - Accent2 3 3 2 2" xfId="2215" xr:uid="{C1FCCA79-2D8A-4D37-A9CA-D15F534E5D58}"/>
+    <cellStyle name="20% - Accent2 3 3 3" xfId="470" xr:uid="{F507B5C4-D4BD-4E40-86F1-819416EDCCD4}"/>
+    <cellStyle name="20% - Accent2 3 3 3 2" xfId="1835" xr:uid="{4FBE7819-AF91-4114-9CD1-DDE1EEE05DB4}"/>
+    <cellStyle name="20% - Accent2 3 3 4" xfId="1100" xr:uid="{CE003E2C-40FE-4E6C-B55E-7088A1213BE1}"/>
+    <cellStyle name="20% - Accent2 3 3 5" xfId="1579" xr:uid="{0C9F2DAC-B277-43F1-AA19-CD5705434B65}"/>
+    <cellStyle name="20% - Accent2 3 4" xfId="589" xr:uid="{0F35BA0F-5E57-4937-BCF4-8A6C406B325E}"/>
+    <cellStyle name="20% - Accent2 3 4 2" xfId="1229" xr:uid="{79614DEC-89E6-4E39-B093-DDFEB10451BC}"/>
+    <cellStyle name="20% - Accent2 3 4 3" xfId="1947" xr:uid="{1C2F352E-B9B0-491B-A353-A41E57AB9883}"/>
+    <cellStyle name="20% - Accent2 3 5" xfId="729" xr:uid="{3614539C-42D0-4A0F-9C0C-19187A0372CA}"/>
+    <cellStyle name="20% - Accent2 3 5 2" xfId="2087" xr:uid="{AB81EA74-D43D-423F-8437-29BB48108275}"/>
+    <cellStyle name="20% - Accent2 3 6" xfId="340" xr:uid="{3B1D7064-D97E-4223-AF19-1322932A198D}"/>
+    <cellStyle name="20% - Accent2 3 6 2" xfId="1707" xr:uid="{6667BE59-AA4D-460B-89A3-6CF1239F5CD6}"/>
+    <cellStyle name="20% - Accent2 3 7" xfId="140" xr:uid="{502E38C3-8C1B-4A77-B655-1A5A719D3ADE}"/>
+    <cellStyle name="20% - Accent2 3 7 2" xfId="1509" xr:uid="{EC8B9C7B-D8CB-4841-AEE7-B982BAB49FAE}"/>
+    <cellStyle name="20% - Accent2 3 8" xfId="1030" xr:uid="{EA2047B4-13EC-403B-A426-E41A70639857}"/>
+    <cellStyle name="20% - Accent2 3 9" xfId="1439" xr:uid="{67B589B4-99D4-420C-B7DF-190D2101C8D2}"/>
+    <cellStyle name="20% - Accent2 4" xfId="83" xr:uid="{B8BCE255-E3B2-42C9-ABD7-12B83B90396E}"/>
+    <cellStyle name="20% - Accent2 4 2" xfId="283" xr:uid="{A50D5A46-21FB-47ED-A067-877F64A06DD1}"/>
+    <cellStyle name="20% - Accent2 4 2 2" xfId="547" xr:uid="{60B14A45-F727-497F-830B-BA70B784E2A5}"/>
+    <cellStyle name="20% - Accent2 4 2 2 2" xfId="929" xr:uid="{090269B9-8FBB-4C87-84E6-3783B701CD48}"/>
+    <cellStyle name="20% - Accent2 4 2 2 2 2" xfId="2285" xr:uid="{F09E4DDF-D80D-411B-A157-BBF6FF7883D7}"/>
+    <cellStyle name="20% - Accent2 4 2 2 3" xfId="1314" xr:uid="{DC88A561-365F-4509-AF54-FF4D5913821C}"/>
+    <cellStyle name="20% - Accent2 4 2 2 4" xfId="1905" xr:uid="{338433A2-F424-4924-8A47-8801EBF970AB}"/>
+    <cellStyle name="20% - Accent2 4 2 3" xfId="659" xr:uid="{A257CCAC-97B1-46DB-A74E-1710CF0A47EB}"/>
+    <cellStyle name="20% - Accent2 4 2 3 2" xfId="2017" xr:uid="{8B82B71C-7BAF-4CB6-A2D3-BE049E4B76D9}"/>
+    <cellStyle name="20% - Accent2 4 2 4" xfId="800" xr:uid="{74C04292-3193-4C5C-BAB5-4366D917E83A}"/>
+    <cellStyle name="20% - Accent2 4 2 4 2" xfId="2158" xr:uid="{AAD1590A-0CD2-47A1-A404-478C589C8B31}"/>
+    <cellStyle name="20% - Accent2 4 2 5" xfId="411" xr:uid="{F63B188C-9537-4156-B4EA-7C175A03F52F}"/>
+    <cellStyle name="20% - Accent2 4 2 5 2" xfId="1778" xr:uid="{F2AA2695-5B12-4CEC-86AF-2800B262DAD5}"/>
+    <cellStyle name="20% - Accent2 4 2 6" xfId="1170" xr:uid="{22307B94-061F-4C72-99F8-1E89FC236952}"/>
+    <cellStyle name="20% - Accent2 4 2 7" xfId="1650" xr:uid="{6ACEB614-8033-45DC-B074-89D2EEDB0546}"/>
+    <cellStyle name="20% - Accent2 4 3" xfId="224" xr:uid="{57D3897F-462D-4AE6-A1A3-A5BD131AE86D}"/>
+    <cellStyle name="20% - Accent2 4 3 2" xfId="872" xr:uid="{617FAFCA-D9D7-4DE0-B7DE-CD7DF9B48667}"/>
+    <cellStyle name="20% - Accent2 4 3 2 2" xfId="2229" xr:uid="{298FE312-24D9-41CA-B499-34CFFFE33A0C}"/>
+    <cellStyle name="20% - Accent2 4 3 3" xfId="484" xr:uid="{81BCFD92-44C3-4E53-B44E-F3828FFBE3D4}"/>
+    <cellStyle name="20% - Accent2 4 3 3 2" xfId="1849" xr:uid="{EC78E915-CCB2-401C-97CB-E260DF9606D5}"/>
+    <cellStyle name="20% - Accent2 4 3 4" xfId="1114" xr:uid="{9651BB12-0EE9-4478-9C0B-7571F6B49F24}"/>
+    <cellStyle name="20% - Accent2 4 3 5" xfId="1593" xr:uid="{001668AB-F0DD-47C6-861C-7E70240A4F11}"/>
+    <cellStyle name="20% - Accent2 4 4" xfId="603" xr:uid="{76F2E484-8F1F-41B0-9417-3D00C992C55F}"/>
+    <cellStyle name="20% - Accent2 4 4 2" xfId="1243" xr:uid="{DACA8251-DE2D-4DA9-843C-C6A3BD80D824}"/>
+    <cellStyle name="20% - Accent2 4 4 3" xfId="1961" xr:uid="{15C43ECE-1A0C-4C09-8D0C-2FDC8E103E11}"/>
+    <cellStyle name="20% - Accent2 4 5" xfId="743" xr:uid="{53991C67-9427-433D-AFD9-C1AFEB677712}"/>
+    <cellStyle name="20% - Accent2 4 5 2" xfId="2101" xr:uid="{C02F78AA-C082-4747-A739-1E205DB87406}"/>
+    <cellStyle name="20% - Accent2 4 6" xfId="354" xr:uid="{A0329962-6BE9-4F0C-8817-269EAF3EE6F0}"/>
+    <cellStyle name="20% - Accent2 4 6 2" xfId="1721" xr:uid="{C9C12165-C7C0-4A66-A814-4ACD6B4D7D60}"/>
+    <cellStyle name="20% - Accent2 4 7" xfId="154" xr:uid="{299F42CC-E016-4B8F-9288-3D26456CBB12}"/>
+    <cellStyle name="20% - Accent2 4 7 2" xfId="1523" xr:uid="{C33E8091-7B9A-4F54-9752-B3514E933CEB}"/>
+    <cellStyle name="20% - Accent2 4 8" xfId="1044" xr:uid="{A2BCFF34-885C-4B11-9F54-676C145F56DD}"/>
+    <cellStyle name="20% - Accent2 4 9" xfId="1453" xr:uid="{5CC0491F-9E01-41F1-BDAF-DCC2EF5136D1}"/>
+    <cellStyle name="20% - Accent2 5" xfId="97" xr:uid="{D094BFBC-2474-4EE2-9BD2-A2DA61062DD1}"/>
+    <cellStyle name="20% - Accent2 5 2" xfId="240" xr:uid="{AF334843-396E-4A5A-9302-A3C70960B7E1}"/>
+    <cellStyle name="20% - Accent2 5 2 2" xfId="885" xr:uid="{00CA2E49-D361-4D46-AC01-C66C21602260}"/>
+    <cellStyle name="20% - Accent2 5 2 2 2" xfId="2241" xr:uid="{9EE73759-F4CA-427D-8828-EF740BFACCD3}"/>
+    <cellStyle name="20% - Accent2 5 2 3" xfId="500" xr:uid="{25FD0569-E58A-4FF5-84ED-4F5827D0218F}"/>
+    <cellStyle name="20% - Accent2 5 2 3 2" xfId="1861" xr:uid="{50E2015D-03FF-4826-AA24-EB2C3509F12F}"/>
+    <cellStyle name="20% - Accent2 5 2 4" xfId="1126" xr:uid="{E364736B-0965-46FB-B614-96CE1B21755E}"/>
+    <cellStyle name="20% - Accent2 5 2 5" xfId="1607" xr:uid="{F80AA6BD-95A8-4098-95B9-8A719C638951}"/>
+    <cellStyle name="20% - Accent2 5 3" xfId="673" xr:uid="{EC7936C3-63DE-4AAA-BE44-19E59DA2FDFF}"/>
+    <cellStyle name="20% - Accent2 5 3 2" xfId="1257" xr:uid="{07BF313F-7F89-47E9-9985-2CC0C88AB073}"/>
+    <cellStyle name="20% - Accent2 5 3 3" xfId="2031" xr:uid="{0DD491D4-C14D-481C-925C-A0B2E77B12A8}"/>
+    <cellStyle name="20% - Accent2 5 4" xfId="757" xr:uid="{E18C92A8-803D-4C27-97EF-E5D8B3FBA661}"/>
+    <cellStyle name="20% - Accent2 5 4 2" xfId="2115" xr:uid="{EE953A09-598A-448C-8172-0C7025335114}"/>
+    <cellStyle name="20% - Accent2 5 5" xfId="368" xr:uid="{A23BDD63-5DB9-48C5-A8A1-96CC0F6FD67F}"/>
+    <cellStyle name="20% - Accent2 5 5 2" xfId="1735" xr:uid="{2FD7714F-81B7-4860-82E8-EC2A3A60F6E8}"/>
+    <cellStyle name="20% - Accent2 5 6" xfId="168" xr:uid="{B4004DDC-EB19-4066-907A-908E8C690621}"/>
+    <cellStyle name="20% - Accent2 5 6 2" xfId="1537" xr:uid="{AA188850-5ACC-44B4-B34F-6E9D5F6DD292}"/>
+    <cellStyle name="20% - Accent2 5 7" xfId="1058" xr:uid="{52EF1EF5-E3AF-45E6-B287-3AD579200D82}"/>
+    <cellStyle name="20% - Accent2 5 8" xfId="1467" xr:uid="{93D80CEE-9B84-4039-815B-E54272CBB469}"/>
+    <cellStyle name="20% - Accent2 6" xfId="180" xr:uid="{A4FE9015-8670-4228-9BCB-2F014244FA3E}"/>
+    <cellStyle name="20% - Accent2 6 2" xfId="615" xr:uid="{5555A34A-4FA5-42FA-9B2C-04A4EF5E89FE}"/>
+    <cellStyle name="20% - Accent2 6 2 2" xfId="1270" xr:uid="{CF7AA88E-677F-4FCF-A2E8-1DA519F60BD1}"/>
+    <cellStyle name="20% - Accent2 6 2 3" xfId="1973" xr:uid="{947E1881-AE1A-4AC0-8061-0E4793600158}"/>
+    <cellStyle name="20% - Accent2 6 3" xfId="815" xr:uid="{FEF04FE6-D6B3-4C22-B8B1-E5EE7982EC75}"/>
+    <cellStyle name="20% - Accent2 6 3 2" xfId="2173" xr:uid="{6ADC478D-AB74-4E74-BB58-FF7FD7E3EA11}"/>
+    <cellStyle name="20% - Accent2 6 4" xfId="426" xr:uid="{07BD2695-6786-4F98-BBB8-6F7CC341EE9F}"/>
+    <cellStyle name="20% - Accent2 6 4 2" xfId="1793" xr:uid="{D344471C-BD8D-433D-8704-9B5061273D8C}"/>
+    <cellStyle name="20% - Accent2 6 5" xfId="1070" xr:uid="{2DFA3F9A-A65B-4BA5-B77A-33D36A4C970A}"/>
+    <cellStyle name="20% - Accent2 6 6" xfId="1549" xr:uid="{6DF51922-051A-42F1-BB94-A49EE5DFEE08}"/>
+    <cellStyle name="20% - Accent2 7" xfId="298" xr:uid="{337BB41A-F678-455E-A742-3F6D5FF2E92F}"/>
+    <cellStyle name="20% - Accent2 7 2" xfId="687" xr:uid="{2912F4CB-5B59-4899-AA4C-8A4AB7F57DBB}"/>
+    <cellStyle name="20% - Accent2 7 2 2" xfId="1328" xr:uid="{10FBA897-7BD2-4ECD-BEDD-688FD9188D36}"/>
+    <cellStyle name="20% - Accent2 7 2 3" xfId="2045" xr:uid="{FBD0AF7E-7FA6-4493-9314-87E1B5448184}"/>
+    <cellStyle name="20% - Accent2 7 3" xfId="828" xr:uid="{052A2D18-A612-4694-805C-E6702BD18B7B}"/>
+    <cellStyle name="20% - Accent2 7 3 2" xfId="2185" xr:uid="{C214E403-B08E-479A-9626-FF471555B8F8}"/>
+    <cellStyle name="20% - Accent2 7 4" xfId="440" xr:uid="{673F66EF-1F58-4BF5-A06B-E4BA67B465EB}"/>
+    <cellStyle name="20% - Accent2 7 4 2" xfId="1805" xr:uid="{AAE2EA68-B88B-4BBE-93F6-0C1CFA90C78F}"/>
+    <cellStyle name="20% - Accent2 7 5" xfId="1184" xr:uid="{47C02B2C-37FD-4764-B95E-D8369991168C}"/>
+    <cellStyle name="20% - Accent2 7 6" xfId="1665" xr:uid="{3A28A9D4-89AD-40C5-A465-CD8710244AD7}"/>
+    <cellStyle name="20% - Accent2 8" xfId="559" xr:uid="{DED73A8F-D786-4996-9A0A-738345DDC9AA}"/>
+    <cellStyle name="20% - Accent2 8 2" xfId="1198" xr:uid="{FA7A5124-E03A-40CF-A179-C30D41578361}"/>
+    <cellStyle name="20% - Accent2 8 3" xfId="1917" xr:uid="{352A8CBB-2B47-4D7D-B616-BEF78F035C4C}"/>
+    <cellStyle name="20% - Accent2 9" xfId="699" xr:uid="{BD53D093-4E70-4D84-8D2E-B298712E60F5}"/>
+    <cellStyle name="20% - Accent2 9 2" xfId="1342" xr:uid="{F60C6F15-9C29-42B9-A5F7-825A13084A23}"/>
+    <cellStyle name="20% - Accent2 9 3" xfId="2057" xr:uid="{2CDDD437-014A-488F-8B82-83AEE2822626}"/>
+    <cellStyle name="20% - Accent3" xfId="23" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3 10" xfId="312" xr:uid="{624CB621-10BE-447E-99F0-7EED36C67340}"/>
+    <cellStyle name="20% - Accent3 10 2" xfId="1358" xr:uid="{7AD5E283-F21B-4D01-9F2C-204299C0DC13}"/>
+    <cellStyle name="20% - Accent3 10 3" xfId="1679" xr:uid="{C3ECF11F-5406-42CB-B3A5-08F174E976DA}"/>
+    <cellStyle name="20% - Accent3 11" xfId="112" xr:uid="{102B751D-663B-4942-95AC-72E9397CAD86}"/>
+    <cellStyle name="20% - Accent3 11 2" xfId="1371" xr:uid="{C9081249-DB6A-4991-9CBD-ED58F36FFC73}"/>
+    <cellStyle name="20% - Accent3 11 3" xfId="1481" xr:uid="{909687CD-0AF7-4A92-B57C-80A5B80D5231}"/>
+    <cellStyle name="20% - Accent3 12" xfId="945" xr:uid="{1CC59B79-8248-49C3-B3DA-5FA586992EB5}"/>
+    <cellStyle name="20% - Accent3 12 2" xfId="1384" xr:uid="{940E55EF-0AE7-41D4-9D96-6A9854DDDAA1}"/>
+    <cellStyle name="20% - Accent3 12 3" xfId="2301" xr:uid="{B6BD012B-AB23-4BC3-85A4-26D03E4F2B32}"/>
+    <cellStyle name="20% - Accent3 13" xfId="959" xr:uid="{51A7BF2B-5FAF-4B1B-9681-0CD886A95C6D}"/>
+    <cellStyle name="20% - Accent3 13 2" xfId="1398" xr:uid="{6F78D4BC-81CB-486A-865F-F0FE51C2356A}"/>
+    <cellStyle name="20% - Accent3 13 3" xfId="2315" xr:uid="{B5E8D7E1-090D-44BC-AA0F-06F76A6B94D1}"/>
+    <cellStyle name="20% - Accent3 14" xfId="973" xr:uid="{AD5F2E32-D592-4ECF-AB1C-BC0E30C426FE}"/>
+    <cellStyle name="20% - Accent3 14 2" xfId="2329" xr:uid="{9B22E09C-3AF3-4ABF-A230-1834D8809AFF}"/>
+    <cellStyle name="20% - Accent3 15" xfId="989" xr:uid="{5C403BDA-D7E3-43EE-B41B-2D3965CB4E1E}"/>
+    <cellStyle name="20% - Accent3 16" xfId="1002" xr:uid="{9FD3F947-B735-4F70-A976-53B2D41B9053}"/>
+    <cellStyle name="20% - Accent3 17" xfId="1411" xr:uid="{13572B86-5F5E-48AA-B207-1CBF243A157C}"/>
+    <cellStyle name="20% - Accent3 2" xfId="53" xr:uid="{0B61A4F2-2513-48EC-AD3D-72D13997F864}"/>
+    <cellStyle name="20% - Accent3 2 2" xfId="258" xr:uid="{FCFD8945-D496-46DC-9A9B-33C85E10356C}"/>
+    <cellStyle name="20% - Accent3 2 2 2" xfId="521" xr:uid="{2C11CD06-2CCC-40DD-A78D-95CC8DD9E5AD}"/>
+    <cellStyle name="20% - Accent3 2 2 2 2" xfId="903" xr:uid="{80518B9E-15D8-456C-81CE-9005A90CEEA4}"/>
+    <cellStyle name="20% - Accent3 2 2 2 2 2" xfId="2259" xr:uid="{D2BE2D0C-78B9-4393-A162-4E862DBD504C}"/>
+    <cellStyle name="20% - Accent3 2 2 2 3" xfId="1288" xr:uid="{EE8DA690-5724-40A0-95E0-CC0E2DB2C8F3}"/>
+    <cellStyle name="20% - Accent3 2 2 2 4" xfId="1879" xr:uid="{0EC59C7D-5479-4D2A-A629-E9D03BD683CC}"/>
+    <cellStyle name="20% - Accent3 2 2 3" xfId="633" xr:uid="{044B8534-39ED-407F-BF10-11C58A9A7250}"/>
+    <cellStyle name="20% - Accent3 2 2 3 2" xfId="1991" xr:uid="{69CB8571-0F48-4958-8DA2-25D4DA7DCC5C}"/>
+    <cellStyle name="20% - Accent3 2 2 4" xfId="775" xr:uid="{7C6A116A-9DC4-47E3-B413-CD896B4D9BB3}"/>
+    <cellStyle name="20% - Accent3 2 2 4 2" xfId="2133" xr:uid="{550F64B2-2BD7-42DF-9247-4F62F3E5D772}"/>
+    <cellStyle name="20% - Accent3 2 2 5" xfId="386" xr:uid="{B0B74B2F-48F1-49BB-BA2F-6977FA3CA32E}"/>
+    <cellStyle name="20% - Accent3 2 2 5 2" xfId="1753" xr:uid="{4ED59E3E-490E-480E-BFF9-48BAEF586771}"/>
+    <cellStyle name="20% - Accent3 2 2 6" xfId="1144" xr:uid="{624540F3-4710-4EFB-98B3-06818F4CD175}"/>
+    <cellStyle name="20% - Accent3 2 2 7" xfId="1625" xr:uid="{2AD7E32D-B4F0-4FD6-9AEE-78DDBB4A879A}"/>
+    <cellStyle name="20% - Accent3 2 3" xfId="198" xr:uid="{E843D835-231E-4A4B-B8B6-8E3D5CCF3A20}"/>
+    <cellStyle name="20% - Accent3 2 3 2" xfId="846" xr:uid="{D48D564A-F7A4-422A-8727-FC69746285BE}"/>
+    <cellStyle name="20% - Accent3 2 3 2 2" xfId="2203" xr:uid="{DDAC7D5E-5B4E-4CB8-875A-51A9E4F9FC76}"/>
+    <cellStyle name="20% - Accent3 2 3 3" xfId="458" xr:uid="{EA407AB4-5D5D-4639-BB46-7B97BFA3A5C1}"/>
+    <cellStyle name="20% - Accent3 2 3 3 2" xfId="1823" xr:uid="{CE25C292-2A09-4E41-A5ED-3EAA6F7E91C2}"/>
+    <cellStyle name="20% - Accent3 2 3 4" xfId="1088" xr:uid="{29C59C6A-1F7E-4D8A-87F8-8A5B8116F893}"/>
+    <cellStyle name="20% - Accent3 2 3 5" xfId="1567" xr:uid="{F88B6434-B0BB-40F4-9CFE-C2339A146F10}"/>
+    <cellStyle name="20% - Accent3 2 4" xfId="577" xr:uid="{B2ECFD8C-E638-4FC1-8E74-983728E5C6C6}"/>
+    <cellStyle name="20% - Accent3 2 4 2" xfId="1217" xr:uid="{CF3AED8F-1E8A-4EB0-BEB6-AE7072FDCBEC}"/>
+    <cellStyle name="20% - Accent3 2 4 3" xfId="1935" xr:uid="{886B3D8A-5555-481F-A757-08328AC58154}"/>
+    <cellStyle name="20% - Accent3 2 5" xfId="717" xr:uid="{32B2DD65-60E1-4C51-9231-B902BA77407E}"/>
+    <cellStyle name="20% - Accent3 2 5 2" xfId="2075" xr:uid="{3B3A2D95-0F2A-48E0-B399-2D9C1EC40521}"/>
+    <cellStyle name="20% - Accent3 2 6" xfId="328" xr:uid="{BB7873F5-26E2-4AEE-A2E0-A5964D18A23F}"/>
+    <cellStyle name="20% - Accent3 2 6 2" xfId="1695" xr:uid="{B8C4FEEE-F957-437E-BC4C-6B8777B263EB}"/>
+    <cellStyle name="20% - Accent3 2 7" xfId="128" xr:uid="{6A4524DD-7545-4936-9186-4F344B2695A7}"/>
+    <cellStyle name="20% - Accent3 2 7 2" xfId="1497" xr:uid="{4F9E4CAF-010E-489C-90DD-153EE55BB123}"/>
+    <cellStyle name="20% - Accent3 2 8" xfId="1018" xr:uid="{78E11162-D804-4780-8F26-2C9EF294DB80}"/>
+    <cellStyle name="20% - Accent3 2 9" xfId="1427" xr:uid="{9225957D-5F98-4BD8-AAA7-0088336233E7}"/>
+    <cellStyle name="20% - Accent3 3" xfId="71" xr:uid="{643DCC51-B93F-4236-B687-8BB4AEC3DAFA}"/>
+    <cellStyle name="20% - Accent3 3 2" xfId="272" xr:uid="{2B059B70-4726-45A0-947D-B75A88C6D098}"/>
+    <cellStyle name="20% - Accent3 3 2 2" xfId="535" xr:uid="{7B8616E0-5457-456A-8972-50AF10350496}"/>
+    <cellStyle name="20% - Accent3 3 2 2 2" xfId="917" xr:uid="{3AB6AB20-E0E7-48D5-A5FD-0D4EE6A33538}"/>
+    <cellStyle name="20% - Accent3 3 2 2 2 2" xfId="2273" xr:uid="{D5929BCA-9B4C-40B3-BBDB-76C26E6394E1}"/>
+    <cellStyle name="20% - Accent3 3 2 2 3" xfId="1302" xr:uid="{57419093-73AA-452B-9740-3166241B14AE}"/>
+    <cellStyle name="20% - Accent3 3 2 2 4" xfId="1893" xr:uid="{5ADAE880-A171-4D63-A523-E72D74967025}"/>
+    <cellStyle name="20% - Accent3 3 2 3" xfId="647" xr:uid="{2F066A45-9C0F-4B01-8C8B-180044E4088C}"/>
+    <cellStyle name="20% - Accent3 3 2 3 2" xfId="2005" xr:uid="{A729D754-BE56-41CE-AEF5-88CA642A2E51}"/>
+    <cellStyle name="20% - Accent3 3 2 4" xfId="789" xr:uid="{F44C89F9-40B6-484B-8610-5154D96A9241}"/>
+    <cellStyle name="20% - Accent3 3 2 4 2" xfId="2147" xr:uid="{543A325B-EC68-48C2-A00B-1CE78C4E0257}"/>
+    <cellStyle name="20% - Accent3 3 2 5" xfId="400" xr:uid="{96712D49-50AC-4C69-9E10-8F39F331DCC8}"/>
+    <cellStyle name="20% - Accent3 3 2 5 2" xfId="1767" xr:uid="{13460629-07B5-4989-BD40-BB37C72D48AB}"/>
+    <cellStyle name="20% - Accent3 3 2 6" xfId="1158" xr:uid="{8F1902B0-E678-460C-A2F5-1D1380C72A94}"/>
+    <cellStyle name="20% - Accent3 3 2 7" xfId="1639" xr:uid="{09985715-2C18-4D50-B068-9A04EB29012F}"/>
+    <cellStyle name="20% - Accent3 3 3" xfId="212" xr:uid="{E6988395-BD4F-44C6-BA1C-4BC2D774AD6E}"/>
+    <cellStyle name="20% - Accent3 3 3 2" xfId="860" xr:uid="{856E3764-F0F1-4465-BDB1-B1375BC48929}"/>
+    <cellStyle name="20% - Accent3 3 3 2 2" xfId="2217" xr:uid="{73F1D51F-AA18-406C-AD75-2789BBA55D17}"/>
+    <cellStyle name="20% - Accent3 3 3 3" xfId="472" xr:uid="{71E314A5-373B-4496-9440-F24B26F139F7}"/>
+    <cellStyle name="20% - Accent3 3 3 3 2" xfId="1837" xr:uid="{84D2E978-9A77-4FDB-9EE1-8431F71778EC}"/>
+    <cellStyle name="20% - Accent3 3 3 4" xfId="1102" xr:uid="{AE8D6647-F1F4-4965-A00D-7D492921D181}"/>
+    <cellStyle name="20% - Accent3 3 3 5" xfId="1581" xr:uid="{A5DA7326-1F98-4E62-B4DC-B4E0D293050B}"/>
+    <cellStyle name="20% - Accent3 3 4" xfId="591" xr:uid="{F9BA9C29-DD21-4744-9B7E-BC74D599C792}"/>
+    <cellStyle name="20% - Accent3 3 4 2" xfId="1231" xr:uid="{BFE72B0C-8EF0-426D-AEDD-BC62EC0503FD}"/>
+    <cellStyle name="20% - Accent3 3 4 3" xfId="1949" xr:uid="{36B52C02-5146-4A1F-B012-4CB70F41E71D}"/>
+    <cellStyle name="20% - Accent3 3 5" xfId="731" xr:uid="{AA9E389B-159B-4C96-908F-09142CAD60E5}"/>
+    <cellStyle name="20% - Accent3 3 5 2" xfId="2089" xr:uid="{F204E044-CCE4-4AED-8B58-374D32352D18}"/>
+    <cellStyle name="20% - Accent3 3 6" xfId="342" xr:uid="{2A6F2C67-0E67-4C78-943C-9B14DE14AFE4}"/>
+    <cellStyle name="20% - Accent3 3 6 2" xfId="1709" xr:uid="{25101684-6B1B-4796-9232-AD2B0564B28E}"/>
+    <cellStyle name="20% - Accent3 3 7" xfId="142" xr:uid="{1B88C22E-DE1E-4086-8AD5-A2B0ED426811}"/>
+    <cellStyle name="20% - Accent3 3 7 2" xfId="1511" xr:uid="{9FE9F796-8335-4DB5-8741-BC96BF0BF280}"/>
+    <cellStyle name="20% - Accent3 3 8" xfId="1032" xr:uid="{EDCDBFD3-9069-421D-93D6-1EBE2BCB50F9}"/>
+    <cellStyle name="20% - Accent3 3 9" xfId="1441" xr:uid="{60AAA237-4D61-461C-9336-3C1EC99D93FB}"/>
+    <cellStyle name="20% - Accent3 4" xfId="85" xr:uid="{2F680087-1B51-42C6-ACA9-13D5B2EB88CD}"/>
+    <cellStyle name="20% - Accent3 4 2" xfId="285" xr:uid="{AC0173FE-0660-4280-9FC2-DE165554356A}"/>
+    <cellStyle name="20% - Accent3 4 2 2" xfId="549" xr:uid="{CAE6B5CA-2B6E-484B-8A41-C64DBD4D3460}"/>
+    <cellStyle name="20% - Accent3 4 2 2 2" xfId="931" xr:uid="{079438AF-3FC4-4E3D-84B6-6142E2F471B2}"/>
+    <cellStyle name="20% - Accent3 4 2 2 2 2" xfId="2287" xr:uid="{3E455034-A1CC-483F-9D9C-9D86E5D6E2A5}"/>
+    <cellStyle name="20% - Accent3 4 2 2 3" xfId="1316" xr:uid="{AFC27C04-BBF7-4E3E-AF09-4FA7857EAFF3}"/>
+    <cellStyle name="20% - Accent3 4 2 2 4" xfId="1907" xr:uid="{AC1DFDF1-BC08-4FDB-A216-CC7E4389E953}"/>
+    <cellStyle name="20% - Accent3 4 2 3" xfId="661" xr:uid="{292DAEAE-ACC8-463A-8D36-F893596894FA}"/>
+    <cellStyle name="20% - Accent3 4 2 3 2" xfId="2019" xr:uid="{BC400A16-6157-4703-BA5A-15B419CF9F3D}"/>
+    <cellStyle name="20% - Accent3 4 2 4" xfId="802" xr:uid="{629C7483-151C-4AC5-8FAC-DB451F0ED80E}"/>
+    <cellStyle name="20% - Accent3 4 2 4 2" xfId="2160" xr:uid="{AC502529-DB2A-43F4-9046-3721D3B5464B}"/>
+    <cellStyle name="20% - Accent3 4 2 5" xfId="413" xr:uid="{B1BB26C3-6171-4402-B2D9-9AD1A8B4388C}"/>
+    <cellStyle name="20% - Accent3 4 2 5 2" xfId="1780" xr:uid="{F79A8D65-C268-4DB2-846C-4A9E785F568D}"/>
+    <cellStyle name="20% - Accent3 4 2 6" xfId="1172" xr:uid="{280F3C19-13DB-45C4-9DE2-141316CB8070}"/>
+    <cellStyle name="20% - Accent3 4 2 7" xfId="1652" xr:uid="{D8DB67CB-0150-4808-91FB-F80155EB910C}"/>
+    <cellStyle name="20% - Accent3 4 3" xfId="226" xr:uid="{60ADC9E6-5800-4F14-A9EE-F03AE7145B87}"/>
+    <cellStyle name="20% - Accent3 4 3 2" xfId="874" xr:uid="{E925DA3D-6937-4166-9D36-9FDA69B941B4}"/>
+    <cellStyle name="20% - Accent3 4 3 2 2" xfId="2231" xr:uid="{66F0B16E-33BE-40A4-8B0F-966ACF4A15BA}"/>
+    <cellStyle name="20% - Accent3 4 3 3" xfId="486" xr:uid="{3E1C0697-C909-4977-A9AF-B567B0846236}"/>
+    <cellStyle name="20% - Accent3 4 3 3 2" xfId="1851" xr:uid="{D0B97777-2EDC-4908-B7F8-8160B06E788A}"/>
+    <cellStyle name="20% - Accent3 4 3 4" xfId="1116" xr:uid="{FE43B131-BCD9-4095-87B7-AD96BFE7DF23}"/>
+    <cellStyle name="20% - Accent3 4 3 5" xfId="1595" xr:uid="{C8D0F75B-B936-4E00-BE87-1092D402320A}"/>
+    <cellStyle name="20% - Accent3 4 4" xfId="605" xr:uid="{BA232CF4-969A-462A-9256-8BE9C57C56D2}"/>
+    <cellStyle name="20% - Accent3 4 4 2" xfId="1245" xr:uid="{A55B6F0C-736B-40EE-B73C-345428909A49}"/>
+    <cellStyle name="20% - Accent3 4 4 3" xfId="1963" xr:uid="{1519C75D-EB0F-42E0-AB89-FCF6F245C263}"/>
+    <cellStyle name="20% - Accent3 4 5" xfId="745" xr:uid="{4ED081FE-CE3F-4161-AC7F-34F63D6EAC30}"/>
+    <cellStyle name="20% - Accent3 4 5 2" xfId="2103" xr:uid="{AD230BD5-BC09-48EA-8A15-03036DF2FC22}"/>
+    <cellStyle name="20% - Accent3 4 6" xfId="356" xr:uid="{8F1059E1-F584-4CCE-A1D6-CEC211E4477E}"/>
+    <cellStyle name="20% - Accent3 4 6 2" xfId="1723" xr:uid="{2D3E558C-47CD-4BDD-ADDC-983B7669B381}"/>
+    <cellStyle name="20% - Accent3 4 7" xfId="156" xr:uid="{F752E24F-3A31-4890-A3EE-67D9C0CF80F5}"/>
+    <cellStyle name="20% - Accent3 4 7 2" xfId="1525" xr:uid="{822BA23E-E786-48ED-9F85-45B051D72C27}"/>
+    <cellStyle name="20% - Accent3 4 8" xfId="1046" xr:uid="{AC52D67B-4499-4B0C-A06A-70838C6355FA}"/>
+    <cellStyle name="20% - Accent3 4 9" xfId="1455" xr:uid="{B339D89A-C5C2-4BD3-8A5F-372D2259FE87}"/>
+    <cellStyle name="20% - Accent3 5" xfId="99" xr:uid="{A788E4B4-869A-4C9A-8CDF-E4F8045C5E1C}"/>
+    <cellStyle name="20% - Accent3 5 2" xfId="242" xr:uid="{E4FDFDE6-9C2C-470D-B218-45250CD4E29D}"/>
+    <cellStyle name="20% - Accent3 5 2 2" xfId="887" xr:uid="{4E3246B5-D66E-4E1D-A79D-45AA65D05C3F}"/>
+    <cellStyle name="20% - Accent3 5 2 2 2" xfId="2243" xr:uid="{B505FF0B-2E91-4E07-B846-44B5F4AFD169}"/>
+    <cellStyle name="20% - Accent3 5 2 3" xfId="502" xr:uid="{A5DE38C0-CC5F-40C9-B565-FD712D738900}"/>
+    <cellStyle name="20% - Accent3 5 2 3 2" xfId="1863" xr:uid="{B3567274-48AF-47BF-AF46-DFE10512BD54}"/>
+    <cellStyle name="20% - Accent3 5 2 4" xfId="1128" xr:uid="{39130520-9750-4D52-8D6F-8CBA64A319DB}"/>
+    <cellStyle name="20% - Accent3 5 2 5" xfId="1609" xr:uid="{56AD5971-1282-4FA1-917F-4BAE87E64284}"/>
+    <cellStyle name="20% - Accent3 5 3" xfId="675" xr:uid="{EB2E41B3-914B-4AF5-AF9D-F5B5A22FEC42}"/>
+    <cellStyle name="20% - Accent3 5 3 2" xfId="1259" xr:uid="{2775F86E-4212-4234-918D-8099BE7CB6E4}"/>
+    <cellStyle name="20% - Accent3 5 3 3" xfId="2033" xr:uid="{2F2E5A17-ED18-4926-B6BF-7ECDACF5A37F}"/>
+    <cellStyle name="20% - Accent3 5 4" xfId="759" xr:uid="{184FBFF3-38C8-4C83-B29B-268C7E757AF3}"/>
+    <cellStyle name="20% - Accent3 5 4 2" xfId="2117" xr:uid="{C8F8A02B-2FD4-4B47-A178-BA64F21D74CE}"/>
+    <cellStyle name="20% - Accent3 5 5" xfId="370" xr:uid="{7542B624-B8E2-45A6-B131-27A794954623}"/>
+    <cellStyle name="20% - Accent3 5 5 2" xfId="1737" xr:uid="{9B01A7B6-361B-42B8-82E5-09052E9DB43E}"/>
+    <cellStyle name="20% - Accent3 5 6" xfId="170" xr:uid="{77A90AD6-D9E8-4F64-88B6-1B8F2CE5FCF6}"/>
+    <cellStyle name="20% - Accent3 5 6 2" xfId="1539" xr:uid="{1248E855-98F4-4940-8A18-EDE0A33651D5}"/>
+    <cellStyle name="20% - Accent3 5 7" xfId="1060" xr:uid="{91579641-1BB5-4E6E-B1D7-BB706D14D541}"/>
+    <cellStyle name="20% - Accent3 5 8" xfId="1469" xr:uid="{A84512E2-F4AC-45F7-938D-7F4ADC385A07}"/>
+    <cellStyle name="20% - Accent3 6" xfId="182" xr:uid="{9822CBAE-4B70-4F0C-B4F5-E13FDD9BB213}"/>
+    <cellStyle name="20% - Accent3 6 2" xfId="617" xr:uid="{A50F177E-7A6E-4FD2-8687-325532470A2F}"/>
+    <cellStyle name="20% - Accent3 6 2 2" xfId="1272" xr:uid="{9AB56E17-0A7A-4D99-86B5-597E400F2239}"/>
+    <cellStyle name="20% - Accent3 6 2 3" xfId="1975" xr:uid="{AD532514-FF7E-4C29-B393-560CC1972C98}"/>
+    <cellStyle name="20% - Accent3 6 3" xfId="817" xr:uid="{CD50EB74-9CE3-4B98-967D-492FC8C6D11E}"/>
+    <cellStyle name="20% - Accent3 6 3 2" xfId="2175" xr:uid="{58215BAC-FAE6-4782-9ED1-9DA9A19033C8}"/>
+    <cellStyle name="20% - Accent3 6 4" xfId="428" xr:uid="{0DF60740-8AC9-4B9F-B811-4AB24E0FD93B}"/>
+    <cellStyle name="20% - Accent3 6 4 2" xfId="1795" xr:uid="{631AB854-83A3-4B2E-9440-7007FDA04B48}"/>
+    <cellStyle name="20% - Accent3 6 5" xfId="1072" xr:uid="{65CBF978-03B2-43B6-95FD-CCDFBE7048B5}"/>
+    <cellStyle name="20% - Accent3 6 6" xfId="1551" xr:uid="{6A78D953-BF61-45F1-B60A-B13AD9E9F98C}"/>
+    <cellStyle name="20% - Accent3 7" xfId="300" xr:uid="{C06A3638-8C19-4A70-8203-605989C3D9BD}"/>
+    <cellStyle name="20% - Accent3 7 2" xfId="689" xr:uid="{B048C1C3-7A9F-4449-BFD3-0E5EF78C0285}"/>
+    <cellStyle name="20% - Accent3 7 2 2" xfId="1330" xr:uid="{8F94111E-5B75-47FF-ADA9-07024320ED74}"/>
+    <cellStyle name="20% - Accent3 7 2 3" xfId="2047" xr:uid="{04068FD2-99EC-4F40-A389-E34BE041C06D}"/>
+    <cellStyle name="20% - Accent3 7 3" xfId="830" xr:uid="{1C396714-15FF-4DCA-B1C7-B389A29C3EC0}"/>
+    <cellStyle name="20% - Accent3 7 3 2" xfId="2187" xr:uid="{6C3DC169-AB4B-4325-9CBB-ADF03F340024}"/>
+    <cellStyle name="20% - Accent3 7 4" xfId="442" xr:uid="{7195BF89-6235-4908-98BB-50D22803360D}"/>
+    <cellStyle name="20% - Accent3 7 4 2" xfId="1807" xr:uid="{073B4F5E-851E-46F8-A37E-35C041976164}"/>
+    <cellStyle name="20% - Accent3 7 5" xfId="1186" xr:uid="{584056C6-454A-411C-B580-D11230981E44}"/>
+    <cellStyle name="20% - Accent3 7 6" xfId="1667" xr:uid="{95D4120F-18EC-4033-8E77-7DF4CFFFA31D}"/>
+    <cellStyle name="20% - Accent3 8" xfId="561" xr:uid="{6FA678D0-B84A-48AC-B318-9134589045BE}"/>
+    <cellStyle name="20% - Accent3 8 2" xfId="1200" xr:uid="{E2167D03-A2DF-4401-8E22-0336BAEFFE44}"/>
+    <cellStyle name="20% - Accent3 8 3" xfId="1919" xr:uid="{E3C4017F-A9B2-42D8-AFB5-90A5E122D1FA}"/>
+    <cellStyle name="20% - Accent3 9" xfId="701" xr:uid="{E68F7C6C-EA53-432D-AED5-80ADC9433577}"/>
+    <cellStyle name="20% - Accent3 9 2" xfId="1344" xr:uid="{3918DE89-1575-4387-B358-4A43E71AB380}"/>
+    <cellStyle name="20% - Accent3 9 3" xfId="2059" xr:uid="{73AF6E1F-F183-4ACF-9A38-04C493E3D929}"/>
+    <cellStyle name="20% - Accent4" xfId="26" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4 10" xfId="314" xr:uid="{84E32266-1AD0-4949-A9E7-29837A6CC812}"/>
+    <cellStyle name="20% - Accent4 10 2" xfId="1360" xr:uid="{B214D6AF-03A4-4B2B-8341-28F9D58CB1A6}"/>
+    <cellStyle name="20% - Accent4 10 3" xfId="1681" xr:uid="{DB8CD0D1-FE00-4DDF-BF19-87EF793B1C5E}"/>
+    <cellStyle name="20% - Accent4 11" xfId="114" xr:uid="{28733A07-9D54-40BB-9955-1D0709BFEEFA}"/>
+    <cellStyle name="20% - Accent4 11 2" xfId="1373" xr:uid="{A2A73383-B2AE-4B24-9BE0-08F7BB81B123}"/>
+    <cellStyle name="20% - Accent4 11 3" xfId="1483" xr:uid="{9EEC8BAC-9FB7-46C0-AE63-F3FF7BF1E9B6}"/>
+    <cellStyle name="20% - Accent4 12" xfId="947" xr:uid="{F870E522-82B7-4E4F-8689-DC40E06FE15D}"/>
+    <cellStyle name="20% - Accent4 12 2" xfId="1386" xr:uid="{78C81C37-2392-4C60-ADF8-B28981E8FDAC}"/>
+    <cellStyle name="20% - Accent4 12 3" xfId="2303" xr:uid="{4B8A3062-1FA5-48C3-A9DA-E57F6C3F3E5A}"/>
+    <cellStyle name="20% - Accent4 13" xfId="961" xr:uid="{EC4E8C86-A7F0-4903-AF56-4498551AE1FF}"/>
+    <cellStyle name="20% - Accent4 13 2" xfId="1400" xr:uid="{BF52CBF3-8DE7-48F7-8CEF-F36548FFCB2F}"/>
+    <cellStyle name="20% - Accent4 13 3" xfId="2317" xr:uid="{FBCBD05E-BFE1-47D5-86D2-37FA3898B502}"/>
+    <cellStyle name="20% - Accent4 14" xfId="975" xr:uid="{F70E1E91-9A09-4D5D-AC04-8F0A59A78F7A}"/>
+    <cellStyle name="20% - Accent4 14 2" xfId="2331" xr:uid="{CF15E50D-B10C-44C7-AE3F-85B4CD80A974}"/>
+    <cellStyle name="20% - Accent4 15" xfId="991" xr:uid="{677FDAC8-7B80-40BE-886C-887BC2635E97}"/>
+    <cellStyle name="20% - Accent4 16" xfId="1004" xr:uid="{495749B5-1011-4CC6-8B2B-D6EE86532771}"/>
+    <cellStyle name="20% - Accent4 17" xfId="1413" xr:uid="{6EBA1CEF-3E2A-4CE0-8732-023EE14E600E}"/>
+    <cellStyle name="20% - Accent4 2" xfId="55" xr:uid="{EE43E381-D948-4AA5-9AE4-17BB33D83C0D}"/>
+    <cellStyle name="20% - Accent4 2 2" xfId="260" xr:uid="{468A970F-711B-4FE8-BE35-53674C9009F6}"/>
+    <cellStyle name="20% - Accent4 2 2 2" xfId="523" xr:uid="{F737756A-810C-4C85-BA2C-E96CEF445D29}"/>
+    <cellStyle name="20% - Accent4 2 2 2 2" xfId="905" xr:uid="{F2F0712B-7DF3-4DFB-BA48-82CA18B01ADA}"/>
+    <cellStyle name="20% - Accent4 2 2 2 2 2" xfId="2261" xr:uid="{43E239A9-3635-4D17-A7D4-5F502D85ACB5}"/>
+    <cellStyle name="20% - Accent4 2 2 2 3" xfId="1290" xr:uid="{C9C78543-FD35-48AC-83C5-73C9C8BE8CD2}"/>
+    <cellStyle name="20% - Accent4 2 2 2 4" xfId="1881" xr:uid="{24F5CD16-4C98-4E48-9F4E-893E5835CE04}"/>
+    <cellStyle name="20% - Accent4 2 2 3" xfId="635" xr:uid="{2DB5022A-9A07-4D67-B75F-6ED4F66FF3DD}"/>
+    <cellStyle name="20% - Accent4 2 2 3 2" xfId="1993" xr:uid="{F11B1109-FBB5-4104-9DAE-2E1C17BA4B4E}"/>
+    <cellStyle name="20% - Accent4 2 2 4" xfId="777" xr:uid="{13A1CDC8-34AC-4583-BDFD-157F9B61549D}"/>
+    <cellStyle name="20% - Accent4 2 2 4 2" xfId="2135" xr:uid="{906ABFBA-3A93-40C2-97C9-99DC228E1E76}"/>
+    <cellStyle name="20% - Accent4 2 2 5" xfId="388" xr:uid="{EC684AB5-9AE2-453D-950D-C4AB3319F750}"/>
+    <cellStyle name="20% - Accent4 2 2 5 2" xfId="1755" xr:uid="{5DBD153B-9914-4938-99A8-FD879C1FCB74}"/>
+    <cellStyle name="20% - Accent4 2 2 6" xfId="1146" xr:uid="{57758D88-88CE-4819-8286-5EC944F337A0}"/>
+    <cellStyle name="20% - Accent4 2 2 7" xfId="1627" xr:uid="{3A316A01-9A92-49FC-9F55-843AF5018761}"/>
+    <cellStyle name="20% - Accent4 2 3" xfId="200" xr:uid="{D20583F9-72E2-48B0-92F1-631ABA62A1B3}"/>
+    <cellStyle name="20% - Accent4 2 3 2" xfId="848" xr:uid="{D5E80D90-A42D-4E49-8674-9BFBF5AC6C5B}"/>
+    <cellStyle name="20% - Accent4 2 3 2 2" xfId="2205" xr:uid="{9D8EFD15-75E5-4A0E-AC8D-CEF01CEB090A}"/>
+    <cellStyle name="20% - Accent4 2 3 3" xfId="460" xr:uid="{C223D656-6965-474C-A461-F15D340D52B9}"/>
+    <cellStyle name="20% - Accent4 2 3 3 2" xfId="1825" xr:uid="{4516AB52-B57B-4244-945C-9E157E7C3ACB}"/>
+    <cellStyle name="20% - Accent4 2 3 4" xfId="1090" xr:uid="{7ABBD4FB-3E77-4AE7-9059-29C236F3CC91}"/>
+    <cellStyle name="20% - Accent4 2 3 5" xfId="1569" xr:uid="{76525549-FC0D-4BD6-AD07-EAF32DD3C500}"/>
+    <cellStyle name="20% - Accent4 2 4" xfId="579" xr:uid="{F6978EC7-39AA-47A8-9514-1004C7201DA9}"/>
+    <cellStyle name="20% - Accent4 2 4 2" xfId="1219" xr:uid="{F08B7240-F788-4FFB-AC11-7E17DA505502}"/>
+    <cellStyle name="20% - Accent4 2 4 3" xfId="1937" xr:uid="{EA3D9537-4339-4447-A2C6-0D539F6A5277}"/>
+    <cellStyle name="20% - Accent4 2 5" xfId="719" xr:uid="{E4210F7E-F3CA-4D98-97D3-FE8D5F1C290E}"/>
+    <cellStyle name="20% - Accent4 2 5 2" xfId="2077" xr:uid="{ABFDBCDA-9A5D-4C65-A99B-3179FDEBEA50}"/>
+    <cellStyle name="20% - Accent4 2 6" xfId="330" xr:uid="{80CAD70A-440B-4BAA-B95D-E61E1A310BF2}"/>
+    <cellStyle name="20% - Accent4 2 6 2" xfId="1697" xr:uid="{4A87D093-499C-4E45-895B-3184A104C069}"/>
+    <cellStyle name="20% - Accent4 2 7" xfId="130" xr:uid="{05C0EBB9-5391-4671-BC93-F9E7283BA1BC}"/>
+    <cellStyle name="20% - Accent4 2 7 2" xfId="1499" xr:uid="{AF554850-16F3-4477-A907-656340F7C613}"/>
+    <cellStyle name="20% - Accent4 2 8" xfId="1020" xr:uid="{DB0D63D6-F3B4-4E14-B670-E326D1BA55EB}"/>
+    <cellStyle name="20% - Accent4 2 9" xfId="1429" xr:uid="{1EFB196D-1382-4717-A04D-E67F71139BB4}"/>
+    <cellStyle name="20% - Accent4 3" xfId="73" xr:uid="{1E06157A-CA0D-4455-BD47-F17BACFBFC2A}"/>
+    <cellStyle name="20% - Accent4 3 2" xfId="274" xr:uid="{130CAED7-4FC0-442A-AB5F-601BA2B10913}"/>
+    <cellStyle name="20% - Accent4 3 2 2" xfId="537" xr:uid="{BA65E010-7557-48D2-965F-A663C9D6FCD4}"/>
+    <cellStyle name="20% - Accent4 3 2 2 2" xfId="919" xr:uid="{7C5216C2-7F7F-4503-BF8A-816FDFF12ECC}"/>
+    <cellStyle name="20% - Accent4 3 2 2 2 2" xfId="2275" xr:uid="{8E76D999-63FC-4F16-911B-91457D6FBBCD}"/>
+    <cellStyle name="20% - Accent4 3 2 2 3" xfId="1304" xr:uid="{20B2FFC3-3150-4B12-BE20-E8912973CA60}"/>
+    <cellStyle name="20% - Accent4 3 2 2 4" xfId="1895" xr:uid="{622D98F6-63C3-4BD2-9320-C5CA1F7CE6B8}"/>
+    <cellStyle name="20% - Accent4 3 2 3" xfId="649" xr:uid="{5300C553-F655-4196-B9CE-78F000E2A1A2}"/>
+    <cellStyle name="20% - Accent4 3 2 3 2" xfId="2007" xr:uid="{E4887BFB-D990-45C3-9A16-DAF16FED3B48}"/>
+    <cellStyle name="20% - Accent4 3 2 4" xfId="791" xr:uid="{0C85BD6F-1925-42C1-B18F-165686F248BA}"/>
+    <cellStyle name="20% - Accent4 3 2 4 2" xfId="2149" xr:uid="{3946C09F-7754-479A-B50F-B37FA4DAEDB6}"/>
+    <cellStyle name="20% - Accent4 3 2 5" xfId="402" xr:uid="{D3969EDA-E055-4FB2-9BC4-61E9B369916F}"/>
+    <cellStyle name="20% - Accent4 3 2 5 2" xfId="1769" xr:uid="{4A1C5D58-6843-48A6-A821-D2D11E378CF2}"/>
+    <cellStyle name="20% - Accent4 3 2 6" xfId="1160" xr:uid="{AA59111A-1B32-4F12-A3E4-C4743474DCF9}"/>
+    <cellStyle name="20% - Accent4 3 2 7" xfId="1641" xr:uid="{94F9C50E-6992-495D-BDD0-859545488577}"/>
+    <cellStyle name="20% - Accent4 3 3" xfId="214" xr:uid="{1476B9AE-87B4-4CC5-A97C-1EEA23DA7AA3}"/>
+    <cellStyle name="20% - Accent4 3 3 2" xfId="862" xr:uid="{EC28E977-1CBD-4CCC-9FC6-785C9B9F1ACE}"/>
+    <cellStyle name="20% - Accent4 3 3 2 2" xfId="2219" xr:uid="{3BEAE0C3-C01B-4678-90AA-526CC4F35E53}"/>
+    <cellStyle name="20% - Accent4 3 3 3" xfId="474" xr:uid="{68FCA14A-DE6C-47F0-B696-21693F0DA37F}"/>
+    <cellStyle name="20% - Accent4 3 3 3 2" xfId="1839" xr:uid="{08B1A497-919B-4EF1-B09A-E9C6BA86B7A0}"/>
+    <cellStyle name="20% - Accent4 3 3 4" xfId="1104" xr:uid="{8BB90887-8619-4A52-AB73-CC2B2E594CC9}"/>
+    <cellStyle name="20% - Accent4 3 3 5" xfId="1583" xr:uid="{D697B871-8618-455A-98E4-121FDD0090A6}"/>
+    <cellStyle name="20% - Accent4 3 4" xfId="593" xr:uid="{AA82ABC2-F1DE-433A-9060-CA95642173B6}"/>
+    <cellStyle name="20% - Accent4 3 4 2" xfId="1233" xr:uid="{57AA4C16-C236-4A33-8E19-CA32F6920D2B}"/>
+    <cellStyle name="20% - Accent4 3 4 3" xfId="1951" xr:uid="{D07D30D5-84A8-4CB9-A4CD-6289A8FE105C}"/>
+    <cellStyle name="20% - Accent4 3 5" xfId="733" xr:uid="{16E6DDE5-13C3-453C-BD95-678F389544AA}"/>
+    <cellStyle name="20% - Accent4 3 5 2" xfId="2091" xr:uid="{1A71F9E2-C9ED-47F0-9EF5-FBEE0074C06B}"/>
+    <cellStyle name="20% - Accent4 3 6" xfId="344" xr:uid="{31D30EC7-1F16-4E94-808B-AAA2ED4314EA}"/>
+    <cellStyle name="20% - Accent4 3 6 2" xfId="1711" xr:uid="{F51BFCB6-327F-450B-9B2E-DE94D1DA0CDF}"/>
+    <cellStyle name="20% - Accent4 3 7" xfId="144" xr:uid="{D21C35E7-26CE-41C2-84BD-C48B604D3D41}"/>
+    <cellStyle name="20% - Accent4 3 7 2" xfId="1513" xr:uid="{5061A5D6-BFAE-4D10-8C90-FBA62B762CCC}"/>
+    <cellStyle name="20% - Accent4 3 8" xfId="1034" xr:uid="{6C951B05-E269-4B07-9BAA-6DEB99F716AD}"/>
+    <cellStyle name="20% - Accent4 3 9" xfId="1443" xr:uid="{5FBE4931-C23C-4519-A515-1F915D3F12A6}"/>
+    <cellStyle name="20% - Accent4 4" xfId="87" xr:uid="{58816538-D437-403F-8DCD-2C831F624F36}"/>
+    <cellStyle name="20% - Accent4 4 2" xfId="287" xr:uid="{43D0B402-5116-41B5-A090-4667891F215E}"/>
+    <cellStyle name="20% - Accent4 4 2 2" xfId="551" xr:uid="{C05C07AC-E97A-4C22-BAE4-0393ACD73BE2}"/>
+    <cellStyle name="20% - Accent4 4 2 2 2" xfId="933" xr:uid="{D4F82AF1-0629-4462-A302-5AAB46598E2A}"/>
+    <cellStyle name="20% - Accent4 4 2 2 2 2" xfId="2289" xr:uid="{0DB1607A-DEC9-4F37-B98F-09907A1213AB}"/>
+    <cellStyle name="20% - Accent4 4 2 2 3" xfId="1318" xr:uid="{369D62D1-FE41-4A79-A59B-DF52F2F702E7}"/>
+    <cellStyle name="20% - Accent4 4 2 2 4" xfId="1909" xr:uid="{ACFF6965-59D7-41A8-ADE7-D85058375AF6}"/>
+    <cellStyle name="20% - Accent4 4 2 3" xfId="663" xr:uid="{1CF66C65-46A0-4656-B628-639510F964C0}"/>
+    <cellStyle name="20% - Accent4 4 2 3 2" xfId="2021" xr:uid="{42A2925F-836E-4638-BA11-EC390F2C3B1C}"/>
+    <cellStyle name="20% - Accent4 4 2 4" xfId="804" xr:uid="{DC2BE783-F314-4BC9-819C-445B2ABD6DD5}"/>
+    <cellStyle name="20% - Accent4 4 2 4 2" xfId="2162" xr:uid="{0A29D72E-13B6-46CA-B826-77A3AD787FA3}"/>
+    <cellStyle name="20% - Accent4 4 2 5" xfId="415" xr:uid="{362A2316-E76C-470A-8CEC-4D660968F90C}"/>
+    <cellStyle name="20% - Accent4 4 2 5 2" xfId="1782" xr:uid="{48FBB427-903D-4BB8-9DD4-C1651CA13ACD}"/>
+    <cellStyle name="20% - Accent4 4 2 6" xfId="1174" xr:uid="{45972B64-4985-40EC-BAA0-F20A903193E6}"/>
+    <cellStyle name="20% - Accent4 4 2 7" xfId="1654" xr:uid="{88B4976E-47F3-42A6-90B0-40CED1BF2840}"/>
+    <cellStyle name="20% - Accent4 4 3" xfId="228" xr:uid="{072D15AC-DE6A-4F1E-A2E0-E0194FF74756}"/>
+    <cellStyle name="20% - Accent4 4 3 2" xfId="876" xr:uid="{4BC913E3-2DB2-4A47-9048-484F7EE32CCD}"/>
+    <cellStyle name="20% - Accent4 4 3 2 2" xfId="2233" xr:uid="{AD0BEDD5-D02B-4129-A7A6-FC47BD524E3D}"/>
+    <cellStyle name="20% - Accent4 4 3 3" xfId="488" xr:uid="{56DCFC6F-0381-40FE-8490-F32D6349E01D}"/>
+    <cellStyle name="20% - Accent4 4 3 3 2" xfId="1853" xr:uid="{6F2C0708-65A5-4437-89D2-E16449C33EFC}"/>
+    <cellStyle name="20% - Accent4 4 3 4" xfId="1118" xr:uid="{2A3A3D48-CE9E-494F-97A6-31E17A62607E}"/>
+    <cellStyle name="20% - Accent4 4 3 5" xfId="1597" xr:uid="{84E9CA34-38EF-4F85-BC2B-B8D85C66E42B}"/>
+    <cellStyle name="20% - Accent4 4 4" xfId="607" xr:uid="{9FF28C05-27B3-4473-A4C1-73104EB2E632}"/>
+    <cellStyle name="20% - Accent4 4 4 2" xfId="1247" xr:uid="{F8D872FD-3A8A-40A4-9145-E26573B2B01D}"/>
+    <cellStyle name="20% - Accent4 4 4 3" xfId="1965" xr:uid="{5C7F6BF9-B5AA-429D-8071-68518FAB32CC}"/>
+    <cellStyle name="20% - Accent4 4 5" xfId="747" xr:uid="{A10F886D-FB64-4F33-8E8B-71DFA5E55909}"/>
+    <cellStyle name="20% - Accent4 4 5 2" xfId="2105" xr:uid="{C40F845B-D059-45A1-B428-709463B65E5C}"/>
+    <cellStyle name="20% - Accent4 4 6" xfId="358" xr:uid="{8B4E1F24-D0B2-4D2A-B01C-A8C5CA0E324F}"/>
+    <cellStyle name="20% - Accent4 4 6 2" xfId="1725" xr:uid="{1D935E3A-0A6A-4224-BD7B-B02AFC6154C3}"/>
+    <cellStyle name="20% - Accent4 4 7" xfId="158" xr:uid="{AC24B79E-2045-442D-B6BC-12DC16E1AF8C}"/>
+    <cellStyle name="20% - Accent4 4 7 2" xfId="1527" xr:uid="{01FFB088-95E1-40A8-A204-2AF4391B6714}"/>
+    <cellStyle name="20% - Accent4 4 8" xfId="1048" xr:uid="{EE06EE78-DD3B-4F42-9C4E-DCF3D7A4B7FA}"/>
+    <cellStyle name="20% - Accent4 4 9" xfId="1457" xr:uid="{FBBC54D8-5235-4A03-8F67-A409D3B10941}"/>
+    <cellStyle name="20% - Accent4 5" xfId="101" xr:uid="{97B361D0-72BD-45F9-B835-9C7F7CA80314}"/>
+    <cellStyle name="20% - Accent4 5 2" xfId="244" xr:uid="{02D5A2CF-4951-4D35-8E82-219167915B1D}"/>
+    <cellStyle name="20% - Accent4 5 2 2" xfId="889" xr:uid="{9949C6C3-3FB5-404E-A03F-5F75319F09ED}"/>
+    <cellStyle name="20% - Accent4 5 2 2 2" xfId="2245" xr:uid="{6EE56C6C-0ECB-40DB-A491-52561ECD1385}"/>
+    <cellStyle name="20% - Accent4 5 2 3" xfId="504" xr:uid="{4DC3E12B-5E77-4D07-8654-FF56E295C018}"/>
+    <cellStyle name="20% - Accent4 5 2 3 2" xfId="1865" xr:uid="{A22347C7-2BD6-4C89-85A9-5785ADD33C00}"/>
+    <cellStyle name="20% - Accent4 5 2 4" xfId="1130" xr:uid="{9794974C-E503-4FB0-8336-BAE578E2632F}"/>
+    <cellStyle name="20% - Accent4 5 2 5" xfId="1611" xr:uid="{22C045DD-70D7-4AD4-B092-4F42D0A22765}"/>
+    <cellStyle name="20% - Accent4 5 3" xfId="677" xr:uid="{0779E07A-5997-4AE5-A350-494337C7F080}"/>
+    <cellStyle name="20% - Accent4 5 3 2" xfId="1261" xr:uid="{D2A50779-E8D2-4179-95D2-01DB1F743581}"/>
+    <cellStyle name="20% - Accent4 5 3 3" xfId="2035" xr:uid="{E1714687-38F9-476C-9051-B0BD6EB4B2AE}"/>
+    <cellStyle name="20% - Accent4 5 4" xfId="761" xr:uid="{8035CE1E-02BE-47F7-85F5-1854642648EB}"/>
+    <cellStyle name="20% - Accent4 5 4 2" xfId="2119" xr:uid="{68A61AF5-D60D-47E0-A043-D16FF0AEF49A}"/>
+    <cellStyle name="20% - Accent4 5 5" xfId="372" xr:uid="{57E820F3-D8E0-4A5E-B7B6-2A1D90B509ED}"/>
+    <cellStyle name="20% - Accent4 5 5 2" xfId="1739" xr:uid="{2586D0C1-3D1A-4F04-9139-1C188867DDED}"/>
+    <cellStyle name="20% - Accent4 5 6" xfId="172" xr:uid="{0FD1FE2B-5554-4ADB-AFC1-24521DBF4F8E}"/>
+    <cellStyle name="20% - Accent4 5 6 2" xfId="1541" xr:uid="{9C1CEB54-58A7-484B-988C-87A5973FBF0C}"/>
+    <cellStyle name="20% - Accent4 5 7" xfId="1062" xr:uid="{01A0AA30-90B6-4160-A5B0-CB6E04E5AE0A}"/>
+    <cellStyle name="20% - Accent4 5 8" xfId="1471" xr:uid="{45FEEEEF-8452-4CB2-A52D-BE7E8DAD80A4}"/>
+    <cellStyle name="20% - Accent4 6" xfId="184" xr:uid="{69404FC6-7DFF-4559-97F9-63F0936404E9}"/>
+    <cellStyle name="20% - Accent4 6 2" xfId="619" xr:uid="{67F3B006-83AC-48BB-A89B-60F714B6BAD5}"/>
+    <cellStyle name="20% - Accent4 6 2 2" xfId="1274" xr:uid="{094567FA-A5BF-42F5-80D4-5447979C6934}"/>
+    <cellStyle name="20% - Accent4 6 2 3" xfId="1977" xr:uid="{2394E978-E688-4C83-B128-BC0E926C01CB}"/>
+    <cellStyle name="20% - Accent4 6 3" xfId="819" xr:uid="{D3DA8BE3-3BEE-49B3-BF29-F5312CDDB3AA}"/>
+    <cellStyle name="20% - Accent4 6 3 2" xfId="2177" xr:uid="{BE942BEF-2A93-4F5A-8685-C3FBA7C3E1DF}"/>
+    <cellStyle name="20% - Accent4 6 4" xfId="430" xr:uid="{0A2D0892-0BFD-499D-BB1B-5CA15E89EE72}"/>
+    <cellStyle name="20% - Accent4 6 4 2" xfId="1797" xr:uid="{BE43D484-8B78-46DB-89C3-F0B67319BF9E}"/>
+    <cellStyle name="20% - Accent4 6 5" xfId="1074" xr:uid="{1A0B4481-02F6-42C5-81E4-3874EBC3BF9E}"/>
+    <cellStyle name="20% - Accent4 6 6" xfId="1553" xr:uid="{CF62FD4B-9175-4C0E-BABA-CC1D21A94601}"/>
+    <cellStyle name="20% - Accent4 7" xfId="302" xr:uid="{F63CE262-111D-43E5-BB53-C61D1E442F50}"/>
+    <cellStyle name="20% - Accent4 7 2" xfId="691" xr:uid="{84C6F38F-5DA5-40A4-A8DF-A21211495402}"/>
+    <cellStyle name="20% - Accent4 7 2 2" xfId="1332" xr:uid="{61D80AD2-F9CC-4ECB-8A30-33FDC825EE58}"/>
+    <cellStyle name="20% - Accent4 7 2 3" xfId="2049" xr:uid="{ADB698CB-0188-4E60-AFB9-6C9A35BD9977}"/>
+    <cellStyle name="20% - Accent4 7 3" xfId="832" xr:uid="{0A494592-3638-49AF-ABE1-49C1949F998D}"/>
+    <cellStyle name="20% - Accent4 7 3 2" xfId="2189" xr:uid="{2F6929C2-64B0-495D-AE2D-55758210823C}"/>
+    <cellStyle name="20% - Accent4 7 4" xfId="444" xr:uid="{1BCFF950-36FD-4F0D-8A4E-EEE965924E87}"/>
+    <cellStyle name="20% - Accent4 7 4 2" xfId="1809" xr:uid="{D8F9A651-0955-43BF-9623-E98E684D1CBF}"/>
+    <cellStyle name="20% - Accent4 7 5" xfId="1188" xr:uid="{B962847B-E9B5-43CC-8FEA-34E55FD849C0}"/>
+    <cellStyle name="20% - Accent4 7 6" xfId="1669" xr:uid="{603941AF-F926-4ACC-9E5E-8826BCC766EB}"/>
+    <cellStyle name="20% - Accent4 8" xfId="563" xr:uid="{A1BBD352-E007-4144-800B-842FBD4F3695}"/>
+    <cellStyle name="20% - Accent4 8 2" xfId="1202" xr:uid="{EA86837A-FAAE-4E1D-B2BA-B5CA533CCCDC}"/>
+    <cellStyle name="20% - Accent4 8 3" xfId="1921" xr:uid="{35E733C7-C1D4-4C0E-8384-2863CDB0619B}"/>
+    <cellStyle name="20% - Accent4 9" xfId="703" xr:uid="{4DD3ACE0-8252-400D-9068-2B012586121C}"/>
+    <cellStyle name="20% - Accent4 9 2" xfId="1346" xr:uid="{C8577821-3711-4448-8586-262B4C8BEEAC}"/>
+    <cellStyle name="20% - Accent4 9 3" xfId="2061" xr:uid="{19263B50-C5E5-4CDF-912E-A8945FB9932A}"/>
+    <cellStyle name="20% - Accent5" xfId="29" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5 10" xfId="316" xr:uid="{3CEB1092-494E-421F-A1E6-327582825D2B}"/>
+    <cellStyle name="20% - Accent5 10 2" xfId="1362" xr:uid="{23E070C5-8D96-420F-A047-20A050C791CB}"/>
+    <cellStyle name="20% - Accent5 10 3" xfId="1683" xr:uid="{1E9AFF8E-11E6-460C-AE51-16CF6FCD6A1B}"/>
+    <cellStyle name="20% - Accent5 11" xfId="116" xr:uid="{B0412F6D-D9D0-4C06-81D2-981021FE2DA7}"/>
+    <cellStyle name="20% - Accent5 11 2" xfId="1375" xr:uid="{F5AC1C44-60A1-4F70-ADA8-8622512B5309}"/>
+    <cellStyle name="20% - Accent5 11 3" xfId="1485" xr:uid="{09B842B5-0061-4E0A-9DED-4CD087EB5541}"/>
+    <cellStyle name="20% - Accent5 12" xfId="949" xr:uid="{10313C18-C97E-4B9B-A579-B8EFD2E1ADEB}"/>
+    <cellStyle name="20% - Accent5 12 2" xfId="1388" xr:uid="{E7BBECDA-FE07-4CBB-BA63-D40A20FC2E3D}"/>
+    <cellStyle name="20% - Accent5 12 3" xfId="2305" xr:uid="{DA40126F-6251-4A22-BEA6-2E4F2DFAC9FC}"/>
+    <cellStyle name="20% - Accent5 13" xfId="963" xr:uid="{9588D847-408C-47D4-B0E0-D75EF973B771}"/>
+    <cellStyle name="20% - Accent5 13 2" xfId="1402" xr:uid="{339B3B16-EFD0-4EA2-A7A4-B92A8B3B91FD}"/>
+    <cellStyle name="20% - Accent5 13 3" xfId="2319" xr:uid="{D13FE0C6-872F-4A8D-A9CB-7809CFD1512A}"/>
+    <cellStyle name="20% - Accent5 14" xfId="977" xr:uid="{0CAF3F6D-799E-4C16-8DF7-30C3F52AE775}"/>
+    <cellStyle name="20% - Accent5 14 2" xfId="2333" xr:uid="{DB6B81F7-1530-4ED5-87BA-446E1E9E2794}"/>
+    <cellStyle name="20% - Accent5 15" xfId="993" xr:uid="{0336A99D-7D68-4D85-8B89-C0E0CA23D989}"/>
+    <cellStyle name="20% - Accent5 16" xfId="1006" xr:uid="{3CED4702-D673-400D-81EE-2345A36DE6C3}"/>
+    <cellStyle name="20% - Accent5 17" xfId="1415" xr:uid="{13BA0404-7B51-4216-92B1-440578DECDD9}"/>
+    <cellStyle name="20% - Accent5 2" xfId="57" xr:uid="{55DCA433-FD3A-40F1-AD5F-C3C35DB8C1A9}"/>
+    <cellStyle name="20% - Accent5 2 2" xfId="262" xr:uid="{ECEAA6BC-71C2-45CB-BF7C-5E0916AFA606}"/>
+    <cellStyle name="20% - Accent5 2 2 2" xfId="525" xr:uid="{A0EE84E6-57C4-4B6E-9AD3-A3E3B8BCD11E}"/>
+    <cellStyle name="20% - Accent5 2 2 2 2" xfId="907" xr:uid="{5717F503-F667-4A82-A09A-A73C1F9B930D}"/>
+    <cellStyle name="20% - Accent5 2 2 2 2 2" xfId="2263" xr:uid="{306A20AC-C3EF-4190-A22A-56797E0BF970}"/>
+    <cellStyle name="20% - Accent5 2 2 2 3" xfId="1292" xr:uid="{13925F4A-00EE-4309-AE3B-69C08944F768}"/>
+    <cellStyle name="20% - Accent5 2 2 2 4" xfId="1883" xr:uid="{0BBFB84C-107B-4B68-9750-F3030870EB14}"/>
+    <cellStyle name="20% - Accent5 2 2 3" xfId="637" xr:uid="{B283C1C4-3EF7-4041-855D-C9C9775EB57F}"/>
+    <cellStyle name="20% - Accent5 2 2 3 2" xfId="1995" xr:uid="{37906184-6CA4-4938-B545-408B338BA0E7}"/>
+    <cellStyle name="20% - Accent5 2 2 4" xfId="779" xr:uid="{C0CBE828-97D3-419C-A45E-5882761CC7CE}"/>
+    <cellStyle name="20% - Accent5 2 2 4 2" xfId="2137" xr:uid="{74E6B36A-6D43-4D61-A79F-CF7CCE0AA69F}"/>
+    <cellStyle name="20% - Accent5 2 2 5" xfId="390" xr:uid="{228D4E99-A89C-4D50-9D2A-FFEC5A6DA18E}"/>
+    <cellStyle name="20% - Accent5 2 2 5 2" xfId="1757" xr:uid="{DE13A290-C4A9-4CEE-8EB1-C6CD13F8F7A5}"/>
+    <cellStyle name="20% - Accent5 2 2 6" xfId="1148" xr:uid="{3B2DAE30-B2EA-471E-915D-5DCB811844EC}"/>
+    <cellStyle name="20% - Accent5 2 2 7" xfId="1629" xr:uid="{B59EE6D2-CD55-47E2-855C-0F4156C5979D}"/>
+    <cellStyle name="20% - Accent5 2 3" xfId="202" xr:uid="{C7557F4E-6570-4E8F-9173-67C58260B57E}"/>
+    <cellStyle name="20% - Accent5 2 3 2" xfId="850" xr:uid="{55CFCFC8-E1FB-480A-91DA-46767286CF64}"/>
+    <cellStyle name="20% - Accent5 2 3 2 2" xfId="2207" xr:uid="{6D19A479-77DB-4A5D-896A-06F5D70ED1DF}"/>
+    <cellStyle name="20% - Accent5 2 3 3" xfId="462" xr:uid="{5EF446BF-9F74-4413-A43A-69C1A09C71A7}"/>
+    <cellStyle name="20% - Accent5 2 3 3 2" xfId="1827" xr:uid="{C9175D42-3B9F-4ECB-B09B-3409D7AFF0B5}"/>
+    <cellStyle name="20% - Accent5 2 3 4" xfId="1092" xr:uid="{4EEBCFE3-C012-467F-A176-B29A4D4F5D0F}"/>
+    <cellStyle name="20% - Accent5 2 3 5" xfId="1571" xr:uid="{3F51F238-7213-443E-A35B-0C53D058A86E}"/>
+    <cellStyle name="20% - Accent5 2 4" xfId="581" xr:uid="{485EF688-1C81-4E9B-A4AA-0092F6D7D2A1}"/>
+    <cellStyle name="20% - Accent5 2 4 2" xfId="1221" xr:uid="{994DEED2-AEC0-47B8-AA4B-0B350A6D2D43}"/>
+    <cellStyle name="20% - Accent5 2 4 3" xfId="1939" xr:uid="{C0CD536B-DB3B-4943-9C5A-DE9BAA1C37EA}"/>
+    <cellStyle name="20% - Accent5 2 5" xfId="721" xr:uid="{D1B58201-08B0-4AB3-9F35-A87D2DC99C2D}"/>
+    <cellStyle name="20% - Accent5 2 5 2" xfId="2079" xr:uid="{CDA37FAA-815A-483B-8D19-0EF3CCD7E359}"/>
+    <cellStyle name="20% - Accent5 2 6" xfId="332" xr:uid="{82D91B5F-15E8-4738-8905-F4D8B6E4C008}"/>
+    <cellStyle name="20% - Accent5 2 6 2" xfId="1699" xr:uid="{2F3C8916-3EE0-4D56-94C9-B0E6825176FB}"/>
+    <cellStyle name="20% - Accent5 2 7" xfId="132" xr:uid="{07F30C30-82C5-41D8-99BA-5E04176423F1}"/>
+    <cellStyle name="20% - Accent5 2 7 2" xfId="1501" xr:uid="{64C1D369-FCAC-48CF-BFAF-CD3E78673DE2}"/>
+    <cellStyle name="20% - Accent5 2 8" xfId="1022" xr:uid="{F3F2B3C1-D426-4EB5-9413-664E2BF82791}"/>
+    <cellStyle name="20% - Accent5 2 9" xfId="1431" xr:uid="{606B37D5-01E3-45FE-A84E-68839E47F617}"/>
+    <cellStyle name="20% - Accent5 3" xfId="75" xr:uid="{7F03C87D-37DC-48BC-9BD5-4E91DB579167}"/>
+    <cellStyle name="20% - Accent5 3 2" xfId="276" xr:uid="{266069C3-E412-4CEF-9670-E497130A97FD}"/>
+    <cellStyle name="20% - Accent5 3 2 2" xfId="539" xr:uid="{E21CA3B9-916F-4D38-ABB0-DC5EC352F70D}"/>
+    <cellStyle name="20% - Accent5 3 2 2 2" xfId="921" xr:uid="{01C744BB-8A65-4E90-BD20-220E460A06B9}"/>
+    <cellStyle name="20% - Accent5 3 2 2 2 2" xfId="2277" xr:uid="{4067F00C-13BE-43D7-90F2-6DCF5B6970CC}"/>
+    <cellStyle name="20% - Accent5 3 2 2 3" xfId="1306" xr:uid="{B472BFD4-B892-4142-BA33-F6E3102F56E9}"/>
+    <cellStyle name="20% - Accent5 3 2 2 4" xfId="1897" xr:uid="{A43C99EB-CE02-445B-A9C1-B238C51C4AE8}"/>
+    <cellStyle name="20% - Accent5 3 2 3" xfId="651" xr:uid="{D60BFA34-4571-4155-85CC-7C18B3875755}"/>
+    <cellStyle name="20% - Accent5 3 2 3 2" xfId="2009" xr:uid="{8766310B-2F0E-483A-90FB-C8AA2AA25C04}"/>
+    <cellStyle name="20% - Accent5 3 2 4" xfId="793" xr:uid="{2A022AAD-1B62-4E70-9489-865C5C7A19E0}"/>
+    <cellStyle name="20% - Accent5 3 2 4 2" xfId="2151" xr:uid="{D3831438-C355-476E-A773-3C7608E95F36}"/>
+    <cellStyle name="20% - Accent5 3 2 5" xfId="404" xr:uid="{F6DB7079-773E-40FE-9259-6346DAF42B34}"/>
+    <cellStyle name="20% - Accent5 3 2 5 2" xfId="1771" xr:uid="{280D9F54-4440-462C-AE55-A924983BE598}"/>
+    <cellStyle name="20% - Accent5 3 2 6" xfId="1162" xr:uid="{D0210F32-7EBB-45A4-9016-AF896A50B174}"/>
+    <cellStyle name="20% - Accent5 3 2 7" xfId="1643" xr:uid="{AAF14D25-3AA7-4F4E-9700-5B9D7E18CCFD}"/>
+    <cellStyle name="20% - Accent5 3 3" xfId="216" xr:uid="{7527E481-6E95-46B6-9F47-36C85386D114}"/>
+    <cellStyle name="20% - Accent5 3 3 2" xfId="864" xr:uid="{523A6EB3-DBC3-46F7-8154-C223F1E351F3}"/>
+    <cellStyle name="20% - Accent5 3 3 2 2" xfId="2221" xr:uid="{5FBC88C4-BDF8-4501-8452-A50519EEF887}"/>
+    <cellStyle name="20% - Accent5 3 3 3" xfId="476" xr:uid="{2A8055FA-D5F4-4128-BDE9-FD4B1136FA3E}"/>
+    <cellStyle name="20% - Accent5 3 3 3 2" xfId="1841" xr:uid="{5E464171-976E-4180-A783-4688AE7950BC}"/>
+    <cellStyle name="20% - Accent5 3 3 4" xfId="1106" xr:uid="{6EBF4560-10A1-4A0D-95AF-5AD8DAEFE3CE}"/>
+    <cellStyle name="20% - Accent5 3 3 5" xfId="1585" xr:uid="{EB73EFB6-ADAA-471B-8BB5-D5870C825F4B}"/>
+    <cellStyle name="20% - Accent5 3 4" xfId="595" xr:uid="{B70BCE70-89C9-4C1B-A103-F2A148BBD4DA}"/>
+    <cellStyle name="20% - Accent5 3 4 2" xfId="1235" xr:uid="{3DA43A50-8FB8-41E3-AB10-E55AC63E22E2}"/>
+    <cellStyle name="20% - Accent5 3 4 3" xfId="1953" xr:uid="{D5258615-4AF8-4130-BD7F-F4F5317F8B8E}"/>
+    <cellStyle name="20% - Accent5 3 5" xfId="735" xr:uid="{71003F44-98F5-4B07-A924-96C1C7DFC0BC}"/>
+    <cellStyle name="20% - Accent5 3 5 2" xfId="2093" xr:uid="{7A38E90A-B071-466A-912A-206915DC1D0B}"/>
+    <cellStyle name="20% - Accent5 3 6" xfId="346" xr:uid="{B5AF7831-F224-4705-B829-F74252832621}"/>
+    <cellStyle name="20% - Accent5 3 6 2" xfId="1713" xr:uid="{A473B0E9-1FB8-49B7-90E2-2D8614F2423C}"/>
+    <cellStyle name="20% - Accent5 3 7" xfId="146" xr:uid="{A15BF2E9-6A78-4027-AEF1-0833B99208FA}"/>
+    <cellStyle name="20% - Accent5 3 7 2" xfId="1515" xr:uid="{36DEC8AF-154F-4201-BF3C-665E8CE7A339}"/>
+    <cellStyle name="20% - Accent5 3 8" xfId="1036" xr:uid="{AA671E2E-3032-4612-A2C5-0DD384A2FCBA}"/>
+    <cellStyle name="20% - Accent5 3 9" xfId="1445" xr:uid="{00B82E35-BB61-481D-A04D-BCE8B2F60BCB}"/>
+    <cellStyle name="20% - Accent5 4" xfId="89" xr:uid="{08C39389-C14B-4A12-8013-FA696F430CDF}"/>
+    <cellStyle name="20% - Accent5 4 2" xfId="289" xr:uid="{6351F2AB-1D7B-4D7D-8C2F-BFDABA4EE28E}"/>
+    <cellStyle name="20% - Accent5 4 2 2" xfId="553" xr:uid="{9B007076-4538-491A-B990-62F2F954A2C2}"/>
+    <cellStyle name="20% - Accent5 4 2 2 2" xfId="935" xr:uid="{682A9F49-F0ED-47CD-902D-E9168F5246B8}"/>
+    <cellStyle name="20% - Accent5 4 2 2 2 2" xfId="2291" xr:uid="{3FC1D300-0A38-4090-B160-8BA7E28CAB21}"/>
+    <cellStyle name="20% - Accent5 4 2 2 3" xfId="1320" xr:uid="{A2A7B40F-F310-4846-BB8C-DFF651605970}"/>
+    <cellStyle name="20% - Accent5 4 2 2 4" xfId="1911" xr:uid="{24530A04-2DDB-4F94-A579-4BF20AD27C10}"/>
+    <cellStyle name="20% - Accent5 4 2 3" xfId="665" xr:uid="{5352A057-CF62-4754-98E4-0B500A76CBD7}"/>
+    <cellStyle name="20% - Accent5 4 2 3 2" xfId="2023" xr:uid="{A0F8353C-82B1-42B5-AD01-C70AD475280F}"/>
+    <cellStyle name="20% - Accent5 4 2 4" xfId="806" xr:uid="{BE5F29F9-DAAF-4DA9-99A5-529269061447}"/>
+    <cellStyle name="20% - Accent5 4 2 4 2" xfId="2164" xr:uid="{715C276C-9B19-459B-8DF2-AB3A6654F086}"/>
+    <cellStyle name="20% - Accent5 4 2 5" xfId="417" xr:uid="{242FADCD-89EB-4F6B-9842-86C7F991AE21}"/>
+    <cellStyle name="20% - Accent5 4 2 5 2" xfId="1784" xr:uid="{0BFCC829-38B0-4466-80C2-07F09ABD010C}"/>
+    <cellStyle name="20% - Accent5 4 2 6" xfId="1176" xr:uid="{7FF18CE5-CEC0-44E7-9C1D-5C93BA91B416}"/>
+    <cellStyle name="20% - Accent5 4 2 7" xfId="1656" xr:uid="{1F9720BC-9AE6-41D9-8EAE-F1D54161EDA3}"/>
+    <cellStyle name="20% - Accent5 4 3" xfId="230" xr:uid="{573C3C86-6710-45AE-AA87-3D40904FF78B}"/>
+    <cellStyle name="20% - Accent5 4 3 2" xfId="878" xr:uid="{204F4A99-B00B-43DF-BEC7-75C7BB827742}"/>
+    <cellStyle name="20% - Accent5 4 3 2 2" xfId="2235" xr:uid="{B5A4B9B2-8034-43EF-B46A-B091B5A90ABA}"/>
+    <cellStyle name="20% - Accent5 4 3 3" xfId="490" xr:uid="{A6A2D8A6-7BA6-4F08-A810-54CD4B4381C4}"/>
+    <cellStyle name="20% - Accent5 4 3 3 2" xfId="1855" xr:uid="{9986CB0C-7143-401A-B7E0-41108C4F3EE8}"/>
+    <cellStyle name="20% - Accent5 4 3 4" xfId="1120" xr:uid="{84E17FC4-F903-4534-84CC-37D6251918C0}"/>
+    <cellStyle name="20% - Accent5 4 3 5" xfId="1599" xr:uid="{94C51D74-894E-4E91-BC14-65605085EBDF}"/>
+    <cellStyle name="20% - Accent5 4 4" xfId="609" xr:uid="{890684B8-ACD6-4611-BCC1-48744CFC7A08}"/>
+    <cellStyle name="20% - Accent5 4 4 2" xfId="1249" xr:uid="{FBF66F78-F33D-4923-8209-4C694D847840}"/>
+    <cellStyle name="20% - Accent5 4 4 3" xfId="1967" xr:uid="{CA9A71D3-36F5-4C01-BA62-BBB7BC675228}"/>
+    <cellStyle name="20% - Accent5 4 5" xfId="749" xr:uid="{4A41252B-7BE0-4420-9CF4-675C75EDBFBA}"/>
+    <cellStyle name="20% - Accent5 4 5 2" xfId="2107" xr:uid="{56BB7E5C-7356-4E0B-99F6-690CF17C434A}"/>
+    <cellStyle name="20% - Accent5 4 6" xfId="360" xr:uid="{D1E13033-0D2A-430F-9638-F40929F89F38}"/>
+    <cellStyle name="20% - Accent5 4 6 2" xfId="1727" xr:uid="{B384DB07-CE10-4CA1-A648-364DB33533A2}"/>
+    <cellStyle name="20% - Accent5 4 7" xfId="160" xr:uid="{B87D6D62-C9DA-4DFB-B9F3-064862C54491}"/>
+    <cellStyle name="20% - Accent5 4 7 2" xfId="1529" xr:uid="{96D32E7A-EEFF-45D1-955A-C831C95DC708}"/>
+    <cellStyle name="20% - Accent5 4 8" xfId="1050" xr:uid="{440C0197-D62C-40D2-98DA-413E9F9AEBAB}"/>
+    <cellStyle name="20% - Accent5 4 9" xfId="1459" xr:uid="{399CD5E7-7F87-486A-B4D0-D84C54F3804C}"/>
+    <cellStyle name="20% - Accent5 5" xfId="103" xr:uid="{A6E558AA-5C1B-4692-94EF-421C428FE5FD}"/>
+    <cellStyle name="20% - Accent5 5 2" xfId="246" xr:uid="{1F597F50-EDA2-4548-8A18-AD0A01089737}"/>
+    <cellStyle name="20% - Accent5 5 2 2" xfId="891" xr:uid="{6F52E82C-C05D-4F3A-82C1-AE09BEDAED01}"/>
+    <cellStyle name="20% - Accent5 5 2 2 2" xfId="2247" xr:uid="{1D5BAF19-E16B-484B-B946-B54D77BE32F4}"/>
+    <cellStyle name="20% - Accent5 5 2 3" xfId="506" xr:uid="{AD330BD1-E704-402B-BF15-A93820440FE3}"/>
+    <cellStyle name="20% - Accent5 5 2 3 2" xfId="1867" xr:uid="{2AAAF35B-798A-4098-B7B1-4D55F93E4DA9}"/>
+    <cellStyle name="20% - Accent5 5 2 4" xfId="1132" xr:uid="{23FD65A5-8C32-4F0B-B94A-FEC1C6EC4D97}"/>
+    <cellStyle name="20% - Accent5 5 2 5" xfId="1613" xr:uid="{B835938B-808A-41A8-928F-E5CE13EB24C0}"/>
+    <cellStyle name="20% - Accent5 5 3" xfId="679" xr:uid="{932EE961-9FA4-402D-9B38-9B15BD048A66}"/>
+    <cellStyle name="20% - Accent5 5 3 2" xfId="1263" xr:uid="{88C672C5-F228-4893-9470-2EF65D7CE66D}"/>
+    <cellStyle name="20% - Accent5 5 3 3" xfId="2037" xr:uid="{0F109835-6792-4BE7-AAAE-75266A57359E}"/>
+    <cellStyle name="20% - Accent5 5 4" xfId="763" xr:uid="{732922E3-91FA-4A0F-88D0-D6DE333AA335}"/>
+    <cellStyle name="20% - Accent5 5 4 2" xfId="2121" xr:uid="{0AAB8608-7103-4805-8226-CF45810324B4}"/>
+    <cellStyle name="20% - Accent5 5 5" xfId="374" xr:uid="{46BD6424-0BBF-440C-B18E-BFD2A2444D0E}"/>
+    <cellStyle name="20% - Accent5 5 5 2" xfId="1741" xr:uid="{FE24FBB2-0AE7-41D4-ACCD-ED0AC2BEBAD5}"/>
+    <cellStyle name="20% - Accent5 5 6" xfId="174" xr:uid="{9FCEBE68-D387-498A-B3C7-E6840514FF4E}"/>
+    <cellStyle name="20% - Accent5 5 6 2" xfId="1543" xr:uid="{FDD07C38-7449-4C13-9BFD-5335444D0941}"/>
+    <cellStyle name="20% - Accent5 5 7" xfId="1064" xr:uid="{BD8824E5-0C3E-4A23-8C39-35FD3D881BFC}"/>
+    <cellStyle name="20% - Accent5 5 8" xfId="1473" xr:uid="{9FE58AB5-EB87-4243-A78C-EC4F3B794A08}"/>
+    <cellStyle name="20% - Accent5 6" xfId="186" xr:uid="{3AC486AE-8B86-443B-966C-6B6133744332}"/>
+    <cellStyle name="20% - Accent5 6 2" xfId="621" xr:uid="{424FDC9F-6C74-4F26-9253-DD5993AB7336}"/>
+    <cellStyle name="20% - Accent5 6 2 2" xfId="1276" xr:uid="{52F80351-A34A-42D3-BF19-CC9BC43AD143}"/>
+    <cellStyle name="20% - Accent5 6 2 3" xfId="1979" xr:uid="{DB2F367E-6F67-4B5E-9D34-BCA6D3F2C5FF}"/>
+    <cellStyle name="20% - Accent5 6 3" xfId="821" xr:uid="{91730223-EF2B-4E86-91D4-6DD5B1B1EE06}"/>
+    <cellStyle name="20% - Accent5 6 3 2" xfId="2179" xr:uid="{B92A2618-611A-4FDB-A6BE-A11FFF325461}"/>
+    <cellStyle name="20% - Accent5 6 4" xfId="432" xr:uid="{596C3C2B-EA04-4928-981F-A9E841941EC9}"/>
+    <cellStyle name="20% - Accent5 6 4 2" xfId="1799" xr:uid="{B8CAC144-D18D-4D4E-A9D2-24AA575EAA57}"/>
+    <cellStyle name="20% - Accent5 6 5" xfId="1076" xr:uid="{6B0072B7-1063-4468-8708-BABB43784D68}"/>
+    <cellStyle name="20% - Accent5 6 6" xfId="1555" xr:uid="{42495D39-39AA-4C67-A635-70F4D676E558}"/>
+    <cellStyle name="20% - Accent5 7" xfId="304" xr:uid="{61CF11B1-C03E-454B-B375-562577649896}"/>
+    <cellStyle name="20% - Accent5 7 2" xfId="693" xr:uid="{A63962A1-742F-4B3B-9D66-2EA9D05CC20C}"/>
+    <cellStyle name="20% - Accent5 7 2 2" xfId="1334" xr:uid="{53B0BB28-44F6-4851-A670-67A394C340A1}"/>
+    <cellStyle name="20% - Accent5 7 2 3" xfId="2051" xr:uid="{B990BE65-8529-40BA-9872-EC7B450A4BC6}"/>
+    <cellStyle name="20% - Accent5 7 3" xfId="834" xr:uid="{A4E8D23F-8F48-4C67-8327-7CDB64142B9E}"/>
+    <cellStyle name="20% - Accent5 7 3 2" xfId="2191" xr:uid="{D4289AC3-65B7-4C96-892F-983AB72A008C}"/>
+    <cellStyle name="20% - Accent5 7 4" xfId="446" xr:uid="{03E9A7E2-EFD4-4F32-9775-1C6EAEA12DB5}"/>
+    <cellStyle name="20% - Accent5 7 4 2" xfId="1811" xr:uid="{881B7097-D741-4AB4-9FD3-459F32E8BFD3}"/>
+    <cellStyle name="20% - Accent5 7 5" xfId="1190" xr:uid="{111A09D8-4A2A-47BD-BE3E-D74750AC3025}"/>
+    <cellStyle name="20% - Accent5 7 6" xfId="1671" xr:uid="{91416FBC-B8F8-4B51-A8B2-F25FB1A0EA2E}"/>
+    <cellStyle name="20% - Accent5 8" xfId="565" xr:uid="{E113735D-6558-4657-B048-8D60F00C0796}"/>
+    <cellStyle name="20% - Accent5 8 2" xfId="1204" xr:uid="{932E6CB7-6192-44F7-89A6-F49B0E2FB0B8}"/>
+    <cellStyle name="20% - Accent5 8 3" xfId="1923" xr:uid="{1758A23A-7296-49B1-AE0A-C20613A2F9C9}"/>
+    <cellStyle name="20% - Accent5 9" xfId="705" xr:uid="{22A667C1-D5D5-45DC-9D7B-9244A0A0991B}"/>
+    <cellStyle name="20% - Accent5 9 2" xfId="1348" xr:uid="{59B02694-FC25-4D39-863B-049E4DD36583}"/>
+    <cellStyle name="20% - Accent5 9 3" xfId="2063" xr:uid="{B727F0C2-3E72-49B4-AE68-1B45670C180B}"/>
+    <cellStyle name="20% - Accent6" xfId="32" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6 10" xfId="318" xr:uid="{BB68B941-8EA0-4832-A72A-C4FE8CF1B0B2}"/>
+    <cellStyle name="20% - Accent6 10 2" xfId="1364" xr:uid="{E5862828-B448-4DCA-BA3D-554F60672083}"/>
+    <cellStyle name="20% - Accent6 10 3" xfId="1685" xr:uid="{41C29057-F44C-47C5-9571-B481BFA2BD3C}"/>
+    <cellStyle name="20% - Accent6 11" xfId="118" xr:uid="{04B95B97-501C-45E5-B8B9-5E531980C948}"/>
+    <cellStyle name="20% - Accent6 11 2" xfId="1377" xr:uid="{EB969E0C-89E8-416D-8582-0CB941B4B956}"/>
+    <cellStyle name="20% - Accent6 11 3" xfId="1487" xr:uid="{F50D7523-CBE4-441E-97F9-3DFB023B3575}"/>
+    <cellStyle name="20% - Accent6 12" xfId="951" xr:uid="{4B380A22-978F-41C3-A930-FA599C966C69}"/>
+    <cellStyle name="20% - Accent6 12 2" xfId="1390" xr:uid="{9B2B9713-BE18-42ED-94F6-E25FAF896A14}"/>
+    <cellStyle name="20% - Accent6 12 3" xfId="2307" xr:uid="{324870F4-CB9F-44EF-AA9C-A0F277F7B205}"/>
+    <cellStyle name="20% - Accent6 13" xfId="965" xr:uid="{69C974B0-DEB8-4351-ABCE-9B170D5A729A}"/>
+    <cellStyle name="20% - Accent6 13 2" xfId="1404" xr:uid="{4EF9AF83-E5B8-4ECA-8E80-A591B5AB2AA5}"/>
+    <cellStyle name="20% - Accent6 13 3" xfId="2321" xr:uid="{66A7E51C-888D-4B8B-AD22-B2273C0205C7}"/>
+    <cellStyle name="20% - Accent6 14" xfId="979" xr:uid="{2700B363-A543-40F3-8EA6-42FD347A344A}"/>
+    <cellStyle name="20% - Accent6 14 2" xfId="2335" xr:uid="{15043E23-9F8B-4338-9628-15A128F22FD9}"/>
+    <cellStyle name="20% - Accent6 15" xfId="995" xr:uid="{0202C1B6-943D-4E7C-AD14-D07712E7D0FF}"/>
+    <cellStyle name="20% - Accent6 16" xfId="1008" xr:uid="{81904832-625D-44C0-8AFB-3DCC8D6FF56E}"/>
+    <cellStyle name="20% - Accent6 17" xfId="1417" xr:uid="{46B9874A-994D-4D54-AAF1-59E35CFDEC4E}"/>
+    <cellStyle name="20% - Accent6 2" xfId="59" xr:uid="{14481D08-85F6-42C9-84B4-0F14B19227E2}"/>
+    <cellStyle name="20% - Accent6 2 2" xfId="264" xr:uid="{02F6E368-2619-4C31-8723-6CACD73B4020}"/>
+    <cellStyle name="20% - Accent6 2 2 2" xfId="527" xr:uid="{19477131-71D1-44EC-848F-DC32D8B2948C}"/>
+    <cellStyle name="20% - Accent6 2 2 2 2" xfId="909" xr:uid="{97496E4D-9668-44B8-A4E7-6021DB5303B1}"/>
+    <cellStyle name="20% - Accent6 2 2 2 2 2" xfId="2265" xr:uid="{C1E21109-1A44-4D65-921F-AC065898A420}"/>
+    <cellStyle name="20% - Accent6 2 2 2 3" xfId="1294" xr:uid="{42BD22BC-F686-4D18-960E-9EC9D4F75DB5}"/>
+    <cellStyle name="20% - Accent6 2 2 2 4" xfId="1885" xr:uid="{74926E1C-EC3C-4E3E-A5A8-D847BDA6C903}"/>
+    <cellStyle name="20% - Accent6 2 2 3" xfId="639" xr:uid="{30F08734-5F92-43B6-8E22-79B2A9263706}"/>
+    <cellStyle name="20% - Accent6 2 2 3 2" xfId="1997" xr:uid="{B87F2BEE-F1CF-451B-9590-0801DA46E499}"/>
+    <cellStyle name="20% - Accent6 2 2 4" xfId="781" xr:uid="{63377FB9-4E69-4887-B24B-7E29068B4B83}"/>
+    <cellStyle name="20% - Accent6 2 2 4 2" xfId="2139" xr:uid="{4E382572-A155-4431-90B4-2061E9637FD6}"/>
+    <cellStyle name="20% - Accent6 2 2 5" xfId="392" xr:uid="{7D510503-74DF-415B-AB65-428FA0425DD8}"/>
+    <cellStyle name="20% - Accent6 2 2 5 2" xfId="1759" xr:uid="{ABF5A9FB-9525-49F6-808B-8C3143068377}"/>
+    <cellStyle name="20% - Accent6 2 2 6" xfId="1150" xr:uid="{E3E9696F-0768-4092-9BDE-97169C6696F6}"/>
+    <cellStyle name="20% - Accent6 2 2 7" xfId="1631" xr:uid="{8ACB292B-0327-4F17-B338-E965D29C102F}"/>
+    <cellStyle name="20% - Accent6 2 3" xfId="204" xr:uid="{7FBE0BAD-E46D-423D-92B6-037110B589DA}"/>
+    <cellStyle name="20% - Accent6 2 3 2" xfId="852" xr:uid="{196ADE1A-5620-4357-A112-519D537B2F0B}"/>
+    <cellStyle name="20% - Accent6 2 3 2 2" xfId="2209" xr:uid="{F15D66D5-C185-4D15-B11F-767C88427452}"/>
+    <cellStyle name="20% - Accent6 2 3 3" xfId="464" xr:uid="{5D0880A2-ADA2-4FF4-AAA7-777EB93A7BC1}"/>
+    <cellStyle name="20% - Accent6 2 3 3 2" xfId="1829" xr:uid="{91BD2560-2AE3-4D8B-94C6-C92D613C3FDF}"/>
+    <cellStyle name="20% - Accent6 2 3 4" xfId="1094" xr:uid="{B58E1B56-5BCB-43E9-9FFA-E021FD8237E0}"/>
+    <cellStyle name="20% - Accent6 2 3 5" xfId="1573" xr:uid="{47C7FC5A-B1B8-4A9A-A672-4C689E9CD671}"/>
+    <cellStyle name="20% - Accent6 2 4" xfId="583" xr:uid="{D3DE9132-4445-48D5-B638-C17886CD0EFF}"/>
+    <cellStyle name="20% - Accent6 2 4 2" xfId="1223" xr:uid="{05650DFF-0E36-4127-89A4-E731ABE2DB12}"/>
+    <cellStyle name="20% - Accent6 2 4 3" xfId="1941" xr:uid="{54501863-E9B1-4FB2-8592-38079A28248F}"/>
+    <cellStyle name="20% - Accent6 2 5" xfId="723" xr:uid="{E67388A2-F348-4B7B-9C90-BB9EB5050E1C}"/>
+    <cellStyle name="20% - Accent6 2 5 2" xfId="2081" xr:uid="{6AF6BA25-FCF3-49D1-A407-2B3E99B086D6}"/>
+    <cellStyle name="20% - Accent6 2 6" xfId="334" xr:uid="{134FBACC-8A5D-41AB-A679-3A7226F350A4}"/>
+    <cellStyle name="20% - Accent6 2 6 2" xfId="1701" xr:uid="{8BD476BB-9F1B-4D25-993C-5B5A8CED7A19}"/>
+    <cellStyle name="20% - Accent6 2 7" xfId="134" xr:uid="{D971207D-5704-4D4D-B5E9-820A2603797F}"/>
+    <cellStyle name="20% - Accent6 2 7 2" xfId="1503" xr:uid="{C1DD376B-86AE-452B-9C96-74E0EBF84104}"/>
+    <cellStyle name="20% - Accent6 2 8" xfId="1024" xr:uid="{94BD9855-8743-48A6-825E-5AA32320EB8A}"/>
+    <cellStyle name="20% - Accent6 2 9" xfId="1433" xr:uid="{7368426A-95FA-4B4B-B529-332AC27C79CF}"/>
+    <cellStyle name="20% - Accent6 3" xfId="77" xr:uid="{3556D69F-E1AC-4CA6-B705-2F64B83CEBBD}"/>
+    <cellStyle name="20% - Accent6 3 2" xfId="278" xr:uid="{E9B458C4-BE80-4981-9AB2-8D8839EE8708}"/>
+    <cellStyle name="20% - Accent6 3 2 2" xfId="541" xr:uid="{FB65787A-528F-41B9-9793-B36FB3A041B7}"/>
+    <cellStyle name="20% - Accent6 3 2 2 2" xfId="923" xr:uid="{7E974267-5782-4010-9D17-FE7FE816C4D7}"/>
+    <cellStyle name="20% - Accent6 3 2 2 2 2" xfId="2279" xr:uid="{EB42B4E1-BAE2-4C8F-9B40-940D78E7CF11}"/>
+    <cellStyle name="20% - Accent6 3 2 2 3" xfId="1308" xr:uid="{01F19CB5-C642-4944-BE07-65506F944C3C}"/>
+    <cellStyle name="20% - Accent6 3 2 2 4" xfId="1899" xr:uid="{CE4C3A91-D284-4E14-972D-34A7839B8184}"/>
+    <cellStyle name="20% - Accent6 3 2 3" xfId="653" xr:uid="{47F92041-5C66-44A5-81CB-0CDB33BF22E6}"/>
+    <cellStyle name="20% - Accent6 3 2 3 2" xfId="2011" xr:uid="{5F4524F3-5A8E-4939-BE18-A2AD85BFB8EF}"/>
+    <cellStyle name="20% - Accent6 3 2 4" xfId="795" xr:uid="{6C124AB5-FC1F-4B90-82F6-BAB0FE58F620}"/>
+    <cellStyle name="20% - Accent6 3 2 4 2" xfId="2153" xr:uid="{6F5625DB-FF0C-4E22-AA30-C2CE15766E80}"/>
+    <cellStyle name="20% - Accent6 3 2 5" xfId="406" xr:uid="{9B44D68C-760A-433A-997B-BF1CAF4AEA9A}"/>
+    <cellStyle name="20% - Accent6 3 2 5 2" xfId="1773" xr:uid="{43736E34-5ED6-4BD4-8722-438D3D2A8BE0}"/>
+    <cellStyle name="20% - Accent6 3 2 6" xfId="1164" xr:uid="{BE7F0ECB-DC03-4566-8B5F-CA5A7594D0C8}"/>
+    <cellStyle name="20% - Accent6 3 2 7" xfId="1645" xr:uid="{DE2CE86C-BE15-48F1-85EB-933BCD6CFCB4}"/>
+    <cellStyle name="20% - Accent6 3 3" xfId="218" xr:uid="{B202565D-6AAD-4CD5-9952-1185D58BEE1B}"/>
+    <cellStyle name="20% - Accent6 3 3 2" xfId="866" xr:uid="{40BB83B8-DD6D-45C0-B030-D3FE3954CEF6}"/>
+    <cellStyle name="20% - Accent6 3 3 2 2" xfId="2223" xr:uid="{DBEF1CE0-2DFC-450C-BBE3-12155BD36791}"/>
+    <cellStyle name="20% - Accent6 3 3 3" xfId="478" xr:uid="{019716F7-2EB2-4A80-B49C-0F2A94B4F9CA}"/>
+    <cellStyle name="20% - Accent6 3 3 3 2" xfId="1843" xr:uid="{ABAEB656-9065-4E0E-8616-0B8F99E1345D}"/>
+    <cellStyle name="20% - Accent6 3 3 4" xfId="1108" xr:uid="{2C20BAC1-B994-496D-B2AD-5C19AE4860D8}"/>
+    <cellStyle name="20% - Accent6 3 3 5" xfId="1587" xr:uid="{B9682860-6290-448A-9939-3DC62B4B7EAF}"/>
+    <cellStyle name="20% - Accent6 3 4" xfId="597" xr:uid="{CA0AF8B1-7029-4358-9A18-7452F73836E8}"/>
+    <cellStyle name="20% - Accent6 3 4 2" xfId="1237" xr:uid="{3459B84F-252B-40AF-8AF9-5F1082ABB9FA}"/>
+    <cellStyle name="20% - Accent6 3 4 3" xfId="1955" xr:uid="{B6352F69-0C77-4970-8AE0-4BBC535FCBC9}"/>
+    <cellStyle name="20% - Accent6 3 5" xfId="737" xr:uid="{34D86024-6F1D-4417-98D1-027D88E3044F}"/>
+    <cellStyle name="20% - Accent6 3 5 2" xfId="2095" xr:uid="{1241FB0B-C9F9-49A8-B165-48F38395B50D}"/>
+    <cellStyle name="20% - Accent6 3 6" xfId="348" xr:uid="{3F3C1B49-B399-470A-BE26-4F0AC8CF03FC}"/>
+    <cellStyle name="20% - Accent6 3 6 2" xfId="1715" xr:uid="{B1C850FA-8436-4127-94EE-2CDE91DBAAA9}"/>
+    <cellStyle name="20% - Accent6 3 7" xfId="148" xr:uid="{8178AF9E-4E0A-48E6-BCB6-DE6F4E628342}"/>
+    <cellStyle name="20% - Accent6 3 7 2" xfId="1517" xr:uid="{4B06964B-1446-4FF9-85F3-F0157F2EC17C}"/>
+    <cellStyle name="20% - Accent6 3 8" xfId="1038" xr:uid="{607B808C-A15C-4ED6-B2CD-69071DD803F4}"/>
+    <cellStyle name="20% - Accent6 3 9" xfId="1447" xr:uid="{FA6C3A29-4EFB-49CA-A856-F00E7B2AD641}"/>
+    <cellStyle name="20% - Accent6 4" xfId="91" xr:uid="{937F77E6-F979-4442-974F-C81A34666593}"/>
+    <cellStyle name="20% - Accent6 4 2" xfId="291" xr:uid="{D09C6962-EC9B-485C-A5D8-0CAC54B6CB31}"/>
+    <cellStyle name="20% - Accent6 4 2 2" xfId="555" xr:uid="{B8F61E5B-0035-41E1-AF72-3CF82FBA2AC2}"/>
+    <cellStyle name="20% - Accent6 4 2 2 2" xfId="937" xr:uid="{FDB48EF4-5224-4DB9-A80F-7C5F7797D741}"/>
+    <cellStyle name="20% - Accent6 4 2 2 2 2" xfId="2293" xr:uid="{01CCA781-164E-42E7-8916-6A82B269C19A}"/>
+    <cellStyle name="20% - Accent6 4 2 2 3" xfId="1322" xr:uid="{E4CDF6E1-A7BB-4B71-B988-4B0829CA351B}"/>
+    <cellStyle name="20% - Accent6 4 2 2 4" xfId="1913" xr:uid="{15D54204-ABBE-4BAF-8A8B-D3E5A1C7DCB5}"/>
+    <cellStyle name="20% - Accent6 4 2 3" xfId="667" xr:uid="{0D764084-0E84-40BD-88F4-DD1EF1E6FB75}"/>
+    <cellStyle name="20% - Accent6 4 2 3 2" xfId="2025" xr:uid="{69347D48-5EDE-465F-914F-FBE991DC119A}"/>
+    <cellStyle name="20% - Accent6 4 2 4" xfId="808" xr:uid="{ED051BCD-85DF-4E02-B445-241F290548FD}"/>
+    <cellStyle name="20% - Accent6 4 2 4 2" xfId="2166" xr:uid="{F1E9D6C9-9900-4DAD-90CF-FEC812097CAD}"/>
+    <cellStyle name="20% - Accent6 4 2 5" xfId="419" xr:uid="{A1FD1D1D-75FB-4869-A966-62B82B22BFED}"/>
+    <cellStyle name="20% - Accent6 4 2 5 2" xfId="1786" xr:uid="{797CAE62-102B-4DEC-9C02-48902AEE883B}"/>
+    <cellStyle name="20% - Accent6 4 2 6" xfId="1178" xr:uid="{2D8323C9-1F2D-4B31-94F6-AD5384B5C725}"/>
+    <cellStyle name="20% - Accent6 4 2 7" xfId="1658" xr:uid="{73E456A8-E814-4449-9E0B-413E97127B70}"/>
+    <cellStyle name="20% - Accent6 4 3" xfId="232" xr:uid="{29054A37-BFA1-4703-8974-FDA3EB9379CA}"/>
+    <cellStyle name="20% - Accent6 4 3 2" xfId="880" xr:uid="{D7E2AE72-F8D2-4288-A5D3-969FBA41821B}"/>
+    <cellStyle name="20% - Accent6 4 3 2 2" xfId="2237" xr:uid="{9FF8B5B6-BC80-43F7-8E20-778559E9CD52}"/>
+    <cellStyle name="20% - Accent6 4 3 3" xfId="492" xr:uid="{25EC3E4D-9B42-4350-8DEE-F96AD16E4CB6}"/>
+    <cellStyle name="20% - Accent6 4 3 3 2" xfId="1857" xr:uid="{37D86B40-A35B-4598-9B12-87BF6DD01832}"/>
+    <cellStyle name="20% - Accent6 4 3 4" xfId="1122" xr:uid="{16CE3060-1331-4BB4-988D-8F19BAE459FA}"/>
+    <cellStyle name="20% - Accent6 4 3 5" xfId="1601" xr:uid="{87DAD360-1B68-436C-9340-336C0D899D20}"/>
+    <cellStyle name="20% - Accent6 4 4" xfId="611" xr:uid="{2370BA8B-DCAF-4F4B-A3E0-9F1A6B90C661}"/>
+    <cellStyle name="20% - Accent6 4 4 2" xfId="1251" xr:uid="{1DF9573F-9433-4E7B-9C34-53FDCBEFFE91}"/>
+    <cellStyle name="20% - Accent6 4 4 3" xfId="1969" xr:uid="{4D0DB129-112E-4A40-8418-ABA9CC72F75D}"/>
+    <cellStyle name="20% - Accent6 4 5" xfId="751" xr:uid="{7754AE20-4B31-401E-A134-81CD3512E241}"/>
+    <cellStyle name="20% - Accent6 4 5 2" xfId="2109" xr:uid="{B4C099CD-392A-4380-A320-3390A30ED5BD}"/>
+    <cellStyle name="20% - Accent6 4 6" xfId="362" xr:uid="{26571F0E-F324-497B-B0C0-35A6C8549F4F}"/>
+    <cellStyle name="20% - Accent6 4 6 2" xfId="1729" xr:uid="{C492CCF8-6994-4161-B352-EF32FDE646B7}"/>
+    <cellStyle name="20% - Accent6 4 7" xfId="162" xr:uid="{3FC0D130-E985-420E-A35D-F161C0372621}"/>
+    <cellStyle name="20% - Accent6 4 7 2" xfId="1531" xr:uid="{030D79DB-960C-49EA-9341-DECEC176E018}"/>
+    <cellStyle name="20% - Accent6 4 8" xfId="1052" xr:uid="{CC0506CD-89C2-4ED5-BEA9-44AF376C3847}"/>
+    <cellStyle name="20% - Accent6 4 9" xfId="1461" xr:uid="{57EF86ED-B5C3-47ED-B7F8-80A214B5053C}"/>
+    <cellStyle name="20% - Accent6 5" xfId="105" xr:uid="{9C5B1766-B0BB-40CA-A300-19FB2291F5BA}"/>
+    <cellStyle name="20% - Accent6 5 2" xfId="248" xr:uid="{366815DE-3E7A-4A54-BC12-B811A5E152E2}"/>
+    <cellStyle name="20% - Accent6 5 2 2" xfId="893" xr:uid="{F3F725A6-A70A-422D-B2AA-2BD239074D15}"/>
+    <cellStyle name="20% - Accent6 5 2 2 2" xfId="2249" xr:uid="{B3DDE6DD-7240-4E9B-8CE1-81A8443CE9AD}"/>
+    <cellStyle name="20% - Accent6 5 2 3" xfId="508" xr:uid="{2EE34CA1-B2C6-4F01-9BEF-E69A37D99929}"/>
+    <cellStyle name="20% - Accent6 5 2 3 2" xfId="1869" xr:uid="{A69D4C0D-BF58-422E-B701-55226A8329ED}"/>
+    <cellStyle name="20% - Accent6 5 2 4" xfId="1134" xr:uid="{5E10E336-E6F7-432A-A0C3-3AC8326A23CE}"/>
+    <cellStyle name="20% - Accent6 5 2 5" xfId="1615" xr:uid="{C50664ED-F1E0-4E5F-8F3D-F26FCAA451F5}"/>
+    <cellStyle name="20% - Accent6 5 3" xfId="681" xr:uid="{6346AA5A-2C1C-41E9-8891-337697DBDB72}"/>
+    <cellStyle name="20% - Accent6 5 3 2" xfId="1265" xr:uid="{02F2A667-B64D-406B-BED2-9C1650555AF5}"/>
+    <cellStyle name="20% - Accent6 5 3 3" xfId="2039" xr:uid="{5C2264FC-84D8-4C9E-BD60-83844AC0425A}"/>
+    <cellStyle name="20% - Accent6 5 4" xfId="765" xr:uid="{74241150-EA33-464D-93EC-7B7363B730D3}"/>
+    <cellStyle name="20% - Accent6 5 4 2" xfId="2123" xr:uid="{727B8C74-16B2-4CB3-AF63-566BD0BF1660}"/>
+    <cellStyle name="20% - Accent6 5 5" xfId="376" xr:uid="{6040B96E-35FA-4710-B0EB-00D9F427E43B}"/>
+    <cellStyle name="20% - Accent6 5 5 2" xfId="1743" xr:uid="{C752A57D-2F87-4923-B90B-EAC2EB6EB6B4}"/>
+    <cellStyle name="20% - Accent6 5 6" xfId="176" xr:uid="{CEE6C16E-2B99-4ED6-86E8-1F39ADBB582F}"/>
+    <cellStyle name="20% - Accent6 5 6 2" xfId="1545" xr:uid="{6B21856E-CC03-42B1-BB88-06074142BC35}"/>
+    <cellStyle name="20% - Accent6 5 7" xfId="1066" xr:uid="{21713DE8-6FEA-4454-9847-236F842BFD0F}"/>
+    <cellStyle name="20% - Accent6 5 8" xfId="1475" xr:uid="{7A2AD032-60A8-4254-BA0C-C636B717ACC4}"/>
+    <cellStyle name="20% - Accent6 6" xfId="188" xr:uid="{8B1CFB9D-D463-40E3-9E38-BCDEE100A75A}"/>
+    <cellStyle name="20% - Accent6 6 2" xfId="623" xr:uid="{D11C45F9-B9FD-4371-BEED-E78EC3C52798}"/>
+    <cellStyle name="20% - Accent6 6 2 2" xfId="1278" xr:uid="{60286D92-39A4-4715-AAF1-DE137DB4EF4F}"/>
+    <cellStyle name="20% - Accent6 6 2 3" xfId="1981" xr:uid="{F7CACB69-8019-4184-8493-5BD7ADE9F8D8}"/>
+    <cellStyle name="20% - Accent6 6 3" xfId="823" xr:uid="{D08F4237-8756-4E4E-8E4B-E3D51FCEBC73}"/>
+    <cellStyle name="20% - Accent6 6 3 2" xfId="2181" xr:uid="{28FB1C68-C5D0-47BB-B28F-0705DF09F9D0}"/>
+    <cellStyle name="20% - Accent6 6 4" xfId="434" xr:uid="{D07F72DA-6861-4BBC-AAA9-206070AE1AF0}"/>
+    <cellStyle name="20% - Accent6 6 4 2" xfId="1801" xr:uid="{5CECEFFB-3F2F-4510-93B2-5E153D8AB38E}"/>
+    <cellStyle name="20% - Accent6 6 5" xfId="1078" xr:uid="{2795188B-C62D-499E-A8B0-A5C13BC7AD4E}"/>
+    <cellStyle name="20% - Accent6 6 6" xfId="1557" xr:uid="{FB171A70-B826-4C19-9A43-ACED3E1A6BB7}"/>
+    <cellStyle name="20% - Accent6 7" xfId="306" xr:uid="{3A40B2DB-2A9A-46A6-8E59-24C58F738985}"/>
+    <cellStyle name="20% - Accent6 7 2" xfId="695" xr:uid="{55A95D2A-78A9-4342-BABE-62B73618321E}"/>
+    <cellStyle name="20% - Accent6 7 2 2" xfId="1336" xr:uid="{B2464552-7D32-4477-8554-4F934BC0D08B}"/>
+    <cellStyle name="20% - Accent6 7 2 3" xfId="2053" xr:uid="{EADB727C-8710-419B-91F8-87E90A719115}"/>
+    <cellStyle name="20% - Accent6 7 3" xfId="836" xr:uid="{C405C716-AF7D-4889-A1D2-D1E8F019F19C}"/>
+    <cellStyle name="20% - Accent6 7 3 2" xfId="2193" xr:uid="{769F6BB5-A37F-4A75-A3D8-A77288F7B793}"/>
+    <cellStyle name="20% - Accent6 7 4" xfId="448" xr:uid="{AB0C44AD-829A-461F-A146-88815F63B468}"/>
+    <cellStyle name="20% - Accent6 7 4 2" xfId="1813" xr:uid="{BE785FFB-194E-4B91-A0E1-B594AB2BF72A}"/>
+    <cellStyle name="20% - Accent6 7 5" xfId="1192" xr:uid="{8D25941D-306C-422D-B83C-F0F50F0DF201}"/>
+    <cellStyle name="20% - Accent6 7 6" xfId="1673" xr:uid="{15A55AFA-9528-4B2C-B37C-ACC02CF78A04}"/>
+    <cellStyle name="20% - Accent6 8" xfId="567" xr:uid="{17EE87C6-7563-41FD-AD6C-BA133F97C600}"/>
+    <cellStyle name="20% - Accent6 8 2" xfId="1206" xr:uid="{239510A0-9AA4-4861-8349-389A78DC8306}"/>
+    <cellStyle name="20% - Accent6 8 3" xfId="1925" xr:uid="{1A88651A-A5F0-4F9C-8072-2B8EBC73D0BD}"/>
+    <cellStyle name="20% - Accent6 9" xfId="707" xr:uid="{885B0791-5378-423E-BED2-D352A7BA90F0}"/>
+    <cellStyle name="20% - Accent6 9 2" xfId="1350" xr:uid="{6FC53737-E4C5-41EB-8DC8-284C399E9372}"/>
+    <cellStyle name="20% - Accent6 9 3" xfId="2065" xr:uid="{FE720B8B-5AC4-46F3-BC39-330C6698DAD7}"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1 10" xfId="309" xr:uid="{DFD51285-9085-4D9B-A79A-1133E62D0742}"/>
+    <cellStyle name="40% - Accent1 10 2" xfId="1355" xr:uid="{40B8595A-7524-40CA-8DAC-01D8431E5E8B}"/>
+    <cellStyle name="40% - Accent1 10 3" xfId="1676" xr:uid="{E9290C8D-8300-49C6-9AE5-AFFB9D6CFDF6}"/>
+    <cellStyle name="40% - Accent1 11" xfId="109" xr:uid="{44BD7A80-F23B-4424-8B55-A2C5DB8CBFA7}"/>
+    <cellStyle name="40% - Accent1 11 2" xfId="1368" xr:uid="{085C1764-6504-4995-A725-DA9D29551934}"/>
+    <cellStyle name="40% - Accent1 11 3" xfId="1478" xr:uid="{225D6A64-F169-4840-B6D8-E28DD4AA2B8D}"/>
+    <cellStyle name="40% - Accent1 12" xfId="942" xr:uid="{427362AE-3205-4249-B6BF-06318AE57DBA}"/>
+    <cellStyle name="40% - Accent1 12 2" xfId="1381" xr:uid="{2DA1B4D7-847D-403D-8295-31766E436BBC}"/>
+    <cellStyle name="40% - Accent1 12 3" xfId="2298" xr:uid="{E34A4EA3-D0C2-4B85-98CE-80EC9016AB11}"/>
+    <cellStyle name="40% - Accent1 13" xfId="956" xr:uid="{922E01DD-16B4-456F-BA79-8B9C0496F5CB}"/>
+    <cellStyle name="40% - Accent1 13 2" xfId="1395" xr:uid="{71EE2EDC-24DA-4497-B009-4DD8054AFC48}"/>
+    <cellStyle name="40% - Accent1 13 3" xfId="2312" xr:uid="{AA9C0141-6CE3-4044-8C59-8A0F08D0DDBC}"/>
+    <cellStyle name="40% - Accent1 14" xfId="970" xr:uid="{063789A4-E092-4A0E-A564-C015A93CBD31}"/>
+    <cellStyle name="40% - Accent1 14 2" xfId="2326" xr:uid="{7F9D58D7-8E34-42DD-82AA-6E1B01D9BD4B}"/>
+    <cellStyle name="40% - Accent1 15" xfId="986" xr:uid="{BDA4A41F-BCC0-4FD3-A228-7159A7839DA6}"/>
+    <cellStyle name="40% - Accent1 16" xfId="999" xr:uid="{EBAD645F-A6A5-457F-BB5B-E1185C9493F8}"/>
+    <cellStyle name="40% - Accent1 17" xfId="1408" xr:uid="{F8FAA827-7F80-4064-8E22-CCE4A9033B6C}"/>
+    <cellStyle name="40% - Accent1 2" xfId="50" xr:uid="{8CDF23A2-384C-4202-94A2-6BF7C2C7E7AA}"/>
+    <cellStyle name="40% - Accent1 2 2" xfId="255" xr:uid="{EA9B566C-A60C-4C4A-9DDF-B230E744538E}"/>
+    <cellStyle name="40% - Accent1 2 2 2" xfId="518" xr:uid="{C9D9A0B7-6142-48BF-85A4-35FEDEC12AF1}"/>
+    <cellStyle name="40% - Accent1 2 2 2 2" xfId="900" xr:uid="{B1E87C0E-6230-4703-BC78-A2A40336082D}"/>
+    <cellStyle name="40% - Accent1 2 2 2 2 2" xfId="2256" xr:uid="{1C118428-83E4-4A18-B7EA-6923D0CC10B5}"/>
+    <cellStyle name="40% - Accent1 2 2 2 3" xfId="1285" xr:uid="{44831C48-E6DA-4F40-8191-A614F5995A0B}"/>
+    <cellStyle name="40% - Accent1 2 2 2 4" xfId="1876" xr:uid="{AB307FF1-F65C-4C6F-B51F-BFFCDD09B22F}"/>
+    <cellStyle name="40% - Accent1 2 2 3" xfId="630" xr:uid="{F65000D3-2A7A-4AC3-9580-58AF7DC94EE7}"/>
+    <cellStyle name="40% - Accent1 2 2 3 2" xfId="1988" xr:uid="{DF18F369-9647-4B1A-86CF-D13612DDE619}"/>
+    <cellStyle name="40% - Accent1 2 2 4" xfId="772" xr:uid="{4DED210B-A0FF-44EC-94BB-D1E2C7BB8865}"/>
+    <cellStyle name="40% - Accent1 2 2 4 2" xfId="2130" xr:uid="{9B297FD0-5F1C-488B-826B-4DEA0AC2235E}"/>
+    <cellStyle name="40% - Accent1 2 2 5" xfId="383" xr:uid="{82E0431B-A6BE-4DBA-B858-05610F4E03B2}"/>
+    <cellStyle name="40% - Accent1 2 2 5 2" xfId="1750" xr:uid="{C21E4F99-7717-40FB-85FE-7CC87DEA678A}"/>
+    <cellStyle name="40% - Accent1 2 2 6" xfId="1141" xr:uid="{82E290C0-1073-48D8-B4BB-4EB36E7F4C27}"/>
+    <cellStyle name="40% - Accent1 2 2 7" xfId="1622" xr:uid="{31136E66-7C06-4F50-ABCB-039BE2E89607}"/>
+    <cellStyle name="40% - Accent1 2 3" xfId="195" xr:uid="{44AF248F-7CD8-4E5E-A780-ADCF2B678CDD}"/>
+    <cellStyle name="40% - Accent1 2 3 2" xfId="843" xr:uid="{46C8A0D0-8B62-450E-BB8B-7B6147E6AF2E}"/>
+    <cellStyle name="40% - Accent1 2 3 2 2" xfId="2200" xr:uid="{BB12BAFB-DB53-410C-9EC0-F58ACB022FD4}"/>
+    <cellStyle name="40% - Accent1 2 3 3" xfId="455" xr:uid="{89D402AC-0F99-4F1E-9D29-D826093342FC}"/>
+    <cellStyle name="40% - Accent1 2 3 3 2" xfId="1820" xr:uid="{A66F3438-472C-4DCC-B2F8-ED9D0555A56D}"/>
+    <cellStyle name="40% - Accent1 2 3 4" xfId="1085" xr:uid="{2B4FCFCC-4866-4DE2-9202-76314EBA5AA3}"/>
+    <cellStyle name="40% - Accent1 2 3 5" xfId="1564" xr:uid="{16FFBACB-00F5-41EC-9BB7-8999F3C32A40}"/>
+    <cellStyle name="40% - Accent1 2 4" xfId="574" xr:uid="{02ACF6EF-A35F-48C2-8E6B-556672729652}"/>
+    <cellStyle name="40% - Accent1 2 4 2" xfId="1214" xr:uid="{C0E0E5DD-3756-4246-B484-49054AE200CF}"/>
+    <cellStyle name="40% - Accent1 2 4 3" xfId="1932" xr:uid="{3183345B-A5FC-4572-A8D3-E84A135BEED8}"/>
+    <cellStyle name="40% - Accent1 2 5" xfId="714" xr:uid="{415B6442-C707-45E5-A215-0720C8882992}"/>
+    <cellStyle name="40% - Accent1 2 5 2" xfId="2072" xr:uid="{C23664D6-A80A-4089-AB2E-97CE39481553}"/>
+    <cellStyle name="40% - Accent1 2 6" xfId="325" xr:uid="{A8C53FA9-73D9-40D3-A87B-C3E031DC40F5}"/>
+    <cellStyle name="40% - Accent1 2 6 2" xfId="1692" xr:uid="{F0C30A32-690E-47F4-B548-2EBF044C2E45}"/>
+    <cellStyle name="40% - Accent1 2 7" xfId="125" xr:uid="{35CE149F-D405-4DB9-96CB-A08A9F1D07EF}"/>
+    <cellStyle name="40% - Accent1 2 7 2" xfId="1494" xr:uid="{8F97E353-8CF4-42FC-862B-53A9E5D0F938}"/>
+    <cellStyle name="40% - Accent1 2 8" xfId="1015" xr:uid="{8FA6CF1F-DE4B-4E3C-ABB2-A351183C58B2}"/>
+    <cellStyle name="40% - Accent1 2 9" xfId="1424" xr:uid="{8A17912A-E1ED-4C19-BE7B-5507F2F96F7A}"/>
+    <cellStyle name="40% - Accent1 3" xfId="68" xr:uid="{E10E8B4A-772D-41AE-A1D5-C26483675A25}"/>
+    <cellStyle name="40% - Accent1 3 2" xfId="269" xr:uid="{F394A033-6020-4D1D-A302-FC04F4177FE8}"/>
+    <cellStyle name="40% - Accent1 3 2 2" xfId="532" xr:uid="{E4116050-AD32-4741-B9C2-46E2FCC7027B}"/>
+    <cellStyle name="40% - Accent1 3 2 2 2" xfId="914" xr:uid="{EEEFA400-4C66-48A1-8CF3-85205FC31B96}"/>
+    <cellStyle name="40% - Accent1 3 2 2 2 2" xfId="2270" xr:uid="{2F591B87-8002-4EA1-9B47-3BCA3368C4C2}"/>
+    <cellStyle name="40% - Accent1 3 2 2 3" xfId="1299" xr:uid="{EE820B73-04DB-4DFA-9D59-C6C9882EDC13}"/>
+    <cellStyle name="40% - Accent1 3 2 2 4" xfId="1890" xr:uid="{401A8A82-0E76-4C8B-9D1A-B57973C52A98}"/>
+    <cellStyle name="40% - Accent1 3 2 3" xfId="644" xr:uid="{FEC25860-FD53-49DF-9EC1-E71159834023}"/>
+    <cellStyle name="40% - Accent1 3 2 3 2" xfId="2002" xr:uid="{4ED7587B-6EC9-4619-846A-45839C12D40A}"/>
+    <cellStyle name="40% - Accent1 3 2 4" xfId="786" xr:uid="{50A3F70C-F832-4EA7-A5B2-08E2099638C0}"/>
+    <cellStyle name="40% - Accent1 3 2 4 2" xfId="2144" xr:uid="{B9725E40-B41D-4F79-B0E0-9922ACA97B1B}"/>
+    <cellStyle name="40% - Accent1 3 2 5" xfId="397" xr:uid="{F3B9960B-167F-4157-8C5B-4FF43BD4F704}"/>
+    <cellStyle name="40% - Accent1 3 2 5 2" xfId="1764" xr:uid="{B96A0F9A-BD2E-4124-965B-6B353DCCF66D}"/>
+    <cellStyle name="40% - Accent1 3 2 6" xfId="1155" xr:uid="{5311D8AF-60B7-405E-9B79-E97D247D45C0}"/>
+    <cellStyle name="40% - Accent1 3 2 7" xfId="1636" xr:uid="{BA4381A4-012C-4C52-8162-3AE3C72BA654}"/>
+    <cellStyle name="40% - Accent1 3 3" xfId="209" xr:uid="{98803681-7AC5-4942-913C-A13AF25130C8}"/>
+    <cellStyle name="40% - Accent1 3 3 2" xfId="857" xr:uid="{B2FB6F94-E915-411F-86CF-1E9191B5BBEA}"/>
+    <cellStyle name="40% - Accent1 3 3 2 2" xfId="2214" xr:uid="{C77A505F-3935-498D-8A2D-97D6FFD92A7D}"/>
+    <cellStyle name="40% - Accent1 3 3 3" xfId="469" xr:uid="{230F9071-2256-4CA1-9D97-E57F2245D21E}"/>
+    <cellStyle name="40% - Accent1 3 3 3 2" xfId="1834" xr:uid="{16471163-66E1-4375-B906-146F84E74035}"/>
+    <cellStyle name="40% - Accent1 3 3 4" xfId="1099" xr:uid="{8493243D-3EA7-432B-82F4-52A3DA6627AF}"/>
+    <cellStyle name="40% - Accent1 3 3 5" xfId="1578" xr:uid="{3A92124F-68A5-41EE-81A7-2FC911288541}"/>
+    <cellStyle name="40% - Accent1 3 4" xfId="588" xr:uid="{4123E051-6515-4AED-AC30-4B30D367F549}"/>
+    <cellStyle name="40% - Accent1 3 4 2" xfId="1228" xr:uid="{495BE9C0-0AF5-45B9-8CC3-69C59665352B}"/>
+    <cellStyle name="40% - Accent1 3 4 3" xfId="1946" xr:uid="{A29ACBD8-E346-4187-A49D-C64D4E3FF421}"/>
+    <cellStyle name="40% - Accent1 3 5" xfId="728" xr:uid="{23F250EC-6F02-4E20-BBA8-70D712075D2E}"/>
+    <cellStyle name="40% - Accent1 3 5 2" xfId="2086" xr:uid="{712E5E20-05C7-4483-84B7-DC893000DD12}"/>
+    <cellStyle name="40% - Accent1 3 6" xfId="339" xr:uid="{4599E4D5-ADE8-4738-9E73-7273EF14730C}"/>
+    <cellStyle name="40% - Accent1 3 6 2" xfId="1706" xr:uid="{C91D85C0-D6D3-493F-B00E-431C126307BD}"/>
+    <cellStyle name="40% - Accent1 3 7" xfId="139" xr:uid="{81A83B13-77A0-4D06-B813-8C6D41C1D8ED}"/>
+    <cellStyle name="40% - Accent1 3 7 2" xfId="1508" xr:uid="{BC371F16-000F-479F-A353-9F5AF9FA0163}"/>
+    <cellStyle name="40% - Accent1 3 8" xfId="1029" xr:uid="{D7A1DE22-E864-4B98-87D4-64C637FABD04}"/>
+    <cellStyle name="40% - Accent1 3 9" xfId="1438" xr:uid="{0622AC0A-4FAB-45BE-80B4-C497AC405F7F}"/>
+    <cellStyle name="40% - Accent1 4" xfId="82" xr:uid="{C4DE7901-A0B8-46C6-A641-D75479FA165D}"/>
+    <cellStyle name="40% - Accent1 4 2" xfId="282" xr:uid="{7E69F56C-64CA-4ABD-8E89-028718F1116E}"/>
+    <cellStyle name="40% - Accent1 4 2 2" xfId="546" xr:uid="{141A5E78-72B4-4D5F-A81D-8F75725974FE}"/>
+    <cellStyle name="40% - Accent1 4 2 2 2" xfId="928" xr:uid="{34F592B2-B6F7-4763-A390-90D6B1A787A7}"/>
+    <cellStyle name="40% - Accent1 4 2 2 2 2" xfId="2284" xr:uid="{A386D331-71AF-49AA-AE24-AB1199F4B949}"/>
+    <cellStyle name="40% - Accent1 4 2 2 3" xfId="1313" xr:uid="{214FF9F9-AA14-4EF8-A886-B1203A2E5741}"/>
+    <cellStyle name="40% - Accent1 4 2 2 4" xfId="1904" xr:uid="{DADBDC09-6F5E-4CDA-94D8-ED1EC3BBF337}"/>
+    <cellStyle name="40% - Accent1 4 2 3" xfId="658" xr:uid="{BF01A8D7-C98B-415F-9B36-C9D725C920CC}"/>
+    <cellStyle name="40% - Accent1 4 2 3 2" xfId="2016" xr:uid="{2E56C041-AF75-4B32-93E1-CF4ECCC8499F}"/>
+    <cellStyle name="40% - Accent1 4 2 4" xfId="799" xr:uid="{D7364008-2C71-4509-979E-982D4A743162}"/>
+    <cellStyle name="40% - Accent1 4 2 4 2" xfId="2157" xr:uid="{EEA07837-9AF3-46FB-B88D-E20CCA7895B9}"/>
+    <cellStyle name="40% - Accent1 4 2 5" xfId="410" xr:uid="{D732475A-1A80-4124-A454-2647DD5A2F11}"/>
+    <cellStyle name="40% - Accent1 4 2 5 2" xfId="1777" xr:uid="{C96AD2D9-7798-48BE-9F68-5E9BA48D0757}"/>
+    <cellStyle name="40% - Accent1 4 2 6" xfId="1169" xr:uid="{33F117E4-6551-4FC4-9135-13A582565966}"/>
+    <cellStyle name="40% - Accent1 4 2 7" xfId="1649" xr:uid="{3106E9C8-4013-4B46-B339-34DD1F6B98C9}"/>
+    <cellStyle name="40% - Accent1 4 3" xfId="223" xr:uid="{F997268F-2E4C-485A-B51A-B87B583227C3}"/>
+    <cellStyle name="40% - Accent1 4 3 2" xfId="871" xr:uid="{8F5AA8C3-141E-400F-87A5-03B71370BEA7}"/>
+    <cellStyle name="40% - Accent1 4 3 2 2" xfId="2228" xr:uid="{92191AD1-0CA3-4325-987D-94FC693406FE}"/>
+    <cellStyle name="40% - Accent1 4 3 3" xfId="483" xr:uid="{A66E3FDC-6134-4A4B-BA49-102562C28CE5}"/>
+    <cellStyle name="40% - Accent1 4 3 3 2" xfId="1848" xr:uid="{EF346CEF-A4BC-4BA7-9BDD-8E5AB676EC4A}"/>
+    <cellStyle name="40% - Accent1 4 3 4" xfId="1113" xr:uid="{958F4459-2022-43FA-98B8-0A9802780606}"/>
+    <cellStyle name="40% - Accent1 4 3 5" xfId="1592" xr:uid="{B9669A51-D214-43A6-8C4A-C61F5B6EEEBD}"/>
+    <cellStyle name="40% - Accent1 4 4" xfId="602" xr:uid="{7122F856-0A22-45F7-BED1-2028916A819F}"/>
+    <cellStyle name="40% - Accent1 4 4 2" xfId="1242" xr:uid="{F49CE205-1CFE-4C69-8088-4B8C6C1C2E6A}"/>
+    <cellStyle name="40% - Accent1 4 4 3" xfId="1960" xr:uid="{D2481A09-B9B9-483D-BB0D-910DD83EDD4C}"/>
+    <cellStyle name="40% - Accent1 4 5" xfId="742" xr:uid="{07EB63AD-AD6D-40DD-BB5D-51ABFA1CF898}"/>
+    <cellStyle name="40% - Accent1 4 5 2" xfId="2100" xr:uid="{2674469C-6277-45B6-994D-6A71B4E4CE00}"/>
+    <cellStyle name="40% - Accent1 4 6" xfId="353" xr:uid="{98471BC4-D764-4175-8768-4A34BABE3BB6}"/>
+    <cellStyle name="40% - Accent1 4 6 2" xfId="1720" xr:uid="{14F600DF-9AFE-444D-9781-CE9DE0AEB012}"/>
+    <cellStyle name="40% - Accent1 4 7" xfId="153" xr:uid="{39FAA88A-2D9A-4988-B781-70F187D6F837}"/>
+    <cellStyle name="40% - Accent1 4 7 2" xfId="1522" xr:uid="{AD93B686-4328-420B-9057-D3F2B86097EE}"/>
+    <cellStyle name="40% - Accent1 4 8" xfId="1043" xr:uid="{157B959C-534E-4523-9230-6CA598BD0661}"/>
+    <cellStyle name="40% - Accent1 4 9" xfId="1452" xr:uid="{559F1A4F-E1DC-4888-B8E0-5C132BF88817}"/>
+    <cellStyle name="40% - Accent1 5" xfId="96" xr:uid="{34493E5C-E785-47B9-970D-B979098C32BB}"/>
+    <cellStyle name="40% - Accent1 5 2" xfId="239" xr:uid="{27CE19C7-5A27-4BFD-BC11-B24D0EB5E3A3}"/>
+    <cellStyle name="40% - Accent1 5 2 2" xfId="884" xr:uid="{130C16C4-AD75-4A4D-B17E-8FCD90554893}"/>
+    <cellStyle name="40% - Accent1 5 2 2 2" xfId="2240" xr:uid="{E8A3B7AA-B86D-4240-9E79-619343A04BE3}"/>
+    <cellStyle name="40% - Accent1 5 2 3" xfId="499" xr:uid="{F25BD6E0-A154-43A3-B291-DE3982E60C3B}"/>
+    <cellStyle name="40% - Accent1 5 2 3 2" xfId="1860" xr:uid="{66177337-B453-436C-B1DE-C550ADBF2659}"/>
+    <cellStyle name="40% - Accent1 5 2 4" xfId="1125" xr:uid="{7918892B-0724-48F3-832A-A68B10A086C6}"/>
+    <cellStyle name="40% - Accent1 5 2 5" xfId="1606" xr:uid="{3A7822B5-9244-47E6-A34F-753A424D6AA6}"/>
+    <cellStyle name="40% - Accent1 5 3" xfId="672" xr:uid="{B59E7750-BB3C-424F-87E5-D7F84E510615}"/>
+    <cellStyle name="40% - Accent1 5 3 2" xfId="1256" xr:uid="{7B2E6DEA-CBAF-469F-8C3F-7AC6CFAF0392}"/>
+    <cellStyle name="40% - Accent1 5 3 3" xfId="2030" xr:uid="{F38CE4C1-5D57-4E21-9E32-2E7E40A76011}"/>
+    <cellStyle name="40% - Accent1 5 4" xfId="756" xr:uid="{473E0937-22D1-451E-AD38-2EDE3A6A7A03}"/>
+    <cellStyle name="40% - Accent1 5 4 2" xfId="2114" xr:uid="{C499A08F-9FA7-4983-8972-EB3BF9A0505D}"/>
+    <cellStyle name="40% - Accent1 5 5" xfId="367" xr:uid="{1761DEE8-049F-4BC7-A2F8-5FDF15D9CA72}"/>
+    <cellStyle name="40% - Accent1 5 5 2" xfId="1734" xr:uid="{E732431C-3C33-41FF-BB59-8B4D54B108A0}"/>
+    <cellStyle name="40% - Accent1 5 6" xfId="167" xr:uid="{000A614D-0098-4FFA-A5E4-5FC7888407DD}"/>
+    <cellStyle name="40% - Accent1 5 6 2" xfId="1536" xr:uid="{53B03ABB-B3C9-4B05-901A-FB0154A4EB88}"/>
+    <cellStyle name="40% - Accent1 5 7" xfId="1057" xr:uid="{C6072BCA-E5E0-486E-A997-ED28B4BAD9CA}"/>
+    <cellStyle name="40% - Accent1 5 8" xfId="1466" xr:uid="{109752EE-A0E8-4E7A-935B-5C254FA4F33E}"/>
+    <cellStyle name="40% - Accent1 6" xfId="179" xr:uid="{805DBD6F-600B-4AFF-8349-4C331BAEC6C4}"/>
+    <cellStyle name="40% - Accent1 6 2" xfId="614" xr:uid="{6635F4F2-058F-45DD-8A91-0530B1506C76}"/>
+    <cellStyle name="40% - Accent1 6 2 2" xfId="1269" xr:uid="{691ED2E7-506C-42AE-B536-39D43D60723B}"/>
+    <cellStyle name="40% - Accent1 6 2 3" xfId="1972" xr:uid="{3DB1A4C9-EECE-48DF-B36B-8497F5F6E756}"/>
+    <cellStyle name="40% - Accent1 6 3" xfId="814" xr:uid="{796F1BF2-60D7-4CF2-9CE1-D793603F30C4}"/>
+    <cellStyle name="40% - Accent1 6 3 2" xfId="2172" xr:uid="{CF0FC0A4-BEFA-4FF2-98C8-F937109BB729}"/>
+    <cellStyle name="40% - Accent1 6 4" xfId="425" xr:uid="{DAA6E871-C339-4B03-A4CF-5B0B16130582}"/>
+    <cellStyle name="40% - Accent1 6 4 2" xfId="1792" xr:uid="{AA0690F6-B2CF-4DF2-91DC-A4E40F98E2E2}"/>
+    <cellStyle name="40% - Accent1 6 5" xfId="1069" xr:uid="{A54223EF-45BE-4556-A285-216DC4E17E57}"/>
+    <cellStyle name="40% - Accent1 6 6" xfId="1548" xr:uid="{EDBEA5F7-EC33-4246-B612-803679F774E8}"/>
+    <cellStyle name="40% - Accent1 7" xfId="297" xr:uid="{9B708C98-052E-40DA-B55C-D8A1CB2E85C1}"/>
+    <cellStyle name="40% - Accent1 7 2" xfId="686" xr:uid="{0A907403-79A3-4AFB-85F5-33AE8F4C0998}"/>
+    <cellStyle name="40% - Accent1 7 2 2" xfId="1327" xr:uid="{24BE4B70-D981-4D35-AA82-0CF85BD6C98B}"/>
+    <cellStyle name="40% - Accent1 7 2 3" xfId="2044" xr:uid="{760923B8-00EB-4B29-A1B0-AC60B4FDD3C4}"/>
+    <cellStyle name="40% - Accent1 7 3" xfId="827" xr:uid="{4E523FCD-5664-437C-B523-78D4DA1CE446}"/>
+    <cellStyle name="40% - Accent1 7 3 2" xfId="2184" xr:uid="{50FE4183-45C1-4EEE-B8C0-9C617E1F955C}"/>
+    <cellStyle name="40% - Accent1 7 4" xfId="439" xr:uid="{E81BF230-E414-45AC-BBF4-EB79AA1F9141}"/>
+    <cellStyle name="40% - Accent1 7 4 2" xfId="1804" xr:uid="{5BE00125-08AA-4E63-8C1B-469A192F6005}"/>
+    <cellStyle name="40% - Accent1 7 5" xfId="1183" xr:uid="{9B37ECAB-1D36-4975-BDDC-2609680A44FD}"/>
+    <cellStyle name="40% - Accent1 7 6" xfId="1664" xr:uid="{0F5B0F9D-6108-4814-B8F3-E7DC2B3BBC4B}"/>
+    <cellStyle name="40% - Accent1 8" xfId="558" xr:uid="{CC641BFF-A6DE-412E-9CC8-53592610383D}"/>
+    <cellStyle name="40% - Accent1 8 2" xfId="1197" xr:uid="{69F49FD8-33BB-4BDD-A66C-5FD95531AFEE}"/>
+    <cellStyle name="40% - Accent1 8 3" xfId="1916" xr:uid="{90FF8D25-DA0F-435E-9756-82537979074A}"/>
+    <cellStyle name="40% - Accent1 9" xfId="698" xr:uid="{09E88A1B-73DA-4040-8151-3D3BB75458A1}"/>
+    <cellStyle name="40% - Accent1 9 2" xfId="1341" xr:uid="{B2CCC0EF-ECE8-4F30-981F-D0D966E1E431}"/>
+    <cellStyle name="40% - Accent1 9 3" xfId="2056" xr:uid="{1A85258A-1CBF-4A34-8C6A-9A9CB15C80D1}"/>
+    <cellStyle name="40% - Accent2" xfId="21" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2 10" xfId="311" xr:uid="{B4137E64-3317-4768-95A6-E8B5CF37EC9F}"/>
+    <cellStyle name="40% - Accent2 10 2" xfId="1357" xr:uid="{21F3A019-F76E-478F-8F98-3093549B3A15}"/>
+    <cellStyle name="40% - Accent2 10 3" xfId="1678" xr:uid="{5BCEAC9B-6ADD-4C00-8FD9-70415DB46C8A}"/>
+    <cellStyle name="40% - Accent2 11" xfId="111" xr:uid="{FB05C889-4ECE-4C57-8D82-B07012419009}"/>
+    <cellStyle name="40% - Accent2 11 2" xfId="1370" xr:uid="{88C5A208-B238-45D2-B1BA-B5B836AC8123}"/>
+    <cellStyle name="40% - Accent2 11 3" xfId="1480" xr:uid="{D228DB65-720B-43DF-B7D5-9C6EDE221B31}"/>
+    <cellStyle name="40% - Accent2 12" xfId="944" xr:uid="{A74FE937-4221-4831-9DBA-61500D1DA807}"/>
+    <cellStyle name="40% - Accent2 12 2" xfId="1383" xr:uid="{A22A2CC6-D6A8-4BD2-AD62-9ED33D22E7E2}"/>
+    <cellStyle name="40% - Accent2 12 3" xfId="2300" xr:uid="{5FF7322C-D6B9-4819-AAD9-4BEB89346C66}"/>
+    <cellStyle name="40% - Accent2 13" xfId="958" xr:uid="{94DCC92C-ADBD-4CAD-A2DB-A96972DC150D}"/>
+    <cellStyle name="40% - Accent2 13 2" xfId="1397" xr:uid="{3E4DAD95-54F6-4E32-8C39-81FADFF72206}"/>
+    <cellStyle name="40% - Accent2 13 3" xfId="2314" xr:uid="{8AC3C4DF-D1C5-4272-BD9A-CBC835BB0363}"/>
+    <cellStyle name="40% - Accent2 14" xfId="972" xr:uid="{F322CA50-330D-4120-8399-2924F83B4F0B}"/>
+    <cellStyle name="40% - Accent2 14 2" xfId="2328" xr:uid="{CF619A5D-1439-437A-AD06-9F87907989B2}"/>
+    <cellStyle name="40% - Accent2 15" xfId="988" xr:uid="{61F92229-11E7-4F71-B18D-9A2EC9CE01B8}"/>
+    <cellStyle name="40% - Accent2 16" xfId="1001" xr:uid="{E9CE4D00-E812-47E2-96D4-5903BD993D93}"/>
+    <cellStyle name="40% - Accent2 17" xfId="1410" xr:uid="{85F74339-F7DD-4328-9B0A-94BF361CB303}"/>
+    <cellStyle name="40% - Accent2 2" xfId="52" xr:uid="{FF3248BF-6F14-4D2A-AA84-E3C6B1C7EF88}"/>
+    <cellStyle name="40% - Accent2 2 2" xfId="257" xr:uid="{FAEE0091-D7B4-4387-A535-64DC2A425BB2}"/>
+    <cellStyle name="40% - Accent2 2 2 2" xfId="520" xr:uid="{7D60D75D-49FC-4B36-873D-C6F195A03795}"/>
+    <cellStyle name="40% - Accent2 2 2 2 2" xfId="902" xr:uid="{D960D2FA-AE10-4501-9349-9C89036C176A}"/>
+    <cellStyle name="40% - Accent2 2 2 2 2 2" xfId="2258" xr:uid="{E0BEE59A-799A-42F2-8602-4D099F36B71F}"/>
+    <cellStyle name="40% - Accent2 2 2 2 3" xfId="1287" xr:uid="{57C9E42D-B460-43E0-B136-27A613312D25}"/>
+    <cellStyle name="40% - Accent2 2 2 2 4" xfId="1878" xr:uid="{14E0C5FC-D3B4-430A-AE26-8832B6D21492}"/>
+    <cellStyle name="40% - Accent2 2 2 3" xfId="632" xr:uid="{666CA891-C960-4B64-B33B-50F07FE86E33}"/>
+    <cellStyle name="40% - Accent2 2 2 3 2" xfId="1990" xr:uid="{C25400CA-F0E6-4AF3-AEE3-17B4227614C8}"/>
+    <cellStyle name="40% - Accent2 2 2 4" xfId="774" xr:uid="{8DD29EFD-C3ED-4048-B88B-787D2CB6239E}"/>
+    <cellStyle name="40% - Accent2 2 2 4 2" xfId="2132" xr:uid="{E00CA480-1B07-45D3-B8EC-07FFBC25BD37}"/>
+    <cellStyle name="40% - Accent2 2 2 5" xfId="385" xr:uid="{7BEBE430-EF31-4E85-9072-E08D8B0C83D1}"/>
+    <cellStyle name="40% - Accent2 2 2 5 2" xfId="1752" xr:uid="{70A0A0D3-18E7-4416-8969-12BBD8BD72BE}"/>
+    <cellStyle name="40% - Accent2 2 2 6" xfId="1143" xr:uid="{264612B3-D53F-44D7-8199-F0B3881F9C4E}"/>
+    <cellStyle name="40% - Accent2 2 2 7" xfId="1624" xr:uid="{7F2E520C-5A9C-4964-96F8-0D5487901287}"/>
+    <cellStyle name="40% - Accent2 2 3" xfId="197" xr:uid="{18111C14-C1EE-4B9E-8514-BFCB2F5EC5F3}"/>
+    <cellStyle name="40% - Accent2 2 3 2" xfId="845" xr:uid="{7EAD9A08-6EA0-4FCE-9437-4CC136B2B651}"/>
+    <cellStyle name="40% - Accent2 2 3 2 2" xfId="2202" xr:uid="{FC38678F-DE00-4625-92B8-3571EAF66245}"/>
+    <cellStyle name="40% - Accent2 2 3 3" xfId="457" xr:uid="{C9480F01-E4C2-4392-90D0-00EEC7AF430A}"/>
+    <cellStyle name="40% - Accent2 2 3 3 2" xfId="1822" xr:uid="{FE25B3AF-0BDC-413D-B8EC-4B6D40434C49}"/>
+    <cellStyle name="40% - Accent2 2 3 4" xfId="1087" xr:uid="{FC28B324-7220-43D0-92D6-995037076F32}"/>
+    <cellStyle name="40% - Accent2 2 3 5" xfId="1566" xr:uid="{04A7CAD6-8AAE-4934-AE7C-C5D102323A17}"/>
+    <cellStyle name="40% - Accent2 2 4" xfId="576" xr:uid="{C425BFAF-E59F-4857-9AED-E4881019429F}"/>
+    <cellStyle name="40% - Accent2 2 4 2" xfId="1216" xr:uid="{DF2F52AA-6ED9-4F43-871A-9507A6F8FA55}"/>
+    <cellStyle name="40% - Accent2 2 4 3" xfId="1934" xr:uid="{1AB44DD5-918E-48B5-A944-B78F58909F7F}"/>
+    <cellStyle name="40% - Accent2 2 5" xfId="716" xr:uid="{9E6C91BB-9782-43C3-9235-9E12C1FC2E7C}"/>
+    <cellStyle name="40% - Accent2 2 5 2" xfId="2074" xr:uid="{8D838A0B-F6C2-4020-A70E-8B5EE9A0CEC4}"/>
+    <cellStyle name="40% - Accent2 2 6" xfId="327" xr:uid="{13059DCA-A17C-4EF4-A26D-C5CC64EFB864}"/>
+    <cellStyle name="40% - Accent2 2 6 2" xfId="1694" xr:uid="{2C4FD01F-E4F9-4A34-ABBD-4EB64A17E30E}"/>
+    <cellStyle name="40% - Accent2 2 7" xfId="127" xr:uid="{EB040D6C-77B0-4724-8C64-1F50B2822062}"/>
+    <cellStyle name="40% - Accent2 2 7 2" xfId="1496" xr:uid="{FDCFC326-A0A5-4C0B-A446-301D00B50EC6}"/>
+    <cellStyle name="40% - Accent2 2 8" xfId="1017" xr:uid="{3AC96E9F-3E5E-4854-90DF-1655D7EBE1C9}"/>
+    <cellStyle name="40% - Accent2 2 9" xfId="1426" xr:uid="{54AB5701-5642-4563-821E-1EB80E9D0519}"/>
+    <cellStyle name="40% - Accent2 3" xfId="70" xr:uid="{49F5110D-DE36-4534-A606-01C6D45EB501}"/>
+    <cellStyle name="40% - Accent2 3 2" xfId="271" xr:uid="{7B58A3C2-AA6A-42D0-8191-8A30D7A6D313}"/>
+    <cellStyle name="40% - Accent2 3 2 2" xfId="534" xr:uid="{DB08A2BC-3AD0-4065-ACFA-3007DC23B196}"/>
+    <cellStyle name="40% - Accent2 3 2 2 2" xfId="916" xr:uid="{3306D3AF-814B-4B00-8450-03BC83F164CE}"/>
+    <cellStyle name="40% - Accent2 3 2 2 2 2" xfId="2272" xr:uid="{6BC53FAD-ACD7-4009-B81A-A9A6094AF43D}"/>
+    <cellStyle name="40% - Accent2 3 2 2 3" xfId="1301" xr:uid="{E61703C3-DF6B-4FF7-A02C-7A8AD61A44BE}"/>
+    <cellStyle name="40% - Accent2 3 2 2 4" xfId="1892" xr:uid="{90E61F71-9398-4176-A2B5-7036CBA464C1}"/>
+    <cellStyle name="40% - Accent2 3 2 3" xfId="646" xr:uid="{AEF55FE8-8D0D-4EBC-9CAC-4B1C19656AD1}"/>
+    <cellStyle name="40% - Accent2 3 2 3 2" xfId="2004" xr:uid="{1D6A365E-C11B-4E3C-9521-E5D739BD05E9}"/>
+    <cellStyle name="40% - Accent2 3 2 4" xfId="788" xr:uid="{8D085033-746D-4699-998F-A03BF7E515F2}"/>
+    <cellStyle name="40% - Accent2 3 2 4 2" xfId="2146" xr:uid="{22550FD1-E1C8-4B3A-86A2-75757FFE3B51}"/>
+    <cellStyle name="40% - Accent2 3 2 5" xfId="399" xr:uid="{BED11B42-3983-4D1D-BBE2-C8B8C5A0793A}"/>
+    <cellStyle name="40% - Accent2 3 2 5 2" xfId="1766" xr:uid="{2532B1F6-F245-4B67-812C-9BF81A1E90F9}"/>
+    <cellStyle name="40% - Accent2 3 2 6" xfId="1157" xr:uid="{06B64264-0C8F-446C-8121-C096FE5B64C0}"/>
+    <cellStyle name="40% - Accent2 3 2 7" xfId="1638" xr:uid="{5CE84226-F77B-4AFC-92AA-14F1296E66DA}"/>
+    <cellStyle name="40% - Accent2 3 3" xfId="211" xr:uid="{1FF38E93-3975-452D-81F0-123721FE73C7}"/>
+    <cellStyle name="40% - Accent2 3 3 2" xfId="859" xr:uid="{DF782BB8-83DC-4B37-B429-CAA9E95243FF}"/>
+    <cellStyle name="40% - Accent2 3 3 2 2" xfId="2216" xr:uid="{9B248EA3-DCAC-4BFF-9651-F109938A843B}"/>
+    <cellStyle name="40% - Accent2 3 3 3" xfId="471" xr:uid="{CB76E6B9-73CB-4FF2-9804-90AA2AE3C7D3}"/>
+    <cellStyle name="40% - Accent2 3 3 3 2" xfId="1836" xr:uid="{EEB3D4C3-48EE-4A34-8D27-21158F1935C2}"/>
+    <cellStyle name="40% - Accent2 3 3 4" xfId="1101" xr:uid="{9A81E31C-7A50-430E-972C-8FDFD87BCF4F}"/>
+    <cellStyle name="40% - Accent2 3 3 5" xfId="1580" xr:uid="{C8779345-7401-4E89-8A2D-91CFB3ED2985}"/>
+    <cellStyle name="40% - Accent2 3 4" xfId="590" xr:uid="{AC0BAC91-7D2A-460D-A1A1-0DA9F19B1DA4}"/>
+    <cellStyle name="40% - Accent2 3 4 2" xfId="1230" xr:uid="{1F697C9E-0C03-40A2-B42D-70FC8AD5DC1B}"/>
+    <cellStyle name="40% - Accent2 3 4 3" xfId="1948" xr:uid="{6B65D9EB-2CE5-4016-A909-6447B63C6536}"/>
+    <cellStyle name="40% - Accent2 3 5" xfId="730" xr:uid="{119FAC89-18FC-4E70-B174-958E4582ED54}"/>
+    <cellStyle name="40% - Accent2 3 5 2" xfId="2088" xr:uid="{265FD3AF-BEAF-436E-9ED8-0161F106045C}"/>
+    <cellStyle name="40% - Accent2 3 6" xfId="341" xr:uid="{754C3268-E35D-49A5-A29A-093CF5A86AE3}"/>
+    <cellStyle name="40% - Accent2 3 6 2" xfId="1708" xr:uid="{A48D9BF2-DEFC-47BB-A91D-0A87B1F24797}"/>
+    <cellStyle name="40% - Accent2 3 7" xfId="141" xr:uid="{06DA5E46-D055-42AF-B72B-F1D701852BEA}"/>
+    <cellStyle name="40% - Accent2 3 7 2" xfId="1510" xr:uid="{20DD2E71-5E7A-4098-ADB7-F59BDE14A1E5}"/>
+    <cellStyle name="40% - Accent2 3 8" xfId="1031" xr:uid="{14A8418F-CE90-42ED-81DB-4362C8227018}"/>
+    <cellStyle name="40% - Accent2 3 9" xfId="1440" xr:uid="{7B46A3AD-CAEC-4043-A7E8-F04FB1A30BC8}"/>
+    <cellStyle name="40% - Accent2 4" xfId="84" xr:uid="{BBA59256-4E21-41F0-A658-4585050B85A7}"/>
+    <cellStyle name="40% - Accent2 4 2" xfId="284" xr:uid="{19513DF5-8FB4-4DD7-9545-961FCAE23534}"/>
+    <cellStyle name="40% - Accent2 4 2 2" xfId="548" xr:uid="{8E7FA39D-BA5F-4FBC-8D6C-020013598362}"/>
+    <cellStyle name="40% - Accent2 4 2 2 2" xfId="930" xr:uid="{ECDD74C5-DF88-4744-B113-B4C70FD9B0CE}"/>
+    <cellStyle name="40% - Accent2 4 2 2 2 2" xfId="2286" xr:uid="{6C474446-005A-4BA0-B9C6-3566C5AB1BEF}"/>
+    <cellStyle name="40% - Accent2 4 2 2 3" xfId="1315" xr:uid="{5750E211-43ED-42E2-B648-9578B41B1125}"/>
+    <cellStyle name="40% - Accent2 4 2 2 4" xfId="1906" xr:uid="{D5857DF7-68FD-4EA8-96B8-F6B28B5F028F}"/>
+    <cellStyle name="40% - Accent2 4 2 3" xfId="660" xr:uid="{1650B0F5-7907-4DC1-8634-C25ECCBBCD8A}"/>
+    <cellStyle name="40% - Accent2 4 2 3 2" xfId="2018" xr:uid="{2A5472B1-BC61-4CBB-9666-3706EB7D5741}"/>
+    <cellStyle name="40% - Accent2 4 2 4" xfId="801" xr:uid="{7D7635E0-6E1A-4E55-864D-A35FF45223A5}"/>
+    <cellStyle name="40% - Accent2 4 2 4 2" xfId="2159" xr:uid="{0E8BD19E-81B0-4CC3-BB38-7993138A2AE3}"/>
+    <cellStyle name="40% - Accent2 4 2 5" xfId="412" xr:uid="{9C43CC45-1D9E-4F9D-9ADD-71003219DB7E}"/>
+    <cellStyle name="40% - Accent2 4 2 5 2" xfId="1779" xr:uid="{29D419BF-2C03-49F1-ABCF-FFD253CAC93A}"/>
+    <cellStyle name="40% - Accent2 4 2 6" xfId="1171" xr:uid="{19A1CD72-25EC-407F-AEF4-F0D69F700208}"/>
+    <cellStyle name="40% - Accent2 4 2 7" xfId="1651" xr:uid="{B7B6DD86-CB3D-4679-B7AD-FCBA3CC6A489}"/>
+    <cellStyle name="40% - Accent2 4 3" xfId="225" xr:uid="{01F61DF1-9EF8-4E2F-8A2E-950D1495691C}"/>
+    <cellStyle name="40% - Accent2 4 3 2" xfId="873" xr:uid="{BD6607D2-BB2D-42C3-904E-3429B1BA433D}"/>
+    <cellStyle name="40% - Accent2 4 3 2 2" xfId="2230" xr:uid="{C0217792-4B3A-41AF-8423-0C8A67B8B1D6}"/>
+    <cellStyle name="40% - Accent2 4 3 3" xfId="485" xr:uid="{FB530CB1-5D07-4F42-87FD-35594CD4D1A1}"/>
+    <cellStyle name="40% - Accent2 4 3 3 2" xfId="1850" xr:uid="{DCC4FF85-086A-4726-8BB1-4D0F40085C64}"/>
+    <cellStyle name="40% - Accent2 4 3 4" xfId="1115" xr:uid="{5954E946-1B14-408C-A6F4-F234C88C0514}"/>
+    <cellStyle name="40% - Accent2 4 3 5" xfId="1594" xr:uid="{2312F1FD-36C6-45A0-BDE9-2922B56861C1}"/>
+    <cellStyle name="40% - Accent2 4 4" xfId="604" xr:uid="{6ED53F16-FA35-4C99-AE7C-9DE4EAA44552}"/>
+    <cellStyle name="40% - Accent2 4 4 2" xfId="1244" xr:uid="{EED52CEE-384A-41D8-9A1F-6CA569C1A325}"/>
+    <cellStyle name="40% - Accent2 4 4 3" xfId="1962" xr:uid="{169E4352-D766-4F38-8C66-594287B052F0}"/>
+    <cellStyle name="40% - Accent2 4 5" xfId="744" xr:uid="{F465DEB5-C59F-4D57-A67A-F127B182E6F2}"/>
+    <cellStyle name="40% - Accent2 4 5 2" xfId="2102" xr:uid="{B179EBE3-37EE-4D2E-97DD-400D195BCFBA}"/>
+    <cellStyle name="40% - Accent2 4 6" xfId="355" xr:uid="{E8A8FA9A-20C2-46BC-81B1-8D5D58FCC634}"/>
+    <cellStyle name="40% - Accent2 4 6 2" xfId="1722" xr:uid="{86BEC7D5-E467-432D-95D8-D6A2330DF1F3}"/>
+    <cellStyle name="40% - Accent2 4 7" xfId="155" xr:uid="{B548D010-B8D2-4646-B20D-DAB7851C8883}"/>
+    <cellStyle name="40% - Accent2 4 7 2" xfId="1524" xr:uid="{34FA5566-E672-4D31-8CC9-8C7EC812E481}"/>
+    <cellStyle name="40% - Accent2 4 8" xfId="1045" xr:uid="{9405399E-087B-4B7C-9D57-F600B41097F5}"/>
+    <cellStyle name="40% - Accent2 4 9" xfId="1454" xr:uid="{9EE8DFF0-CD08-4F88-A932-ADB32BFA056C}"/>
+    <cellStyle name="40% - Accent2 5" xfId="98" xr:uid="{CFF85F88-DCC0-4343-9A15-AD4D4F770592}"/>
+    <cellStyle name="40% - Accent2 5 2" xfId="241" xr:uid="{725F6481-C39E-497E-B5C5-63CA0573C565}"/>
+    <cellStyle name="40% - Accent2 5 2 2" xfId="886" xr:uid="{4FD85FEF-61C9-4799-A304-FEEED643AFA8}"/>
+    <cellStyle name="40% - Accent2 5 2 2 2" xfId="2242" xr:uid="{6C3B2BBC-FF01-4677-9B02-3DDCDC6A14FA}"/>
+    <cellStyle name="40% - Accent2 5 2 3" xfId="501" xr:uid="{76D9D795-CF7A-461E-9890-6EEDCED2C131}"/>
+    <cellStyle name="40% - Accent2 5 2 3 2" xfId="1862" xr:uid="{19B5EFF7-48B2-4D09-97B7-D5DC56639E2C}"/>
+    <cellStyle name="40% - Accent2 5 2 4" xfId="1127" xr:uid="{8E63C417-E54E-459D-87D4-622B3C3C0F33}"/>
+    <cellStyle name="40% - Accent2 5 2 5" xfId="1608" xr:uid="{42703D45-A720-4435-A8C2-A60636F4823A}"/>
+    <cellStyle name="40% - Accent2 5 3" xfId="674" xr:uid="{F4919308-F92B-4C27-A86E-3BD5EEE28649}"/>
+    <cellStyle name="40% - Accent2 5 3 2" xfId="1258" xr:uid="{441DF36B-C362-4194-B5F0-0D4B6D3DEBB4}"/>
+    <cellStyle name="40% - Accent2 5 3 3" xfId="2032" xr:uid="{BFF97638-8186-4660-AB59-BC0BD34D0B32}"/>
+    <cellStyle name="40% - Accent2 5 4" xfId="758" xr:uid="{13A71DC5-48CA-4179-9707-C8BB0BD993CD}"/>
+    <cellStyle name="40% - Accent2 5 4 2" xfId="2116" xr:uid="{1645C4A7-4DCA-4514-9E02-EA88067BADE8}"/>
+    <cellStyle name="40% - Accent2 5 5" xfId="369" xr:uid="{C7B6EA54-3D4F-4234-8F7A-A72BD054036F}"/>
+    <cellStyle name="40% - Accent2 5 5 2" xfId="1736" xr:uid="{A1B583D5-37AE-4813-8B32-1855743B2996}"/>
+    <cellStyle name="40% - Accent2 5 6" xfId="169" xr:uid="{AFC08B08-2BAE-4CBD-9237-1B366A35DAA4}"/>
+    <cellStyle name="40% - Accent2 5 6 2" xfId="1538" xr:uid="{061C8059-3821-4E20-9FD3-27A1EF865415}"/>
+    <cellStyle name="40% - Accent2 5 7" xfId="1059" xr:uid="{47BEF0CF-158D-4A90-A4A1-BABF1A0E1556}"/>
+    <cellStyle name="40% - Accent2 5 8" xfId="1468" xr:uid="{545FD9B3-21E7-45BD-AF40-5A5C387C12A5}"/>
+    <cellStyle name="40% - Accent2 6" xfId="181" xr:uid="{C1860324-2661-42C2-8FA0-8ED8DDD7DBA0}"/>
+    <cellStyle name="40% - Accent2 6 2" xfId="616" xr:uid="{B316437F-5768-4E26-B34F-86B05CCA0A2D}"/>
+    <cellStyle name="40% - Accent2 6 2 2" xfId="1271" xr:uid="{8E89BCD5-F7E9-4665-9F6A-983E76670858}"/>
+    <cellStyle name="40% - Accent2 6 2 3" xfId="1974" xr:uid="{93C12C92-07F5-4CE0-9FA5-C6AA023F3317}"/>
+    <cellStyle name="40% - Accent2 6 3" xfId="816" xr:uid="{863FEFBD-9856-4F30-8706-086B1E63B05A}"/>
+    <cellStyle name="40% - Accent2 6 3 2" xfId="2174" xr:uid="{724925F6-76FC-4925-9303-6F07F87D22A9}"/>
+    <cellStyle name="40% - Accent2 6 4" xfId="427" xr:uid="{F5B6CCAE-33DE-4807-8BAF-08226A8EAD6C}"/>
+    <cellStyle name="40% - Accent2 6 4 2" xfId="1794" xr:uid="{C5D7FAB3-E1B7-4515-BA60-C439EEE67F66}"/>
+    <cellStyle name="40% - Accent2 6 5" xfId="1071" xr:uid="{2007F9DC-C310-4704-991C-404238E7F63D}"/>
+    <cellStyle name="40% - Accent2 6 6" xfId="1550" xr:uid="{1FDD2F71-36E2-48B3-AEB9-4AB99735E2FA}"/>
+    <cellStyle name="40% - Accent2 7" xfId="299" xr:uid="{B18C4F44-35DC-436E-95A8-B27527709E57}"/>
+    <cellStyle name="40% - Accent2 7 2" xfId="688" xr:uid="{EC20B027-11E1-49E7-A623-C32D14ABB07D}"/>
+    <cellStyle name="40% - Accent2 7 2 2" xfId="1329" xr:uid="{547A7044-9048-4169-9A4E-7B42DB64F939}"/>
+    <cellStyle name="40% - Accent2 7 2 3" xfId="2046" xr:uid="{1DFE0B15-DD57-4A06-96F4-E1D1E61EDB3D}"/>
+    <cellStyle name="40% - Accent2 7 3" xfId="829" xr:uid="{BA295C95-AA61-4165-AFD0-FF7FDF689467}"/>
+    <cellStyle name="40% - Accent2 7 3 2" xfId="2186" xr:uid="{743BB7B4-E576-48AB-923D-F46ED5BDC625}"/>
+    <cellStyle name="40% - Accent2 7 4" xfId="441" xr:uid="{9A35920D-94B0-4D79-971E-97E88D531E87}"/>
+    <cellStyle name="40% - Accent2 7 4 2" xfId="1806" xr:uid="{3D875D1B-33F2-40B8-BB30-934DEA0F6EE5}"/>
+    <cellStyle name="40% - Accent2 7 5" xfId="1185" xr:uid="{DAD1F374-763E-46CD-99F2-A1676DF06809}"/>
+    <cellStyle name="40% - Accent2 7 6" xfId="1666" xr:uid="{7B3B83CC-5E1B-4501-8D70-8082EC1682B4}"/>
+    <cellStyle name="40% - Accent2 8" xfId="560" xr:uid="{3A1FA042-E378-4A19-BABC-680AB559BFB3}"/>
+    <cellStyle name="40% - Accent2 8 2" xfId="1199" xr:uid="{49192B95-7EB0-4277-A349-735DE947BB7F}"/>
+    <cellStyle name="40% - Accent2 8 3" xfId="1918" xr:uid="{02126331-11D5-4372-B643-7E887A30D230}"/>
+    <cellStyle name="40% - Accent2 9" xfId="700" xr:uid="{A2531777-9837-44AA-849C-6FF901DDD212}"/>
+    <cellStyle name="40% - Accent2 9 2" xfId="1343" xr:uid="{57ACDBDD-B1C6-4D81-A157-C2C56D0EF1D2}"/>
+    <cellStyle name="40% - Accent2 9 3" xfId="2058" xr:uid="{8360FD69-BC11-4270-AAB5-6078DD93075D}"/>
+    <cellStyle name="40% - Accent3" xfId="24" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3 10" xfId="313" xr:uid="{AD7D0EAF-132E-4BEB-8FA3-8356571E2C2A}"/>
+    <cellStyle name="40% - Accent3 10 2" xfId="1359" xr:uid="{C02CE692-2E00-45E0-B763-7A63B464BE25}"/>
+    <cellStyle name="40% - Accent3 10 3" xfId="1680" xr:uid="{EB48C534-81FE-4F12-B8F6-74481DA548B3}"/>
+    <cellStyle name="40% - Accent3 11" xfId="113" xr:uid="{9AA2FB75-0174-4F4B-B608-8C5451B07535}"/>
+    <cellStyle name="40% - Accent3 11 2" xfId="1372" xr:uid="{6113077F-1D53-4DF0-AB6E-8B018297C8F3}"/>
+    <cellStyle name="40% - Accent3 11 3" xfId="1482" xr:uid="{02AC2711-04A8-49C9-B29C-810796046BBF}"/>
+    <cellStyle name="40% - Accent3 12" xfId="946" xr:uid="{B7E2C1BB-7D73-4B3A-ACCF-84929EE12906}"/>
+    <cellStyle name="40% - Accent3 12 2" xfId="1385" xr:uid="{FCB8A034-CEF3-4D31-AD70-D541804FD267}"/>
+    <cellStyle name="40% - Accent3 12 3" xfId="2302" xr:uid="{B3AC4AAC-0289-485B-BD7C-5C9D859AB6F8}"/>
+    <cellStyle name="40% - Accent3 13" xfId="960" xr:uid="{D55612FF-430B-45B9-94C1-2A76F5991A14}"/>
+    <cellStyle name="40% - Accent3 13 2" xfId="1399" xr:uid="{19CD1B2A-93C2-4482-BA47-24730C518B1B}"/>
+    <cellStyle name="40% - Accent3 13 3" xfId="2316" xr:uid="{569A1BF8-89E0-4DEB-BC9B-6D60411F04C0}"/>
+    <cellStyle name="40% - Accent3 14" xfId="974" xr:uid="{BB070A65-23FA-4ECB-9035-C527B43E8CAA}"/>
+    <cellStyle name="40% - Accent3 14 2" xfId="2330" xr:uid="{9762607D-8738-4C70-B30E-0EC6304F8754}"/>
+    <cellStyle name="40% - Accent3 15" xfId="990" xr:uid="{44807420-2E6C-4DFA-A3A7-1393DAC2636D}"/>
+    <cellStyle name="40% - Accent3 16" xfId="1003" xr:uid="{C0853C7F-1BC2-46A0-964E-1FCC9CA674FE}"/>
+    <cellStyle name="40% - Accent3 17" xfId="1412" xr:uid="{AD006E9D-37A5-4F2C-A72B-6C5AA92C3E48}"/>
+    <cellStyle name="40% - Accent3 2" xfId="54" xr:uid="{CC78612F-FDAE-460A-A60D-7620C51AD429}"/>
+    <cellStyle name="40% - Accent3 2 2" xfId="259" xr:uid="{BF8C514E-0C1F-4785-A40C-3F4CD5DD3E48}"/>
+    <cellStyle name="40% - Accent3 2 2 2" xfId="522" xr:uid="{3BADAB9D-42F7-456E-AB8A-13F624E8167D}"/>
+    <cellStyle name="40% - Accent3 2 2 2 2" xfId="904" xr:uid="{FAC1B425-7FAD-4C1C-AA70-E4BCD655DAC0}"/>
+    <cellStyle name="40% - Accent3 2 2 2 2 2" xfId="2260" xr:uid="{54475DCF-A762-4834-A7C6-DC8D81BB04F2}"/>
+    <cellStyle name="40% - Accent3 2 2 2 3" xfId="1289" xr:uid="{6E46E9A6-1C16-46A6-97BD-26A55BFCC113}"/>
+    <cellStyle name="40% - Accent3 2 2 2 4" xfId="1880" xr:uid="{9E1F8E64-57CB-4ACE-8876-1C554873A7D4}"/>
+    <cellStyle name="40% - Accent3 2 2 3" xfId="634" xr:uid="{C57D1747-0226-4B3C-9832-222C816041DE}"/>
+    <cellStyle name="40% - Accent3 2 2 3 2" xfId="1992" xr:uid="{1AD300AD-A2F5-4241-AB73-7883B5CF8299}"/>
+    <cellStyle name="40% - Accent3 2 2 4" xfId="776" xr:uid="{AD57F2F4-AD16-477B-827D-B6F40DAED781}"/>
+    <cellStyle name="40% - Accent3 2 2 4 2" xfId="2134" xr:uid="{9B04301F-1F2B-41C9-BCF3-CF29DE0ECE1E}"/>
+    <cellStyle name="40% - Accent3 2 2 5" xfId="387" xr:uid="{0EBA7971-13BE-459D-885D-8FFC3F70EE63}"/>
+    <cellStyle name="40% - Accent3 2 2 5 2" xfId="1754" xr:uid="{4BB1B529-EB0E-42E2-ABB8-B503840AC102}"/>
+    <cellStyle name="40% - Accent3 2 2 6" xfId="1145" xr:uid="{C16F7F33-D657-4298-8370-26FDE30E6302}"/>
+    <cellStyle name="40% - Accent3 2 2 7" xfId="1626" xr:uid="{B8E74FA9-33AE-4452-85CC-957463F76529}"/>
+    <cellStyle name="40% - Accent3 2 3" xfId="199" xr:uid="{C1536D78-8817-49B7-90EF-234BC3530263}"/>
+    <cellStyle name="40% - Accent3 2 3 2" xfId="847" xr:uid="{C5FFC589-F2E6-4601-B357-6AC76D17C385}"/>
+    <cellStyle name="40% - Accent3 2 3 2 2" xfId="2204" xr:uid="{0E2BBB87-7FA8-4DA9-BD25-773170CEF370}"/>
+    <cellStyle name="40% - Accent3 2 3 3" xfId="459" xr:uid="{229175E0-4321-433B-B2E9-69B0BF37B1AD}"/>
+    <cellStyle name="40% - Accent3 2 3 3 2" xfId="1824" xr:uid="{30542E45-763C-438F-B527-537D894F1DD4}"/>
+    <cellStyle name="40% - Accent3 2 3 4" xfId="1089" xr:uid="{92AEE9C1-90DE-440A-8661-11BF31557331}"/>
+    <cellStyle name="40% - Accent3 2 3 5" xfId="1568" xr:uid="{8747B5E4-A103-49E5-BCFD-6DBDCD04B193}"/>
+    <cellStyle name="40% - Accent3 2 4" xfId="578" xr:uid="{580B04A0-A63E-4378-91DC-25DBB71701CC}"/>
+    <cellStyle name="40% - Accent3 2 4 2" xfId="1218" xr:uid="{82A4C9C2-1EBF-40B9-974B-127BD5AD846D}"/>
+    <cellStyle name="40% - Accent3 2 4 3" xfId="1936" xr:uid="{A2B93F1A-E3D8-408B-8C07-3D31C6E528D2}"/>
+    <cellStyle name="40% - Accent3 2 5" xfId="718" xr:uid="{93E74C2D-32EA-4AD8-88B3-9EDA211D632F}"/>
+    <cellStyle name="40% - Accent3 2 5 2" xfId="2076" xr:uid="{EBBE814B-F358-4E0F-9BAF-F750E766D78F}"/>
+    <cellStyle name="40% - Accent3 2 6" xfId="329" xr:uid="{8854C19D-4AA3-4561-8216-7CE149AE0139}"/>
+    <cellStyle name="40% - Accent3 2 6 2" xfId="1696" xr:uid="{CEB3925D-D629-4071-88DE-B94EC27DAEEF}"/>
+    <cellStyle name="40% - Accent3 2 7" xfId="129" xr:uid="{3E611C97-BE8D-4B66-ADE6-98B6F6000D9E}"/>
+    <cellStyle name="40% - Accent3 2 7 2" xfId="1498" xr:uid="{77AC1F63-A460-4140-9C9A-D3527FED947E}"/>
+    <cellStyle name="40% - Accent3 2 8" xfId="1019" xr:uid="{220DD329-12F1-47E7-83BC-20E059EE5699}"/>
+    <cellStyle name="40% - Accent3 2 9" xfId="1428" xr:uid="{50BDEA41-54FF-4AC6-B8A2-364E9D14C2B9}"/>
+    <cellStyle name="40% - Accent3 3" xfId="72" xr:uid="{C25DDE1D-12FB-46D9-A442-C4830EBF8E08}"/>
+    <cellStyle name="40% - Accent3 3 2" xfId="273" xr:uid="{04297E17-E261-4338-9C61-E404FD480DAA}"/>
+    <cellStyle name="40% - Accent3 3 2 2" xfId="536" xr:uid="{BBC26403-0E94-4D40-94B2-9DE46DE3CAEC}"/>
+    <cellStyle name="40% - Accent3 3 2 2 2" xfId="918" xr:uid="{B61B5B37-0075-4443-B12A-0117F54E576D}"/>
+    <cellStyle name="40% - Accent3 3 2 2 2 2" xfId="2274" xr:uid="{FD05067F-6262-481D-98D2-648B77BC9971}"/>
+    <cellStyle name="40% - Accent3 3 2 2 3" xfId="1303" xr:uid="{46690C68-620F-4223-B92E-4505C1EC81B7}"/>
+    <cellStyle name="40% - Accent3 3 2 2 4" xfId="1894" xr:uid="{FB09AB2C-0CF2-44BD-BE0F-848A2B92F4A6}"/>
+    <cellStyle name="40% - Accent3 3 2 3" xfId="648" xr:uid="{FB79CF12-2C38-4C3B-839B-736264CC7077}"/>
+    <cellStyle name="40% - Accent3 3 2 3 2" xfId="2006" xr:uid="{6A93B9DA-B9DD-4479-BEEE-DE3C2D10ACFA}"/>
+    <cellStyle name="40% - Accent3 3 2 4" xfId="790" xr:uid="{152B988B-454C-4B5C-9D64-B2144F0030E7}"/>
+    <cellStyle name="40% - Accent3 3 2 4 2" xfId="2148" xr:uid="{3596FD0F-E727-4225-9B17-EE3421E1FE9A}"/>
+    <cellStyle name="40% - Accent3 3 2 5" xfId="401" xr:uid="{7FB4E6F2-C816-4385-8962-A115DB635754}"/>
+    <cellStyle name="40% - Accent3 3 2 5 2" xfId="1768" xr:uid="{198C742F-6EF8-4918-9CD4-20DDD587867C}"/>
+    <cellStyle name="40% - Accent3 3 2 6" xfId="1159" xr:uid="{A3EAE219-93BA-460A-9DC4-9D5903543B24}"/>
+    <cellStyle name="40% - Accent3 3 2 7" xfId="1640" xr:uid="{5EC56D03-0181-4779-9F70-4810EF03274C}"/>
+    <cellStyle name="40% - Accent3 3 3" xfId="213" xr:uid="{8A6F5778-FE33-4036-88E9-A68BB77DE478}"/>
+    <cellStyle name="40% - Accent3 3 3 2" xfId="861" xr:uid="{B47F09F5-E224-40B4-A5D2-642A51A0D226}"/>
+    <cellStyle name="40% - Accent3 3 3 2 2" xfId="2218" xr:uid="{45EF23C2-1F9A-4509-8482-BB8E9160AB70}"/>
+    <cellStyle name="40% - Accent3 3 3 3" xfId="473" xr:uid="{1EB8994B-CF31-45B6-BE93-0B0CCA6742A7}"/>
+    <cellStyle name="40% - Accent3 3 3 3 2" xfId="1838" xr:uid="{F9BA841B-B1C9-4F02-959F-178CBCBEEE42}"/>
+    <cellStyle name="40% - Accent3 3 3 4" xfId="1103" xr:uid="{ED04969B-5142-4567-AAE1-8B5465BDB8C7}"/>
+    <cellStyle name="40% - Accent3 3 3 5" xfId="1582" xr:uid="{6AD503EC-FC08-407D-9B98-28A379F1C6C7}"/>
+    <cellStyle name="40% - Accent3 3 4" xfId="592" xr:uid="{DA9CF510-795F-4B76-9D8C-4650F94C96B2}"/>
+    <cellStyle name="40% - Accent3 3 4 2" xfId="1232" xr:uid="{87302CE7-C8EA-49BA-843B-6C1385A9B748}"/>
+    <cellStyle name="40% - Accent3 3 4 3" xfId="1950" xr:uid="{E04B52C3-123B-43D4-9113-967F0A28CEB7}"/>
+    <cellStyle name="40% - Accent3 3 5" xfId="732" xr:uid="{4B962CE5-0F5B-4885-9AB6-2246F4B6D30B}"/>
+    <cellStyle name="40% - Accent3 3 5 2" xfId="2090" xr:uid="{0F267AF6-5CCB-4410-A307-EFD95BDC8EE3}"/>
+    <cellStyle name="40% - Accent3 3 6" xfId="343" xr:uid="{73EBB2E1-CE07-4D69-921B-CCA154FE8F0A}"/>
+    <cellStyle name="40% - Accent3 3 6 2" xfId="1710" xr:uid="{280EE153-45A0-4C8B-8BE2-43BF9141E098}"/>
+    <cellStyle name="40% - Accent3 3 7" xfId="143" xr:uid="{7BA65366-6CB9-4902-BEA8-35D41A502346}"/>
+    <cellStyle name="40% - Accent3 3 7 2" xfId="1512" xr:uid="{9F7345AE-881D-4A3A-9E67-11DB26481983}"/>
+    <cellStyle name="40% - Accent3 3 8" xfId="1033" xr:uid="{BCB04541-413C-4E61-BEE7-DEB176885F00}"/>
+    <cellStyle name="40% - Accent3 3 9" xfId="1442" xr:uid="{ADF72688-EBEC-4B09-B418-B57FD69D704E}"/>
+    <cellStyle name="40% - Accent3 4" xfId="86" xr:uid="{5DBD1901-9550-4161-B476-4728CFC7DEE7}"/>
+    <cellStyle name="40% - Accent3 4 2" xfId="286" xr:uid="{5768209D-CA87-49D0-A840-6D79DDF6A8B7}"/>
+    <cellStyle name="40% - Accent3 4 2 2" xfId="550" xr:uid="{63F4E3EE-39C9-4AEC-84EE-FE80DF08BEEC}"/>
+    <cellStyle name="40% - Accent3 4 2 2 2" xfId="932" xr:uid="{3E7FF664-0890-4CC1-A510-AD21DD6C05EB}"/>
+    <cellStyle name="40% - Accent3 4 2 2 2 2" xfId="2288" xr:uid="{92D7D3E1-9031-4082-B971-A7143CC19C2D}"/>
+    <cellStyle name="40% - Accent3 4 2 2 3" xfId="1317" xr:uid="{D6C280DA-D40A-45F4-86C1-E794259D0B8A}"/>
+    <cellStyle name="40% - Accent3 4 2 2 4" xfId="1908" xr:uid="{585E4675-AA31-4E04-ABDA-47DB06B9ECEF}"/>
+    <cellStyle name="40% - Accent3 4 2 3" xfId="662" xr:uid="{E210B051-B35F-479E-B225-5304D29BC946}"/>
+    <cellStyle name="40% - Accent3 4 2 3 2" xfId="2020" xr:uid="{5C7345F0-61EA-4046-8EC1-0B8FF1CD5259}"/>
+    <cellStyle name="40% - Accent3 4 2 4" xfId="803" xr:uid="{C6B54853-E9B2-4FD7-B3D9-E8BD527E8174}"/>
+    <cellStyle name="40% - Accent3 4 2 4 2" xfId="2161" xr:uid="{1432D0D2-292F-4F18-B0AF-EF74A4831829}"/>
+    <cellStyle name="40% - Accent3 4 2 5" xfId="414" xr:uid="{EDC5B2BC-C9AE-4407-BF3B-E136ADEB270F}"/>
+    <cellStyle name="40% - Accent3 4 2 5 2" xfId="1781" xr:uid="{577D64EC-96BE-4B6E-A6C2-C8C854D6A740}"/>
+    <cellStyle name="40% - Accent3 4 2 6" xfId="1173" xr:uid="{E3ACF047-C61C-429E-8231-E92AB58F9B0C}"/>
+    <cellStyle name="40% - Accent3 4 2 7" xfId="1653" xr:uid="{7A063493-7D2C-4212-8B87-F9D5D9D4BF82}"/>
+    <cellStyle name="40% - Accent3 4 3" xfId="227" xr:uid="{D46DB256-1CDD-4519-9F89-4D46CF5482D9}"/>
+    <cellStyle name="40% - Accent3 4 3 2" xfId="875" xr:uid="{EB570AB9-9C5A-4FF2-BC1B-664556B9FCF9}"/>
+    <cellStyle name="40% - Accent3 4 3 2 2" xfId="2232" xr:uid="{3DF295AB-6668-421C-89DD-EA72CCEF01E8}"/>
+    <cellStyle name="40% - Accent3 4 3 3" xfId="487" xr:uid="{C6934402-7F8B-4143-8067-7570CDE443AF}"/>
+    <cellStyle name="40% - Accent3 4 3 3 2" xfId="1852" xr:uid="{5AAD5E6F-95F1-4AFD-A2B8-657C8E4993AC}"/>
+    <cellStyle name="40% - Accent3 4 3 4" xfId="1117" xr:uid="{59F78EDB-5127-4E2F-8CAA-D0E61D42BAF1}"/>
+    <cellStyle name="40% - Accent3 4 3 5" xfId="1596" xr:uid="{73143FCA-61C5-4FF0-9C1C-452BF9219253}"/>
+    <cellStyle name="40% - Accent3 4 4" xfId="606" xr:uid="{B189C329-DD2C-45C9-90F3-DF87804DDCD5}"/>
+    <cellStyle name="40% - Accent3 4 4 2" xfId="1246" xr:uid="{587176B8-8F01-4710-A314-72D3677C236C}"/>
+    <cellStyle name="40% - Accent3 4 4 3" xfId="1964" xr:uid="{747C51E5-E66D-4007-9717-40708ED2F103}"/>
+    <cellStyle name="40% - Accent3 4 5" xfId="746" xr:uid="{5301904A-2BD1-42C8-B1C8-7443A14BD627}"/>
+    <cellStyle name="40% - Accent3 4 5 2" xfId="2104" xr:uid="{68668670-03E5-4EAA-AF51-579A82A789B5}"/>
+    <cellStyle name="40% - Accent3 4 6" xfId="357" xr:uid="{0C99B62A-717F-4122-85B4-5A91FDA0614E}"/>
+    <cellStyle name="40% - Accent3 4 6 2" xfId="1724" xr:uid="{80303DCB-9D26-4D2C-8535-CD5BE0AF4F58}"/>
+    <cellStyle name="40% - Accent3 4 7" xfId="157" xr:uid="{0758344A-2BDA-48D3-9AD5-B07E3A0CE6F5}"/>
+    <cellStyle name="40% - Accent3 4 7 2" xfId="1526" xr:uid="{C0D4FB6C-C2CF-4E2B-8FC6-6060BD3898DC}"/>
+    <cellStyle name="40% - Accent3 4 8" xfId="1047" xr:uid="{D7E9B8E0-AB7D-4185-8D72-E5919D31CCC2}"/>
+    <cellStyle name="40% - Accent3 4 9" xfId="1456" xr:uid="{532913CB-430A-497A-9AEC-42F1D00076EC}"/>
+    <cellStyle name="40% - Accent3 5" xfId="100" xr:uid="{9F63007A-F116-4D26-BEBE-661A2EFDC11C}"/>
+    <cellStyle name="40% - Accent3 5 2" xfId="243" xr:uid="{340558EC-8538-4B26-8006-8F7331031BC6}"/>
+    <cellStyle name="40% - Accent3 5 2 2" xfId="888" xr:uid="{19739F26-D2A9-4D7B-B697-61310458B98E}"/>
+    <cellStyle name="40% - Accent3 5 2 2 2" xfId="2244" xr:uid="{E193CB35-6BF4-478C-A909-9D89F20A5B4A}"/>
+    <cellStyle name="40% - Accent3 5 2 3" xfId="503" xr:uid="{D61C5681-631B-4FF6-B9C8-A5E0E41D5B16}"/>
+    <cellStyle name="40% - Accent3 5 2 3 2" xfId="1864" xr:uid="{9DBD5DB6-C242-4626-9BF7-45F483148F63}"/>
+    <cellStyle name="40% - Accent3 5 2 4" xfId="1129" xr:uid="{33C408AA-B9F0-4CCC-A8EC-ACE70A0096E4}"/>
+    <cellStyle name="40% - Accent3 5 2 5" xfId="1610" xr:uid="{F6861465-D2E3-4E43-BF36-E257F0649ED3}"/>
+    <cellStyle name="40% - Accent3 5 3" xfId="676" xr:uid="{4B068B8E-161B-4C60-90CE-E7DEF00AE76E}"/>
+    <cellStyle name="40% - Accent3 5 3 2" xfId="1260" xr:uid="{C41132B5-EE3B-4082-A71A-9DBFB0B48DCA}"/>
+    <cellStyle name="40% - Accent3 5 3 3" xfId="2034" xr:uid="{FA8C3D00-0D91-450D-8A48-5E7591E425D8}"/>
+    <cellStyle name="40% - Accent3 5 4" xfId="760" xr:uid="{132AE8CE-5329-4D00-AC30-56BE31F2D4BE}"/>
+    <cellStyle name="40% - Accent3 5 4 2" xfId="2118" xr:uid="{C5466235-BBAE-4AD2-9964-B6A7B270EBA5}"/>
+    <cellStyle name="40% - Accent3 5 5" xfId="371" xr:uid="{2CF7BF0A-2AF4-44E8-8175-3EBF4E7EB5D3}"/>
+    <cellStyle name="40% - Accent3 5 5 2" xfId="1738" xr:uid="{4740AC45-B71E-41CA-9EB8-FE3490A9968E}"/>
+    <cellStyle name="40% - Accent3 5 6" xfId="171" xr:uid="{F875650F-CA7F-4CD9-A145-236BCC118E9E}"/>
+    <cellStyle name="40% - Accent3 5 6 2" xfId="1540" xr:uid="{DDAC4EAD-48BD-4F49-BE56-ED7EE9F0F17D}"/>
+    <cellStyle name="40% - Accent3 5 7" xfId="1061" xr:uid="{62982BB8-858A-4239-87E5-E91C25B8334F}"/>
+    <cellStyle name="40% - Accent3 5 8" xfId="1470" xr:uid="{BA068AA0-EA84-4C18-99B0-BC924C82669C}"/>
+    <cellStyle name="40% - Accent3 6" xfId="183" xr:uid="{CEF383AE-1D58-49DC-8377-6AD21D3913F1}"/>
+    <cellStyle name="40% - Accent3 6 2" xfId="618" xr:uid="{3F5C7C45-998F-4CEA-BF66-E44599466B11}"/>
+    <cellStyle name="40% - Accent3 6 2 2" xfId="1273" xr:uid="{4357E298-BF00-4BD5-9CBE-97E7EFFD3221}"/>
+    <cellStyle name="40% - Accent3 6 2 3" xfId="1976" xr:uid="{409A5E71-1684-4DAD-8418-CAE0E9971BD7}"/>
+    <cellStyle name="40% - Accent3 6 3" xfId="818" xr:uid="{42EF28FA-B8BE-487D-81C7-CA12D18241B9}"/>
+    <cellStyle name="40% - Accent3 6 3 2" xfId="2176" xr:uid="{4DBAA84C-58EB-4709-BF99-5B04A4332EAA}"/>
+    <cellStyle name="40% - Accent3 6 4" xfId="429" xr:uid="{6B85F51B-5A0C-42A2-935C-BE380C411B21}"/>
+    <cellStyle name="40% - Accent3 6 4 2" xfId="1796" xr:uid="{546BEC7F-5AC0-4C19-B815-1AD4DBA82996}"/>
+    <cellStyle name="40% - Accent3 6 5" xfId="1073" xr:uid="{BDD275EA-6BAB-4C6C-AE6A-54BF57C82CC3}"/>
+    <cellStyle name="40% - Accent3 6 6" xfId="1552" xr:uid="{ACFC7C23-5841-48C5-941C-EDECB95636A4}"/>
+    <cellStyle name="40% - Accent3 7" xfId="301" xr:uid="{D018AEAD-833A-47BE-B75A-3158FAE38D1A}"/>
+    <cellStyle name="40% - Accent3 7 2" xfId="690" xr:uid="{B410B143-1D0A-4543-94A4-4236005D1339}"/>
+    <cellStyle name="40% - Accent3 7 2 2" xfId="1331" xr:uid="{32CCF535-1688-44C3-8291-5355D9380812}"/>
+    <cellStyle name="40% - Accent3 7 2 3" xfId="2048" xr:uid="{309BE0CB-A548-4E7E-94D7-5B9EE49944C4}"/>
+    <cellStyle name="40% - Accent3 7 3" xfId="831" xr:uid="{C3985DD5-1776-45B5-BFA8-7A95950CF949}"/>
+    <cellStyle name="40% - Accent3 7 3 2" xfId="2188" xr:uid="{0222AAB9-60E8-45BA-8E5D-68E8274ABF2E}"/>
+    <cellStyle name="40% - Accent3 7 4" xfId="443" xr:uid="{25E857CB-2852-4EB2-80EC-FCD8800CEDCF}"/>
+    <cellStyle name="40% - Accent3 7 4 2" xfId="1808" xr:uid="{BD5CEA0C-7174-46CD-9A61-524B4181FCEA}"/>
+    <cellStyle name="40% - Accent3 7 5" xfId="1187" xr:uid="{D77CEC68-9583-44AA-899C-9463DFAE1FDA}"/>
+    <cellStyle name="40% - Accent3 7 6" xfId="1668" xr:uid="{CE326408-43AB-4B0A-9C0E-6C85FE113FF1}"/>
+    <cellStyle name="40% - Accent3 8" xfId="562" xr:uid="{C7880407-EBAB-4CBB-8418-840E5C211139}"/>
+    <cellStyle name="40% - Accent3 8 2" xfId="1201" xr:uid="{5D57172B-FAF2-4D9D-A5A9-54C9B2E996EF}"/>
+    <cellStyle name="40% - Accent3 8 3" xfId="1920" xr:uid="{C80DD2D9-F34E-4C42-BE4A-2FC8690B0951}"/>
+    <cellStyle name="40% - Accent3 9" xfId="702" xr:uid="{3D7044BC-6EC8-489C-8652-27C5C1140A7E}"/>
+    <cellStyle name="40% - Accent3 9 2" xfId="1345" xr:uid="{E9679425-A459-439A-9EAE-1BBFFD1435BF}"/>
+    <cellStyle name="40% - Accent3 9 3" xfId="2060" xr:uid="{1025C2FD-CDE7-4DBF-AF4C-808C36C86266}"/>
+    <cellStyle name="40% - Accent4" xfId="27" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4 10" xfId="315" xr:uid="{36119959-B9AF-4817-A05C-19009F022058}"/>
+    <cellStyle name="40% - Accent4 10 2" xfId="1361" xr:uid="{F12F0A5C-EF16-4C0C-AC14-E0D16E68AE26}"/>
+    <cellStyle name="40% - Accent4 10 3" xfId="1682" xr:uid="{4227359F-574B-4F15-9584-404C2022BEED}"/>
+    <cellStyle name="40% - Accent4 11" xfId="115" xr:uid="{774E5EB7-68E5-46B6-A45E-30F992047440}"/>
+    <cellStyle name="40% - Accent4 11 2" xfId="1374" xr:uid="{60F7FC18-7DB3-4431-AA12-16A3DAE5CFF0}"/>
+    <cellStyle name="40% - Accent4 11 3" xfId="1484" xr:uid="{EB2E2ADB-A241-4922-AFA4-ED2EE6AB69A5}"/>
+    <cellStyle name="40% - Accent4 12" xfId="948" xr:uid="{67FE34FB-36B7-4EBF-9ECC-7D20CB838894}"/>
+    <cellStyle name="40% - Accent4 12 2" xfId="1387" xr:uid="{7CC5E68E-DAF5-4063-A651-0CEBDC79BF24}"/>
+    <cellStyle name="40% - Accent4 12 3" xfId="2304" xr:uid="{3091BD67-1B1F-4D2C-92C7-566A78062C9C}"/>
+    <cellStyle name="40% - Accent4 13" xfId="962" xr:uid="{52E77C3C-67AD-4723-BF1C-846A88FFD0FD}"/>
+    <cellStyle name="40% - Accent4 13 2" xfId="1401" xr:uid="{A06EA6B9-3222-4E73-ADF8-25D2718D4790}"/>
+    <cellStyle name="40% - Accent4 13 3" xfId="2318" xr:uid="{828B1236-2D7B-4E45-870D-945F661DDF7B}"/>
+    <cellStyle name="40% - Accent4 14" xfId="976" xr:uid="{5D4F1114-565F-4B85-887B-EEB3B11AB549}"/>
+    <cellStyle name="40% - Accent4 14 2" xfId="2332" xr:uid="{1FB65990-B90F-4B9E-BE0C-6539F6B734B9}"/>
+    <cellStyle name="40% - Accent4 15" xfId="992" xr:uid="{67EEE61C-BEA5-45C6-A1E9-D77E9674F5F7}"/>
+    <cellStyle name="40% - Accent4 16" xfId="1005" xr:uid="{5B5815F0-C02E-49A7-B43D-0056FE83AA09}"/>
+    <cellStyle name="40% - Accent4 17" xfId="1414" xr:uid="{10A7B439-3A60-4354-8326-FBF7CFA11C47}"/>
+    <cellStyle name="40% - Accent4 2" xfId="56" xr:uid="{9A96FEE5-3660-42E1-8B95-6646EBB4F378}"/>
+    <cellStyle name="40% - Accent4 2 2" xfId="261" xr:uid="{D3AF3AE5-F183-4EA5-8010-EB258EF00C7C}"/>
+    <cellStyle name="40% - Accent4 2 2 2" xfId="524" xr:uid="{F302BDA9-F984-4276-A4E7-34964EC65A06}"/>
+    <cellStyle name="40% - Accent4 2 2 2 2" xfId="906" xr:uid="{897B919F-BD70-4306-96CF-C56D973578BE}"/>
+    <cellStyle name="40% - Accent4 2 2 2 2 2" xfId="2262" xr:uid="{3E858E54-2F6E-4562-BFC7-4D93498D4FAC}"/>
+    <cellStyle name="40% - Accent4 2 2 2 3" xfId="1291" xr:uid="{D8C914DD-E912-41BA-AA9D-864727F9188C}"/>
+    <cellStyle name="40% - Accent4 2 2 2 4" xfId="1882" xr:uid="{8B2201A6-FFC4-48B8-AE76-2A81A8822EA6}"/>
+    <cellStyle name="40% - Accent4 2 2 3" xfId="636" xr:uid="{1D65651D-893F-4A91-99EF-DF850A97501F}"/>
+    <cellStyle name="40% - Accent4 2 2 3 2" xfId="1994" xr:uid="{CB5410DF-BC8E-4C09-B970-B66631FFC95A}"/>
+    <cellStyle name="40% - Accent4 2 2 4" xfId="778" xr:uid="{89CD9172-DD99-4C49-94BE-AA773396698D}"/>
+    <cellStyle name="40% - Accent4 2 2 4 2" xfId="2136" xr:uid="{3D03AC8B-81A1-464B-874E-DD588499D197}"/>
+    <cellStyle name="40% - Accent4 2 2 5" xfId="389" xr:uid="{94129D4B-6910-4DC0-919A-9CA653651C37}"/>
+    <cellStyle name="40% - Accent4 2 2 5 2" xfId="1756" xr:uid="{CD9E21A7-A30D-4C0B-902C-DF6E0194A78A}"/>
+    <cellStyle name="40% - Accent4 2 2 6" xfId="1147" xr:uid="{856D431E-F6E5-45FB-B3DB-D8D42B7AB653}"/>
+    <cellStyle name="40% - Accent4 2 2 7" xfId="1628" xr:uid="{92B5F418-ECED-44E3-B09D-D28D3AB26947}"/>
+    <cellStyle name="40% - Accent4 2 3" xfId="201" xr:uid="{A735B584-75F1-42F7-A50A-085EB50D39F2}"/>
+    <cellStyle name="40% - Accent4 2 3 2" xfId="849" xr:uid="{A498FEF5-10A6-44E5-9304-5AC675D3B743}"/>
+    <cellStyle name="40% - Accent4 2 3 2 2" xfId="2206" xr:uid="{2EF38E89-CEBB-415E-BCBC-E850EFB21DC8}"/>
+    <cellStyle name="40% - Accent4 2 3 3" xfId="461" xr:uid="{D025308D-55A0-4BB7-8F76-C06FD9DEA1F8}"/>
+    <cellStyle name="40% - Accent4 2 3 3 2" xfId="1826" xr:uid="{19397614-7BBB-43EF-BB6F-E00E136B71C6}"/>
+    <cellStyle name="40% - Accent4 2 3 4" xfId="1091" xr:uid="{896E0E40-AAC6-4165-AC4E-C1D0B8EB8390}"/>
+    <cellStyle name="40% - Accent4 2 3 5" xfId="1570" xr:uid="{7F1108A5-5EA5-41FE-91A3-1FF467A8F2A5}"/>
+    <cellStyle name="40% - Accent4 2 4" xfId="580" xr:uid="{15378BD9-731E-4F23-9418-C935134000E6}"/>
+    <cellStyle name="40% - Accent4 2 4 2" xfId="1220" xr:uid="{DCF8F735-A28D-450B-A5FF-D89FD571E9DE}"/>
+    <cellStyle name="40% - Accent4 2 4 3" xfId="1938" xr:uid="{A0E59B33-A49C-462A-8A44-C000854CE20A}"/>
+    <cellStyle name="40% - Accent4 2 5" xfId="720" xr:uid="{08B5530C-8105-473F-A518-A4E0C7F57B94}"/>
+    <cellStyle name="40% - Accent4 2 5 2" xfId="2078" xr:uid="{0337F36E-958A-4ED8-AD4C-7ECDFCE89E11}"/>
+    <cellStyle name="40% - Accent4 2 6" xfId="331" xr:uid="{59B90D56-495E-48C5-8B94-CFABE13C8F92}"/>
+    <cellStyle name="40% - Accent4 2 6 2" xfId="1698" xr:uid="{FD3EED4D-896D-4334-AB74-A605B2FFD03A}"/>
+    <cellStyle name="40% - Accent4 2 7" xfId="131" xr:uid="{323AC3BF-3CEE-48C7-8C16-7FADB5F0407F}"/>
+    <cellStyle name="40% - Accent4 2 7 2" xfId="1500" xr:uid="{9A07660D-2983-4A0C-B398-ACFD0FD1396E}"/>
+    <cellStyle name="40% - Accent4 2 8" xfId="1021" xr:uid="{0DE06EA3-3154-4CD8-9E15-E5026DCADDEB}"/>
+    <cellStyle name="40% - Accent4 2 9" xfId="1430" xr:uid="{CF6250BA-CADF-47F7-976B-73D945256FFB}"/>
+    <cellStyle name="40% - Accent4 3" xfId="74" xr:uid="{5F570F35-43AF-40C1-8B82-36498D85C07D}"/>
+    <cellStyle name="40% - Accent4 3 2" xfId="275" xr:uid="{2DF02F0D-0330-4934-A2FA-56CBAC99ECA2}"/>
+    <cellStyle name="40% - Accent4 3 2 2" xfId="538" xr:uid="{5AA99638-E254-4C2D-BB6A-4920A5F2E25A}"/>
+    <cellStyle name="40% - Accent4 3 2 2 2" xfId="920" xr:uid="{72F055C7-FCAA-4300-A498-50FAACE1A0C3}"/>
+    <cellStyle name="40% - Accent4 3 2 2 2 2" xfId="2276" xr:uid="{1B95E5A6-BF87-4939-AB94-6FE5F36B0023}"/>
+    <cellStyle name="40% - Accent4 3 2 2 3" xfId="1305" xr:uid="{6035A55A-F301-4D72-A1B0-F379D97F8715}"/>
+    <cellStyle name="40% - Accent4 3 2 2 4" xfId="1896" xr:uid="{E49B2741-D6B2-49EE-9C08-3567CB31AA4A}"/>
+    <cellStyle name="40% - Accent4 3 2 3" xfId="650" xr:uid="{271DBF0E-44CE-47C9-B76A-55DFF83E39C2}"/>
+    <cellStyle name="40% - Accent4 3 2 3 2" xfId="2008" xr:uid="{DCFCDFB7-8BEB-4617-8328-C790F55BFB6F}"/>
+    <cellStyle name="40% - Accent4 3 2 4" xfId="792" xr:uid="{2757D41F-0451-4C2B-801F-8582AAADE84C}"/>
+    <cellStyle name="40% - Accent4 3 2 4 2" xfId="2150" xr:uid="{5420211E-D39A-4BFB-9E4C-6D515208B68A}"/>
+    <cellStyle name="40% - Accent4 3 2 5" xfId="403" xr:uid="{A62F6706-8391-4D11-9AF0-CCEC2D3654FD}"/>
+    <cellStyle name="40% - Accent4 3 2 5 2" xfId="1770" xr:uid="{821ECDE9-A80C-494E-B4B0-EBD6F6CC3276}"/>
+    <cellStyle name="40% - Accent4 3 2 6" xfId="1161" xr:uid="{E862F4CF-9E4D-4A56-A1F7-F6F1AAC6044B}"/>
+    <cellStyle name="40% - Accent4 3 2 7" xfId="1642" xr:uid="{F97CF508-77BE-4932-BE99-A24B76E6C235}"/>
+    <cellStyle name="40% - Accent4 3 3" xfId="215" xr:uid="{42CA9693-80E2-434A-A483-FD9C24EEAD2B}"/>
+    <cellStyle name="40% - Accent4 3 3 2" xfId="863" xr:uid="{A891D394-813A-4BA2-928B-728CF48DAADF}"/>
+    <cellStyle name="40% - Accent4 3 3 2 2" xfId="2220" xr:uid="{D44D2896-A288-4F0C-A41B-564D3DFD968F}"/>
+    <cellStyle name="40% - Accent4 3 3 3" xfId="475" xr:uid="{53A24B83-B7C7-442A-8522-96F8CF33A081}"/>
+    <cellStyle name="40% - Accent4 3 3 3 2" xfId="1840" xr:uid="{DA981B92-56C0-4A99-94A8-C7B40913BC61}"/>
+    <cellStyle name="40% - Accent4 3 3 4" xfId="1105" xr:uid="{05F6DD6D-8A19-472D-AA14-001AC603BD18}"/>
+    <cellStyle name="40% - Accent4 3 3 5" xfId="1584" xr:uid="{251EE80D-9D0D-4704-BDDA-941F5C615E2E}"/>
+    <cellStyle name="40% - Accent4 3 4" xfId="594" xr:uid="{3A45E27D-BA7A-4939-8603-E453529EAF2D}"/>
+    <cellStyle name="40% - Accent4 3 4 2" xfId="1234" xr:uid="{D02542DC-86AB-49C0-9606-47C8ECDEEC6D}"/>
+    <cellStyle name="40% - Accent4 3 4 3" xfId="1952" xr:uid="{0EF76F9C-3A9A-4489-BD0A-CB217FB5E0B2}"/>
+    <cellStyle name="40% - Accent4 3 5" xfId="734" xr:uid="{4A891AE0-ADC8-46E0-8FC1-179F7D5D81C1}"/>
+    <cellStyle name="40% - Accent4 3 5 2" xfId="2092" xr:uid="{89285778-04E6-4C94-8493-AC7ABA03491A}"/>
+    <cellStyle name="40% - Accent4 3 6" xfId="345" xr:uid="{B7ACD236-7C1D-473E-A950-B06633AA54A9}"/>
+    <cellStyle name="40% - Accent4 3 6 2" xfId="1712" xr:uid="{01BBC0C5-B441-41B3-936C-7117ABF7BD96}"/>
+    <cellStyle name="40% - Accent4 3 7" xfId="145" xr:uid="{10D49918-55CD-4B24-BDA3-B099B16BB2C0}"/>
+    <cellStyle name="40% - Accent4 3 7 2" xfId="1514" xr:uid="{00AB1566-05AB-4FA1-A25B-BD868F1CCD16}"/>
+    <cellStyle name="40% - Accent4 3 8" xfId="1035" xr:uid="{E5A90C3C-08E5-400A-B9CB-AB03CCC0D3ED}"/>
+    <cellStyle name="40% - Accent4 3 9" xfId="1444" xr:uid="{B25887FE-5F6A-4267-8375-14B29108EB53}"/>
+    <cellStyle name="40% - Accent4 4" xfId="88" xr:uid="{569393C8-B6E5-4C79-8E04-5CE08096F669}"/>
+    <cellStyle name="40% - Accent4 4 2" xfId="288" xr:uid="{181CE641-9095-4387-88C6-65DD1F5D23F4}"/>
+    <cellStyle name="40% - Accent4 4 2 2" xfId="552" xr:uid="{59639F29-968C-4C66-AA41-7016FE0C9890}"/>
+    <cellStyle name="40% - Accent4 4 2 2 2" xfId="934" xr:uid="{3A37D52B-5C66-4557-967A-07658ABDA257}"/>
+    <cellStyle name="40% - Accent4 4 2 2 2 2" xfId="2290" xr:uid="{4E9CC709-9A1A-4F0A-BAEC-A63BD6F375FE}"/>
+    <cellStyle name="40% - Accent4 4 2 2 3" xfId="1319" xr:uid="{7A17A2B7-A075-4EC2-9F57-36C3076E2099}"/>
+    <cellStyle name="40% - Accent4 4 2 2 4" xfId="1910" xr:uid="{F15A8FE8-A4F0-4377-B07E-D28A3BF08F42}"/>
+    <cellStyle name="40% - Accent4 4 2 3" xfId="664" xr:uid="{420BDE7F-1035-4473-AFA7-3EE5105226F0}"/>
+    <cellStyle name="40% - Accent4 4 2 3 2" xfId="2022" xr:uid="{82FFA90B-5D8D-4C94-AECF-ECF7892D1FE0}"/>
+    <cellStyle name="40% - Accent4 4 2 4" xfId="805" xr:uid="{08062A8D-3DA2-401F-A392-9BB545668B4F}"/>
+    <cellStyle name="40% - Accent4 4 2 4 2" xfId="2163" xr:uid="{F61C6C30-C00B-481E-B0B8-67802E4A92E5}"/>
+    <cellStyle name="40% - Accent4 4 2 5" xfId="416" xr:uid="{921EAD1B-3442-4172-97EF-8596D58D3806}"/>
+    <cellStyle name="40% - Accent4 4 2 5 2" xfId="1783" xr:uid="{68D4CC18-5035-4E94-AC2A-EC4CF2D8B3D8}"/>
+    <cellStyle name="40% - Accent4 4 2 6" xfId="1175" xr:uid="{371E46B0-DA47-49A1-8C0A-820272D42420}"/>
+    <cellStyle name="40% - Accent4 4 2 7" xfId="1655" xr:uid="{79098A8A-5E31-4A58-BF60-57162BEE06A6}"/>
+    <cellStyle name="40% - Accent4 4 3" xfId="229" xr:uid="{0FD2C6A7-8B7F-4F5A-8693-5D5ADB256976}"/>
+    <cellStyle name="40% - Accent4 4 3 2" xfId="877" xr:uid="{57E6B0FB-E1DB-4874-8544-5B91FCC5966D}"/>
+    <cellStyle name="40% - Accent4 4 3 2 2" xfId="2234" xr:uid="{6D753555-F8C6-45BD-81A9-878D302DC564}"/>
+    <cellStyle name="40% - Accent4 4 3 3" xfId="489" xr:uid="{B7CE46AD-FC38-4163-B98F-47B880BF4766}"/>
+    <cellStyle name="40% - Accent4 4 3 3 2" xfId="1854" xr:uid="{9B2EF07E-DCEE-407C-A277-EAA6B3059205}"/>
+    <cellStyle name="40% - Accent4 4 3 4" xfId="1119" xr:uid="{A9485BE8-068A-4803-AE46-F02F546501B3}"/>
+    <cellStyle name="40% - Accent4 4 3 5" xfId="1598" xr:uid="{43784621-3383-47CB-B6D7-8918FDD473D6}"/>
+    <cellStyle name="40% - Accent4 4 4" xfId="608" xr:uid="{7B01C4D2-C9E4-4482-B6C9-96509232C168}"/>
+    <cellStyle name="40% - Accent4 4 4 2" xfId="1248" xr:uid="{C3A1DF86-B802-46FA-8119-BF1DD210AF88}"/>
+    <cellStyle name="40% - Accent4 4 4 3" xfId="1966" xr:uid="{23D73C39-A0C1-4324-8EF1-0021BF3977A5}"/>
+    <cellStyle name="40% - Accent4 4 5" xfId="748" xr:uid="{B2C4D752-9C3A-4050-971E-11D54B063A7C}"/>
+    <cellStyle name="40% - Accent4 4 5 2" xfId="2106" xr:uid="{21230A82-23A6-4260-B11E-938420954E02}"/>
+    <cellStyle name="40% - Accent4 4 6" xfId="359" xr:uid="{819DB022-F532-4BF0-9B22-526B810DDBD4}"/>
+    <cellStyle name="40% - Accent4 4 6 2" xfId="1726" xr:uid="{55236189-4C3D-4BE1-ABC9-C1F77A003507}"/>
+    <cellStyle name="40% - Accent4 4 7" xfId="159" xr:uid="{76B2C578-C4B7-453E-A5FD-0420C09C6CE8}"/>
+    <cellStyle name="40% - Accent4 4 7 2" xfId="1528" xr:uid="{DD729D70-11BD-4898-975C-AFB025C85B36}"/>
+    <cellStyle name="40% - Accent4 4 8" xfId="1049" xr:uid="{4D6DA17F-354E-4B30-AA90-D398B62B16D9}"/>
+    <cellStyle name="40% - Accent4 4 9" xfId="1458" xr:uid="{AF4618EB-F3C4-45A7-A52D-B6747B23CCA4}"/>
+    <cellStyle name="40% - Accent4 5" xfId="102" xr:uid="{F7BAE0F6-260C-4D6B-8CDF-F21103EDE61B}"/>
+    <cellStyle name="40% - Accent4 5 2" xfId="245" xr:uid="{D0966528-6A22-4AE8-BFC0-92CF5E22D204}"/>
+    <cellStyle name="40% - Accent4 5 2 2" xfId="890" xr:uid="{BC7612EC-5F37-4E5B-9E95-C0B6A4C60A0B}"/>
+    <cellStyle name="40% - Accent4 5 2 2 2" xfId="2246" xr:uid="{EC7A7BA5-0F4E-40B5-9C29-27ED9FA98E03}"/>
+    <cellStyle name="40% - Accent4 5 2 3" xfId="505" xr:uid="{F5E50D68-3385-491B-B087-B569CA0A9193}"/>
+    <cellStyle name="40% - Accent4 5 2 3 2" xfId="1866" xr:uid="{0421AF33-8EB5-4DD4-8B51-C7FBE5858CFF}"/>
+    <cellStyle name="40% - Accent4 5 2 4" xfId="1131" xr:uid="{9BE0F67D-9B6B-42C7-915E-6948F6920C9A}"/>
+    <cellStyle name="40% - Accent4 5 2 5" xfId="1612" xr:uid="{B487EBFC-3E81-4349-9D8E-A49881EA96E6}"/>
+    <cellStyle name="40% - Accent4 5 3" xfId="678" xr:uid="{459DB9DE-93A8-47A0-83E9-0090B36AF263}"/>
+    <cellStyle name="40% - Accent4 5 3 2" xfId="1262" xr:uid="{1339AAF9-0C30-4443-B330-10C484B852B0}"/>
+    <cellStyle name="40% - Accent4 5 3 3" xfId="2036" xr:uid="{733F6EDC-F282-4611-8B16-885296E6F6C1}"/>
+    <cellStyle name="40% - Accent4 5 4" xfId="762" xr:uid="{6AF91128-6D10-4878-A2D5-BEFE2FEBB333}"/>
+    <cellStyle name="40% - Accent4 5 4 2" xfId="2120" xr:uid="{0B016915-6E11-471C-A05B-DC3C32E0680B}"/>
+    <cellStyle name="40% - Accent4 5 5" xfId="373" xr:uid="{8008782F-8D26-4151-8065-10040B20A9A2}"/>
+    <cellStyle name="40% - Accent4 5 5 2" xfId="1740" xr:uid="{B7ED219C-00E6-42D4-AC96-7F20D282B9F4}"/>
+    <cellStyle name="40% - Accent4 5 6" xfId="173" xr:uid="{3EFA1A99-019B-4019-A65E-7946BF6CDEBD}"/>
+    <cellStyle name="40% - Accent4 5 6 2" xfId="1542" xr:uid="{8EE89AC5-BE7B-4850-91B1-2EDF92E56380}"/>
+    <cellStyle name="40% - Accent4 5 7" xfId="1063" xr:uid="{83EBFE62-5C91-4E55-83D8-71A9CF7C9FE1}"/>
+    <cellStyle name="40% - Accent4 5 8" xfId="1472" xr:uid="{8B6F1371-9090-49BF-9E90-11B1CDCBBE8C}"/>
+    <cellStyle name="40% - Accent4 6" xfId="185" xr:uid="{0E775C2A-717C-4980-B121-8D6A1E17033D}"/>
+    <cellStyle name="40% - Accent4 6 2" xfId="620" xr:uid="{8CF0538D-C178-4ED9-AD66-8A3C6B77C63B}"/>
+    <cellStyle name="40% - Accent4 6 2 2" xfId="1275" xr:uid="{FF78244A-9512-491E-8652-5096140E888E}"/>
+    <cellStyle name="40% - Accent4 6 2 3" xfId="1978" xr:uid="{C72BE292-2D22-400A-B887-ED26AADC1C28}"/>
+    <cellStyle name="40% - Accent4 6 3" xfId="820" xr:uid="{B4C8480F-C65B-42ED-8149-C576ED75593D}"/>
+    <cellStyle name="40% - Accent4 6 3 2" xfId="2178" xr:uid="{E3CA4CD0-919F-4517-ABE5-8BB059578348}"/>
+    <cellStyle name="40% - Accent4 6 4" xfId="431" xr:uid="{EBE48144-F3FD-4209-9777-B4E46549926E}"/>
+    <cellStyle name="40% - Accent4 6 4 2" xfId="1798" xr:uid="{DEA2688B-4F59-4EB2-B215-B1FD2B73E7CA}"/>
+    <cellStyle name="40% - Accent4 6 5" xfId="1075" xr:uid="{D9EDE02A-3EF4-481A-897C-39B332A3F041}"/>
+    <cellStyle name="40% - Accent4 6 6" xfId="1554" xr:uid="{E702ACC8-88C8-459C-B4CB-84D34E6A8A5D}"/>
+    <cellStyle name="40% - Accent4 7" xfId="303" xr:uid="{785D2F74-C2AA-4635-BC36-25E327E12F1A}"/>
+    <cellStyle name="40% - Accent4 7 2" xfId="692" xr:uid="{6552D11F-030A-4B32-84E1-1D133730E3EF}"/>
+    <cellStyle name="40% - Accent4 7 2 2" xfId="1333" xr:uid="{D9F1669E-2B6B-4F47-AB6E-989CC6DD7633}"/>
+    <cellStyle name="40% - Accent4 7 2 3" xfId="2050" xr:uid="{16EC1910-65E1-43A9-9954-AE8383F3E1BB}"/>
+    <cellStyle name="40% - Accent4 7 3" xfId="833" xr:uid="{68EC1F32-565B-4FBF-9571-6AA198D9411E}"/>
+    <cellStyle name="40% - Accent4 7 3 2" xfId="2190" xr:uid="{A6B9F320-6D17-4B56-920B-7D64CB25A71F}"/>
+    <cellStyle name="40% - Accent4 7 4" xfId="445" xr:uid="{E2E199E5-30EB-4A7B-8432-B771D2F86D28}"/>
+    <cellStyle name="40% - Accent4 7 4 2" xfId="1810" xr:uid="{CD6EDC54-0D27-4AF9-A584-FED675476F91}"/>
+    <cellStyle name="40% - Accent4 7 5" xfId="1189" xr:uid="{426A3ABF-93FD-4163-819F-0EFFCED935F3}"/>
+    <cellStyle name="40% - Accent4 7 6" xfId="1670" xr:uid="{2A920DB6-1054-4849-9C79-0C7A6080C2F9}"/>
+    <cellStyle name="40% - Accent4 8" xfId="564" xr:uid="{98B27455-140E-4331-AF7B-799D6A89B741}"/>
+    <cellStyle name="40% - Accent4 8 2" xfId="1203" xr:uid="{5649C922-5D4C-4922-878B-5F1CD9DB7054}"/>
+    <cellStyle name="40% - Accent4 8 3" xfId="1922" xr:uid="{57167BEA-B120-4EEE-8F00-3CE19EF5B462}"/>
+    <cellStyle name="40% - Accent4 9" xfId="704" xr:uid="{254FA120-6CCB-494A-AF55-C9BEDA01396F}"/>
+    <cellStyle name="40% - Accent4 9 2" xfId="1347" xr:uid="{56D6CB2A-2AAE-4CC1-9DE1-63832494EBB3}"/>
+    <cellStyle name="40% - Accent4 9 3" xfId="2062" xr:uid="{1E61A7AA-DD7E-4D9A-AEFA-D2B48124A102}"/>
+    <cellStyle name="40% - Accent5" xfId="30" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5 10" xfId="317" xr:uid="{4F06E12C-BB3E-4FDF-89BB-5BDE2FAA8E4A}"/>
+    <cellStyle name="40% - Accent5 10 2" xfId="1363" xr:uid="{B7ABD8F3-91A3-43E7-A299-4FC143EC6F4E}"/>
+    <cellStyle name="40% - Accent5 10 3" xfId="1684" xr:uid="{7AB5DC7C-792F-4B8F-9F38-1BCFD916BCDB}"/>
+    <cellStyle name="40% - Accent5 11" xfId="117" xr:uid="{340309BD-1193-4246-87BF-1C027E1DC7BF}"/>
+    <cellStyle name="40% - Accent5 11 2" xfId="1376" xr:uid="{081DB921-427C-4195-9E71-8AE448ECF3BA}"/>
+    <cellStyle name="40% - Accent5 11 3" xfId="1486" xr:uid="{C32D6DFE-E6BD-4802-800F-83A52B164566}"/>
+    <cellStyle name="40% - Accent5 12" xfId="950" xr:uid="{3AB2DAC1-2C34-4A04-BF15-EA1641EC5095}"/>
+    <cellStyle name="40% - Accent5 12 2" xfId="1389" xr:uid="{F3887390-3109-4ECC-94D9-1E68891CEF81}"/>
+    <cellStyle name="40% - Accent5 12 3" xfId="2306" xr:uid="{25B4726D-1019-4D8C-9393-361BF8D0C68E}"/>
+    <cellStyle name="40% - Accent5 13" xfId="964" xr:uid="{9A8FAC34-A0E7-4474-8B43-83918ACDE677}"/>
+    <cellStyle name="40% - Accent5 13 2" xfId="1403" xr:uid="{085E33B8-8F33-412F-8F41-6BF28BB01947}"/>
+    <cellStyle name="40% - Accent5 13 3" xfId="2320" xr:uid="{9EDB3B6E-A8CE-4A2B-9924-890C09C714F0}"/>
+    <cellStyle name="40% - Accent5 14" xfId="978" xr:uid="{6DDB5AE1-B73F-4BBE-9043-FA7217B0A823}"/>
+    <cellStyle name="40% - Accent5 14 2" xfId="2334" xr:uid="{747421F2-922D-4808-BCAC-32877B546399}"/>
+    <cellStyle name="40% - Accent5 15" xfId="994" xr:uid="{CFDBC1DD-A6AD-4F48-B3CE-C21E18A96073}"/>
+    <cellStyle name="40% - Accent5 16" xfId="1007" xr:uid="{635CF0AA-FE46-4359-B937-4B3C0620CC97}"/>
+    <cellStyle name="40% - Accent5 17" xfId="1416" xr:uid="{DA119D86-96B7-4BF9-8AEC-DB6CC002AA25}"/>
+    <cellStyle name="40% - Accent5 2" xfId="58" xr:uid="{754F9F17-B7CC-4BA9-908E-30BFD9DD7C00}"/>
+    <cellStyle name="40% - Accent5 2 2" xfId="263" xr:uid="{4EAF2EC4-435E-488E-B9A9-3D4CE565D354}"/>
+    <cellStyle name="40% - Accent5 2 2 2" xfId="526" xr:uid="{C8029C8B-A547-4D2C-B855-85A2072CB54D}"/>
+    <cellStyle name="40% - Accent5 2 2 2 2" xfId="908" xr:uid="{7CB266D2-84B2-4884-AB02-06FC2B75F621}"/>
+    <cellStyle name="40% - Accent5 2 2 2 2 2" xfId="2264" xr:uid="{C89739E2-26FC-463D-A518-00543CC27733}"/>
+    <cellStyle name="40% - Accent5 2 2 2 3" xfId="1293" xr:uid="{1F140995-7EB9-435D-9956-C8B996C4B210}"/>
+    <cellStyle name="40% - Accent5 2 2 2 4" xfId="1884" xr:uid="{D53E382C-5AD2-4C21-BD89-998EC2A773BD}"/>
+    <cellStyle name="40% - Accent5 2 2 3" xfId="638" xr:uid="{5E6FF570-B1E6-43FF-B818-F4543003C6AA}"/>
+    <cellStyle name="40% - Accent5 2 2 3 2" xfId="1996" xr:uid="{ABE46C43-B018-44EB-B8FB-B0BB76F4FC0A}"/>
+    <cellStyle name="40% - Accent5 2 2 4" xfId="780" xr:uid="{729C3CD3-B002-4289-B08F-EF80DD77361F}"/>
+    <cellStyle name="40% - Accent5 2 2 4 2" xfId="2138" xr:uid="{FDDD0D7A-DFBC-4668-AD5E-1C69FD235C5E}"/>
+    <cellStyle name="40% - Accent5 2 2 5" xfId="391" xr:uid="{A9C27056-EB91-4B78-A3D3-D4BDDFD8E7DF}"/>
+    <cellStyle name="40% - Accent5 2 2 5 2" xfId="1758" xr:uid="{A18EEE19-717F-4058-B6FA-234CFDDC7CB2}"/>
+    <cellStyle name="40% - Accent5 2 2 6" xfId="1149" xr:uid="{0FD540F0-05B8-44EA-8F12-AB2CE597F4EB}"/>
+    <cellStyle name="40% - Accent5 2 2 7" xfId="1630" xr:uid="{3D1CB840-ADC6-40CE-B208-5B6050118EA7}"/>
+    <cellStyle name="40% - Accent5 2 3" xfId="203" xr:uid="{75A5A74F-F8A2-4FEE-BF1C-F3034A12AC09}"/>
+    <cellStyle name="40% - Accent5 2 3 2" xfId="851" xr:uid="{9CD955D2-A647-4262-BFD7-A7E44FD16C13}"/>
+    <cellStyle name="40% - Accent5 2 3 2 2" xfId="2208" xr:uid="{60D9943D-3C7B-4210-8F66-F587D50A95C0}"/>
+    <cellStyle name="40% - Accent5 2 3 3" xfId="463" xr:uid="{E83A6E07-7D2D-4A56-B583-58B0158CF547}"/>
+    <cellStyle name="40% - Accent5 2 3 3 2" xfId="1828" xr:uid="{2C82A210-0994-4E0A-92D0-B305208DC118}"/>
+    <cellStyle name="40% - Accent5 2 3 4" xfId="1093" xr:uid="{777DBE60-6D5B-410F-8E33-B97D64701B8D}"/>
+    <cellStyle name="40% - Accent5 2 3 5" xfId="1572" xr:uid="{28869A06-D656-497F-86FB-EC19053FECE3}"/>
+    <cellStyle name="40% - Accent5 2 4" xfId="582" xr:uid="{FFBF6E8F-9474-4C88-8DD0-BB2BADA6A081}"/>
+    <cellStyle name="40% - Accent5 2 4 2" xfId="1222" xr:uid="{600EEBCB-79F8-4C7C-99F8-4B4599817434}"/>
+    <cellStyle name="40% - Accent5 2 4 3" xfId="1940" xr:uid="{2523F8B8-08EC-4E8E-AD65-68253AF2DCFB}"/>
+    <cellStyle name="40% - Accent5 2 5" xfId="722" xr:uid="{70FE8263-91FC-4BA0-AEA1-1A6D09D30A27}"/>
+    <cellStyle name="40% - Accent5 2 5 2" xfId="2080" xr:uid="{5F246B8F-76A7-49EA-8FA8-F26682999EB7}"/>
+    <cellStyle name="40% - Accent5 2 6" xfId="333" xr:uid="{76D8DCAB-4278-4495-A683-FA987D86B137}"/>
+    <cellStyle name="40% - Accent5 2 6 2" xfId="1700" xr:uid="{DD29F896-0C93-4AA7-AAA5-9EEA83410EE7}"/>
+    <cellStyle name="40% - Accent5 2 7" xfId="133" xr:uid="{90FE4897-CB57-471B-92B4-FB4B10FA51F0}"/>
+    <cellStyle name="40% - Accent5 2 7 2" xfId="1502" xr:uid="{4A8BABDE-590C-42F0-88DC-E27F8D17EDC3}"/>
+    <cellStyle name="40% - Accent5 2 8" xfId="1023" xr:uid="{721FDEB8-0ABD-49BD-8619-52C76CD36F68}"/>
+    <cellStyle name="40% - Accent5 2 9" xfId="1432" xr:uid="{A4DD3EF8-7B18-4538-8F20-C3B1CC8B22F6}"/>
+    <cellStyle name="40% - Accent5 3" xfId="76" xr:uid="{21886709-EF24-49AB-88E4-E76B7511D69A}"/>
+    <cellStyle name="40% - Accent5 3 2" xfId="277" xr:uid="{A691D507-DF68-40DB-AF6A-189A3018B3AD}"/>
+    <cellStyle name="40% - Accent5 3 2 2" xfId="540" xr:uid="{78CC5283-FA69-4ECA-889B-5C9E7548AA9C}"/>
+    <cellStyle name="40% - Accent5 3 2 2 2" xfId="922" xr:uid="{72CF884B-BDFF-4548-BB71-09449E0596D9}"/>
+    <cellStyle name="40% - Accent5 3 2 2 2 2" xfId="2278" xr:uid="{25EEFAB3-5E18-4A2C-9BD6-0EDB36327D05}"/>
+    <cellStyle name="40% - Accent5 3 2 2 3" xfId="1307" xr:uid="{A061B281-D863-40DD-A9EA-CB5D58D03E9C}"/>
+    <cellStyle name="40% - Accent5 3 2 2 4" xfId="1898" xr:uid="{2F025F83-3C4A-4E64-B678-F56E075C5880}"/>
+    <cellStyle name="40% - Accent5 3 2 3" xfId="652" xr:uid="{BA53E297-4FD8-42EB-9F79-218DC5A9B4C0}"/>
+    <cellStyle name="40% - Accent5 3 2 3 2" xfId="2010" xr:uid="{D50A4B85-2D25-4B19-9853-889577DA3396}"/>
+    <cellStyle name="40% - Accent5 3 2 4" xfId="794" xr:uid="{D50589AD-AB00-47FC-A6BD-DDCA380E060E}"/>
+    <cellStyle name="40% - Accent5 3 2 4 2" xfId="2152" xr:uid="{CF2B4E91-91E5-4B37-9638-6C6A08F4B6CF}"/>
+    <cellStyle name="40% - Accent5 3 2 5" xfId="405" xr:uid="{6AA9C150-EBCD-46DE-9FBD-533A5138FA60}"/>
+    <cellStyle name="40% - Accent5 3 2 5 2" xfId="1772" xr:uid="{E5B31CD9-FC97-411F-A38D-C9FBCAF2C2E9}"/>
+    <cellStyle name="40% - Accent5 3 2 6" xfId="1163" xr:uid="{06447722-AC65-4F2B-B74C-100BB8204FC0}"/>
+    <cellStyle name="40% - Accent5 3 2 7" xfId="1644" xr:uid="{3AA0F40A-691A-4B92-8707-6A4C1578C988}"/>
+    <cellStyle name="40% - Accent5 3 3" xfId="217" xr:uid="{A2130AB9-66F4-4A0E-8193-1CAB8E1553A7}"/>
+    <cellStyle name="40% - Accent5 3 3 2" xfId="865" xr:uid="{7C35CB6D-21DD-4FEA-94B9-F9BB98B84C19}"/>
+    <cellStyle name="40% - Accent5 3 3 2 2" xfId="2222" xr:uid="{4BCC4721-4989-4DA0-8969-0A7C645322B2}"/>
+    <cellStyle name="40% - Accent5 3 3 3" xfId="477" xr:uid="{80795F1A-E2AB-41D6-AE03-F05348B6D2FC}"/>
+    <cellStyle name="40% - Accent5 3 3 3 2" xfId="1842" xr:uid="{C26C1B4A-A8E1-4AF6-9216-9A5B370D9E98}"/>
+    <cellStyle name="40% - Accent5 3 3 4" xfId="1107" xr:uid="{AAF1BDD1-56F7-4E59-85FB-1CE514F8B189}"/>
+    <cellStyle name="40% - Accent5 3 3 5" xfId="1586" xr:uid="{8D90F28C-8D6A-4279-8901-2F62662F8635}"/>
+    <cellStyle name="40% - Accent5 3 4" xfId="596" xr:uid="{7B6DD0E4-1045-4C96-8BFA-6E3E9E607BC9}"/>
+    <cellStyle name="40% - Accent5 3 4 2" xfId="1236" xr:uid="{588A3CF1-D9C1-4D57-BEDA-4012A71A8B70}"/>
+    <cellStyle name="40% - Accent5 3 4 3" xfId="1954" xr:uid="{CD0A6627-4455-417B-8D3F-11BD13C4828E}"/>
+    <cellStyle name="40% - Accent5 3 5" xfId="736" xr:uid="{0E2B3BD6-33D3-4A74-9C86-B66537D27E83}"/>
+    <cellStyle name="40% - Accent5 3 5 2" xfId="2094" xr:uid="{CB8B0341-2878-4432-8CBC-0EF4B0CB50B9}"/>
+    <cellStyle name="40% - Accent5 3 6" xfId="347" xr:uid="{719B5EEA-EA12-445B-98B2-1B64EAAA6A68}"/>
+    <cellStyle name="40% - Accent5 3 6 2" xfId="1714" xr:uid="{960BDE8B-AAD3-4C9B-A109-1E1B5BDCFFD3}"/>
+    <cellStyle name="40% - Accent5 3 7" xfId="147" xr:uid="{1C1DAC25-23CC-43D3-ABFB-22FE802F2692}"/>
+    <cellStyle name="40% - Accent5 3 7 2" xfId="1516" xr:uid="{ABA3B060-F685-4239-9EC2-FA42A1A53B27}"/>
+    <cellStyle name="40% - Accent5 3 8" xfId="1037" xr:uid="{54F9A91C-2719-474E-A422-86830E9A7CDA}"/>
+    <cellStyle name="40% - Accent5 3 9" xfId="1446" xr:uid="{57FEA3DF-0D9A-45DD-9853-317596B20FB7}"/>
+    <cellStyle name="40% - Accent5 4" xfId="90" xr:uid="{CDFE90C8-97B6-4B79-B48E-8A8BB6BD2BDB}"/>
+    <cellStyle name="40% - Accent5 4 2" xfId="290" xr:uid="{3F593594-F04E-454F-AC94-83C035FEED3F}"/>
+    <cellStyle name="40% - Accent5 4 2 2" xfId="554" xr:uid="{5BD4008D-24DB-490E-97C2-94F732A975D1}"/>
+    <cellStyle name="40% - Accent5 4 2 2 2" xfId="936" xr:uid="{B600B31C-E50C-43EE-8DAE-DCE7E72413AC}"/>
+    <cellStyle name="40% - Accent5 4 2 2 2 2" xfId="2292" xr:uid="{1E911C0E-754A-4592-B050-8E6F4C5D1441}"/>
+    <cellStyle name="40% - Accent5 4 2 2 3" xfId="1321" xr:uid="{ABCDBBAB-1722-41F5-AF73-EAF2797FB65C}"/>
+    <cellStyle name="40% - Accent5 4 2 2 4" xfId="1912" xr:uid="{B578C804-4B20-4730-A346-F5F1FE9A1590}"/>
+    <cellStyle name="40% - Accent5 4 2 3" xfId="666" xr:uid="{399F8C5B-537F-41B5-98B8-18B7F6CED7BE}"/>
+    <cellStyle name="40% - Accent5 4 2 3 2" xfId="2024" xr:uid="{E4361563-FCBD-42D5-946E-0B54E7BE3941}"/>
+    <cellStyle name="40% - Accent5 4 2 4" xfId="807" xr:uid="{39EA2DF4-1EC3-4B20-A66C-4DEA7F165B7B}"/>
+    <cellStyle name="40% - Accent5 4 2 4 2" xfId="2165" xr:uid="{4EBF6307-3A90-4884-9DC4-A3538FD2846F}"/>
+    <cellStyle name="40% - Accent5 4 2 5" xfId="418" xr:uid="{98926D61-1A9B-4F6D-AA80-EEA2B783AD61}"/>
+    <cellStyle name="40% - Accent5 4 2 5 2" xfId="1785" xr:uid="{59BE3900-8870-4AAD-8F63-3125B7182B92}"/>
+    <cellStyle name="40% - Accent5 4 2 6" xfId="1177" xr:uid="{5F2F3D2C-2450-42A8-BF6B-17960FC37C55}"/>
+    <cellStyle name="40% - Accent5 4 2 7" xfId="1657" xr:uid="{848C0F12-9009-46B6-8DBF-D2D44A47842C}"/>
+    <cellStyle name="40% - Accent5 4 3" xfId="231" xr:uid="{BACA9D33-271A-487C-82EA-11A9A82219AC}"/>
+    <cellStyle name="40% - Accent5 4 3 2" xfId="879" xr:uid="{E18A9EB7-71B9-42B9-9358-51A9A1052BF9}"/>
+    <cellStyle name="40% - Accent5 4 3 2 2" xfId="2236" xr:uid="{7AAA434D-CA84-4991-A9D8-49196363BF5C}"/>
+    <cellStyle name="40% - Accent5 4 3 3" xfId="491" xr:uid="{4A262F67-C272-4232-B22D-EB6C25FA783D}"/>
+    <cellStyle name="40% - Accent5 4 3 3 2" xfId="1856" xr:uid="{71C4F883-1758-433E-988E-E975107D1074}"/>
+    <cellStyle name="40% - Accent5 4 3 4" xfId="1121" xr:uid="{A511AEE9-70F7-4FA6-8FD4-E25CB845592B}"/>
+    <cellStyle name="40% - Accent5 4 3 5" xfId="1600" xr:uid="{9A11E544-A1F1-4395-A7F2-F8587F12DCC1}"/>
+    <cellStyle name="40% - Accent5 4 4" xfId="610" xr:uid="{5C16F216-7897-4276-A3D8-90F7A52050E7}"/>
+    <cellStyle name="40% - Accent5 4 4 2" xfId="1250" xr:uid="{3943F0A2-0769-4085-8CCC-4FFE39A71617}"/>
+    <cellStyle name="40% - Accent5 4 4 3" xfId="1968" xr:uid="{6558ADBD-8FB7-44F5-AF62-F169D9A9168A}"/>
+    <cellStyle name="40% - Accent5 4 5" xfId="750" xr:uid="{FB5742E9-F027-4C1D-969B-D29CB347D550}"/>
+    <cellStyle name="40% - Accent5 4 5 2" xfId="2108" xr:uid="{BADE06BF-19AB-46F6-B469-3BF0BCF5B38B}"/>
+    <cellStyle name="40% - Accent5 4 6" xfId="361" xr:uid="{B2A9EA4E-11E3-45AB-9FF5-38BAC5571693}"/>
+    <cellStyle name="40% - Accent5 4 6 2" xfId="1728" xr:uid="{B638A5E6-B3F0-4C53-9FFC-3B50EC189755}"/>
+    <cellStyle name="40% - Accent5 4 7" xfId="161" xr:uid="{B6F70160-DE1B-4C19-8E42-F1A15234136F}"/>
+    <cellStyle name="40% - Accent5 4 7 2" xfId="1530" xr:uid="{BFBB324B-D01F-4756-9A05-D45956EB0DB1}"/>
+    <cellStyle name="40% - Accent5 4 8" xfId="1051" xr:uid="{CF05253F-A9F5-40E0-8B35-228612DAF7F2}"/>
+    <cellStyle name="40% - Accent5 4 9" xfId="1460" xr:uid="{50BDE3BF-3389-45BC-BAF7-5FE5BAE7D008}"/>
+    <cellStyle name="40% - Accent5 5" xfId="104" xr:uid="{9ADDB309-7117-4608-B2A5-530F187643A8}"/>
+    <cellStyle name="40% - Accent5 5 2" xfId="247" xr:uid="{3739B81E-282E-4CA3-A7F3-F52C94E80FFA}"/>
+    <cellStyle name="40% - Accent5 5 2 2" xfId="892" xr:uid="{9A303C7B-8694-4A93-813D-845BCAF1E48D}"/>
+    <cellStyle name="40% - Accent5 5 2 2 2" xfId="2248" xr:uid="{21243650-E4BF-4F95-AB29-C7D03DA3FFC2}"/>
+    <cellStyle name="40% - Accent5 5 2 3" xfId="507" xr:uid="{A31F715F-571D-4EE7-A6E1-75DF65EAA6BB}"/>
+    <cellStyle name="40% - Accent5 5 2 3 2" xfId="1868" xr:uid="{B4155B37-EEF3-4E7E-B14A-C7841AAED677}"/>
+    <cellStyle name="40% - Accent5 5 2 4" xfId="1133" xr:uid="{095AAEAD-4658-4D3C-B5FB-CE6874978984}"/>
+    <cellStyle name="40% - Accent5 5 2 5" xfId="1614" xr:uid="{E73324F5-6A39-4AE4-816E-D4DBED8C2D06}"/>
+    <cellStyle name="40% - Accent5 5 3" xfId="680" xr:uid="{98BBE832-583B-4F73-B272-EC6C5D947E17}"/>
+    <cellStyle name="40% - Accent5 5 3 2" xfId="1264" xr:uid="{BA1586A0-9E1B-4602-BAE2-6EA7B04ED2C5}"/>
+    <cellStyle name="40% - Accent5 5 3 3" xfId="2038" xr:uid="{FABD98F2-12D4-4D91-98F3-A4725BE5C21F}"/>
+    <cellStyle name="40% - Accent5 5 4" xfId="764" xr:uid="{AD5BB179-0739-495D-B243-802D15328254}"/>
+    <cellStyle name="40% - Accent5 5 4 2" xfId="2122" xr:uid="{E3E8731F-D30E-4BA7-9286-566F42490E33}"/>
+    <cellStyle name="40% - Accent5 5 5" xfId="375" xr:uid="{A77C5349-8B44-431D-B2DA-686BEA60E7A5}"/>
+    <cellStyle name="40% - Accent5 5 5 2" xfId="1742" xr:uid="{C1442FFE-5F77-4785-AE56-5BF153F46F6F}"/>
+    <cellStyle name="40% - Accent5 5 6" xfId="175" xr:uid="{15DFA018-C500-4D52-BECD-4F706B6E0703}"/>
+    <cellStyle name="40% - Accent5 5 6 2" xfId="1544" xr:uid="{F85C1FA1-7B94-4507-A83C-9ACCE4D2EC71}"/>
+    <cellStyle name="40% - Accent5 5 7" xfId="1065" xr:uid="{F4637FE6-5683-4C77-B978-414F0FCAF56D}"/>
+    <cellStyle name="40% - Accent5 5 8" xfId="1474" xr:uid="{6A422BCC-4FC4-4ED4-B024-5BEA196DEECA}"/>
+    <cellStyle name="40% - Accent5 6" xfId="187" xr:uid="{58FC85E1-B466-4EB0-B9F9-3925EDF75874}"/>
+    <cellStyle name="40% - Accent5 6 2" xfId="622" xr:uid="{FAC06F3C-F849-4C09-897F-41A7FC1F4A3B}"/>
+    <cellStyle name="40% - Accent5 6 2 2" xfId="1277" xr:uid="{99A31AB6-0279-4773-AD66-25622DF740B8}"/>
+    <cellStyle name="40% - Accent5 6 2 3" xfId="1980" xr:uid="{8FC83AC6-523E-4F65-9BCC-A856A5E5DE7A}"/>
+    <cellStyle name="40% - Accent5 6 3" xfId="822" xr:uid="{0B1E1EDE-3BEA-4507-A8E4-03C9D79B5E78}"/>
+    <cellStyle name="40% - Accent5 6 3 2" xfId="2180" xr:uid="{52E1DA99-888D-48E0-8653-22EE374C9F75}"/>
+    <cellStyle name="40% - Accent5 6 4" xfId="433" xr:uid="{A870D003-3E6C-45F5-B125-E1FEAC614531}"/>
+    <cellStyle name="40% - Accent5 6 4 2" xfId="1800" xr:uid="{71E86159-EFE9-4CBA-87E3-56FB3F47B2DD}"/>
+    <cellStyle name="40% - Accent5 6 5" xfId="1077" xr:uid="{C9E28FAA-6B3E-4DF8-8EE8-D99585D08D0A}"/>
+    <cellStyle name="40% - Accent5 6 6" xfId="1556" xr:uid="{D413247C-E56C-4252-8C88-D23D9839EDED}"/>
+    <cellStyle name="40% - Accent5 7" xfId="305" xr:uid="{EBE7A36E-CFE8-4090-A04A-299879B97456}"/>
+    <cellStyle name="40% - Accent5 7 2" xfId="694" xr:uid="{0D3FC4EF-5563-4A78-931C-F910E86C81F3}"/>
+    <cellStyle name="40% - Accent5 7 2 2" xfId="1335" xr:uid="{DCEC06B7-50EC-4FBC-8C6F-F042DF1820D7}"/>
+    <cellStyle name="40% - Accent5 7 2 3" xfId="2052" xr:uid="{D00E4BEA-7AA2-41BB-B825-BCF8DF0F0D1E}"/>
+    <cellStyle name="40% - Accent5 7 3" xfId="835" xr:uid="{E96DC187-31BC-46FE-8C83-F36BA7560981}"/>
+    <cellStyle name="40% - Accent5 7 3 2" xfId="2192" xr:uid="{9290167B-BBA0-4EF4-8328-F1BEBC2C3970}"/>
+    <cellStyle name="40% - Accent5 7 4" xfId="447" xr:uid="{EB042270-1B56-4758-9F3A-0346DD63D57A}"/>
+    <cellStyle name="40% - Accent5 7 4 2" xfId="1812" xr:uid="{1978D6D7-D890-41A5-9FC7-4D3FB1D79010}"/>
+    <cellStyle name="40% - Accent5 7 5" xfId="1191" xr:uid="{067E58C6-9500-4E8D-8EDE-9B1CA8D7E44B}"/>
+    <cellStyle name="40% - Accent5 7 6" xfId="1672" xr:uid="{34BD09DF-32BB-477F-A5E2-B01DA350E541}"/>
+    <cellStyle name="40% - Accent5 8" xfId="566" xr:uid="{1DDC7350-116E-473E-AD6E-A8778C4D41E0}"/>
+    <cellStyle name="40% - Accent5 8 2" xfId="1205" xr:uid="{23C9CFCB-07A5-4A5B-AC7B-32EC0F5DF201}"/>
+    <cellStyle name="40% - Accent5 8 3" xfId="1924" xr:uid="{56AE9874-9BF8-4822-AB2C-E4EC5C0E128D}"/>
+    <cellStyle name="40% - Accent5 9" xfId="706" xr:uid="{2E9BBE1A-99B3-4AB4-876C-2E4FA9BBEF08}"/>
+    <cellStyle name="40% - Accent5 9 2" xfId="1349" xr:uid="{E6C1C01C-F901-4A56-AD6A-A0677164357E}"/>
+    <cellStyle name="40% - Accent5 9 3" xfId="2064" xr:uid="{EA6C7D6D-5875-40FA-8A25-CC16A1BA48FA}"/>
+    <cellStyle name="40% - Accent6" xfId="33" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6 10" xfId="319" xr:uid="{39471796-C8FE-437B-A4EE-B68CFCCA54C3}"/>
+    <cellStyle name="40% - Accent6 10 2" xfId="1365" xr:uid="{8F319C5D-FB91-4CC7-B78F-98C8AB64EBA4}"/>
+    <cellStyle name="40% - Accent6 10 3" xfId="1686" xr:uid="{EA9CC681-F43B-40FA-82B7-BAB641EB2318}"/>
+    <cellStyle name="40% - Accent6 11" xfId="119" xr:uid="{C2D090DB-52DA-402A-9784-B9D5829CAA36}"/>
+    <cellStyle name="40% - Accent6 11 2" xfId="1378" xr:uid="{7ED4E1F5-86AA-497F-8E76-5F9EE367CEDA}"/>
+    <cellStyle name="40% - Accent6 11 3" xfId="1488" xr:uid="{EC9E72F0-5ABA-48E3-BEA6-00CCCD3E767B}"/>
+    <cellStyle name="40% - Accent6 12" xfId="952" xr:uid="{19AF464D-DB92-4577-82F6-844A6806FDF7}"/>
+    <cellStyle name="40% - Accent6 12 2" xfId="1391" xr:uid="{0A991719-65BA-4836-96E6-9620B88588A9}"/>
+    <cellStyle name="40% - Accent6 12 3" xfId="2308" xr:uid="{585D5754-70AC-4A2D-98F9-50A800AF6CB0}"/>
+    <cellStyle name="40% - Accent6 13" xfId="966" xr:uid="{6DC7439C-4648-48A3-A9D7-6B15F0ED6D21}"/>
+    <cellStyle name="40% - Accent6 13 2" xfId="1405" xr:uid="{98A9C933-39CA-4A9D-B46C-468AFF75BE89}"/>
+    <cellStyle name="40% - Accent6 13 3" xfId="2322" xr:uid="{6FD0FCAF-FCFC-4E61-9EFC-488CDF660D28}"/>
+    <cellStyle name="40% - Accent6 14" xfId="980" xr:uid="{12A942ED-B07B-4703-A1A7-104634FDCDB0}"/>
+    <cellStyle name="40% - Accent6 14 2" xfId="2336" xr:uid="{F64812F6-4133-42EF-97F8-FA81A10C8ADB}"/>
+    <cellStyle name="40% - Accent6 15" xfId="996" xr:uid="{190BBE45-676C-46A0-945C-859F9A5F91FF}"/>
+    <cellStyle name="40% - Accent6 16" xfId="1009" xr:uid="{A742986D-91E7-4C1D-8297-E12D7990BCD8}"/>
+    <cellStyle name="40% - Accent6 17" xfId="1418" xr:uid="{6E8E979D-9D86-4A60-94BF-398BB20564D1}"/>
+    <cellStyle name="40% - Accent6 2" xfId="60" xr:uid="{6A58A091-F97C-4757-8C9B-108B3857297E}"/>
+    <cellStyle name="40% - Accent6 2 2" xfId="265" xr:uid="{773A484C-568A-44F6-A675-703DE46A2F6B}"/>
+    <cellStyle name="40% - Accent6 2 2 2" xfId="528" xr:uid="{40106F62-187A-4B93-953C-C0CA3DF60086}"/>
+    <cellStyle name="40% - Accent6 2 2 2 2" xfId="910" xr:uid="{ACB51EEF-F219-4892-803C-823A0021839D}"/>
+    <cellStyle name="40% - Accent6 2 2 2 2 2" xfId="2266" xr:uid="{90D197A0-B485-43AF-9341-E8279175C6A7}"/>
+    <cellStyle name="40% - Accent6 2 2 2 3" xfId="1295" xr:uid="{8EE6B8C7-6818-4D98-8960-59743F7CB77C}"/>
+    <cellStyle name="40% - Accent6 2 2 2 4" xfId="1886" xr:uid="{4CB84380-E4A3-4B06-859B-8FF3915F4241}"/>
+    <cellStyle name="40% - Accent6 2 2 3" xfId="640" xr:uid="{FF86A174-1F42-4549-A905-B5C81D385793}"/>
+    <cellStyle name="40% - Accent6 2 2 3 2" xfId="1998" xr:uid="{D9337BE9-5A3D-43F1-994F-C5571D7079B5}"/>
+    <cellStyle name="40% - Accent6 2 2 4" xfId="782" xr:uid="{5B9F27FD-0153-4D16-85A7-2A30F60FEFE5}"/>
+    <cellStyle name="40% - Accent6 2 2 4 2" xfId="2140" xr:uid="{C13BFA07-4C7E-4CFC-A9C3-F80C5FD799A0}"/>
+    <cellStyle name="40% - Accent6 2 2 5" xfId="393" xr:uid="{4CD43AA2-6CBC-4DF5-8790-53C4FF8B5071}"/>
+    <cellStyle name="40% - Accent6 2 2 5 2" xfId="1760" xr:uid="{91EDCA07-B016-48C6-830D-9EEC91152863}"/>
+    <cellStyle name="40% - Accent6 2 2 6" xfId="1151" xr:uid="{08C0A7F0-CED4-4445-83AF-2D33E7416E21}"/>
+    <cellStyle name="40% - Accent6 2 2 7" xfId="1632" xr:uid="{DC2EBA76-AF66-4E20-A2C2-C95F9DED32EB}"/>
+    <cellStyle name="40% - Accent6 2 3" xfId="205" xr:uid="{04165685-D521-45C6-9616-BB6F76C2373D}"/>
+    <cellStyle name="40% - Accent6 2 3 2" xfId="853" xr:uid="{76851BBC-45CE-4A77-8237-5F7999415600}"/>
+    <cellStyle name="40% - Accent6 2 3 2 2" xfId="2210" xr:uid="{15D44A2E-5301-4AC3-A8C8-2EF30E9470E4}"/>
+    <cellStyle name="40% - Accent6 2 3 3" xfId="465" xr:uid="{91650D65-8DE6-40D4-A103-04EF2FBF23BF}"/>
+    <cellStyle name="40% - Accent6 2 3 3 2" xfId="1830" xr:uid="{1C374C5C-B9BB-4CA1-B593-33BF24CDFCA9}"/>
+    <cellStyle name="40% - Accent6 2 3 4" xfId="1095" xr:uid="{B3D0FD84-62FB-45D8-8F0C-7A74C8AF01C3}"/>
+    <cellStyle name="40% - Accent6 2 3 5" xfId="1574" xr:uid="{478E19FF-F73C-4D19-891E-E5B530499845}"/>
+    <cellStyle name="40% - Accent6 2 4" xfId="584" xr:uid="{13626D0B-65B9-425F-8D0A-8C62C53C56C9}"/>
+    <cellStyle name="40% - Accent6 2 4 2" xfId="1224" xr:uid="{48E064C5-FB06-437A-9AC1-C47DCA109D35}"/>
+    <cellStyle name="40% - Accent6 2 4 3" xfId="1942" xr:uid="{0E2E8CF2-8CB3-44D4-A3FB-A4DF9D234D15}"/>
+    <cellStyle name="40% - Accent6 2 5" xfId="724" xr:uid="{EECE48ED-0A7A-47FE-ACF6-0941F606673B}"/>
+    <cellStyle name="40% - Accent6 2 5 2" xfId="2082" xr:uid="{18CCB968-BCD2-485D-BA5B-623C64647210}"/>
+    <cellStyle name="40% - Accent6 2 6" xfId="335" xr:uid="{F92A6DB3-68D0-4B94-9BF7-B7BDF1B757AA}"/>
+    <cellStyle name="40% - Accent6 2 6 2" xfId="1702" xr:uid="{B3769F0A-7223-40D5-AA1B-C46AE9299CF4}"/>
+    <cellStyle name="40% - Accent6 2 7" xfId="135" xr:uid="{04412572-711D-45C6-85E3-1BAA78D94F54}"/>
+    <cellStyle name="40% - Accent6 2 7 2" xfId="1504" xr:uid="{3448A7D1-8FFA-4B0D-8A85-E61BF7B46906}"/>
+    <cellStyle name="40% - Accent6 2 8" xfId="1025" xr:uid="{D3185075-9E90-49A8-ABBF-282E96157B40}"/>
+    <cellStyle name="40% - Accent6 2 9" xfId="1434" xr:uid="{7E07BD9A-B1F2-4CF4-83A3-2759F02AF501}"/>
+    <cellStyle name="40% - Accent6 3" xfId="78" xr:uid="{6B18F70B-857C-429A-80A8-9F55E5056D37}"/>
+    <cellStyle name="40% - Accent6 3 2" xfId="279" xr:uid="{7A3A799D-E466-417C-AB83-052873D2E9D2}"/>
+    <cellStyle name="40% - Accent6 3 2 2" xfId="542" xr:uid="{16433B32-ECF9-4E0E-898A-6EBD6F458069}"/>
+    <cellStyle name="40% - Accent6 3 2 2 2" xfId="924" xr:uid="{01131697-0ED4-4B9C-A02D-A3E9C8E35087}"/>
+    <cellStyle name="40% - Accent6 3 2 2 2 2" xfId="2280" xr:uid="{0DAF1402-069F-4B37-8204-30EECB9BCC5E}"/>
+    <cellStyle name="40% - Accent6 3 2 2 3" xfId="1309" xr:uid="{F1A9041A-F6DA-42C2-AA20-4C1C7BBB9A17}"/>
+    <cellStyle name="40% - Accent6 3 2 2 4" xfId="1900" xr:uid="{41B19B2B-3FBA-4AE9-8DF5-E59298E8FEF4}"/>
+    <cellStyle name="40% - Accent6 3 2 3" xfId="654" xr:uid="{CB79F248-A0B9-4E59-A053-6BBA897ABE0D}"/>
+    <cellStyle name="40% - Accent6 3 2 3 2" xfId="2012" xr:uid="{28C5701A-5447-459C-9C76-2AEE932CD6AB}"/>
+    <cellStyle name="40% - Accent6 3 2 4" xfId="796" xr:uid="{EB3E71E4-89AC-48A7-A2A5-79E7A9B6BFA6}"/>
+    <cellStyle name="40% - Accent6 3 2 4 2" xfId="2154" xr:uid="{C4EE280D-B33D-4443-9232-E3DC53426C9D}"/>
+    <cellStyle name="40% - Accent6 3 2 5" xfId="407" xr:uid="{1A9F844A-0648-421C-9C55-0B65149D8302}"/>
+    <cellStyle name="40% - Accent6 3 2 5 2" xfId="1774" xr:uid="{FE38025F-26D9-4FF9-8AFF-0B31871880B9}"/>
+    <cellStyle name="40% - Accent6 3 2 6" xfId="1165" xr:uid="{54744B1A-F8BA-4CF0-B67D-90D87B409F55}"/>
+    <cellStyle name="40% - Accent6 3 2 7" xfId="1646" xr:uid="{89DD7E58-3F6F-44DB-9B93-042C5C33471F}"/>
+    <cellStyle name="40% - Accent6 3 3" xfId="219" xr:uid="{7E4255BC-F3D8-4F76-A0DB-BB9B4E7D1277}"/>
+    <cellStyle name="40% - Accent6 3 3 2" xfId="867" xr:uid="{4A88E15E-E0BA-4108-8094-18EF4B9969EA}"/>
+    <cellStyle name="40% - Accent6 3 3 2 2" xfId="2224" xr:uid="{8EBC47FD-124D-4018-A569-F6266A78F51B}"/>
+    <cellStyle name="40% - Accent6 3 3 3" xfId="479" xr:uid="{D67F3B09-9D6A-4428-95F8-8A507CC58EC1}"/>
+    <cellStyle name="40% - Accent6 3 3 3 2" xfId="1844" xr:uid="{2BED63A3-8605-45E9-A024-953AE9AD3C01}"/>
+    <cellStyle name="40% - Accent6 3 3 4" xfId="1109" xr:uid="{ACF9EC4B-365C-4043-BC8F-40685EBCE044}"/>
+    <cellStyle name="40% - Accent6 3 3 5" xfId="1588" xr:uid="{5BB8A1EA-83E7-481C-AF90-AB62867A7E6A}"/>
+    <cellStyle name="40% - Accent6 3 4" xfId="598" xr:uid="{E2D291B9-AE51-476D-A5B8-BC44EAE7D942}"/>
+    <cellStyle name="40% - Accent6 3 4 2" xfId="1238" xr:uid="{B5883238-DAD6-4731-B171-6AA9830DA7D0}"/>
+    <cellStyle name="40% - Accent6 3 4 3" xfId="1956" xr:uid="{2F7A6B4E-7A08-4326-AEB0-63DD86C268C0}"/>
+    <cellStyle name="40% - Accent6 3 5" xfId="738" xr:uid="{EFC4500F-1B5F-473D-8CA7-1994117A7CE0}"/>
+    <cellStyle name="40% - Accent6 3 5 2" xfId="2096" xr:uid="{D25FACF7-7061-4E10-B5CF-606822C84FDF}"/>
+    <cellStyle name="40% - Accent6 3 6" xfId="349" xr:uid="{4EAC312A-DAC0-4E36-AEC5-66F097A77549}"/>
+    <cellStyle name="40% - Accent6 3 6 2" xfId="1716" xr:uid="{A5A9AF41-04B4-4341-9E32-2E9C789F015F}"/>
+    <cellStyle name="40% - Accent6 3 7" xfId="149" xr:uid="{C5873B72-FFA3-46B9-9B2E-C6E4DDFF703E}"/>
+    <cellStyle name="40% - Accent6 3 7 2" xfId="1518" xr:uid="{8FA75F08-7C80-4E52-A24E-38E8B5C005FF}"/>
+    <cellStyle name="40% - Accent6 3 8" xfId="1039" xr:uid="{568B6EB3-35FC-4475-8BB3-16FD008F4A23}"/>
+    <cellStyle name="40% - Accent6 3 9" xfId="1448" xr:uid="{42390D8A-D72A-4B63-812B-E172F89E1600}"/>
+    <cellStyle name="40% - Accent6 4" xfId="92" xr:uid="{01B15B17-B4F1-431C-8F5F-DF6EADAD1FEA}"/>
+    <cellStyle name="40% - Accent6 4 2" xfId="292" xr:uid="{6AA416E1-D34F-446E-8F7C-C3155FAFF2E4}"/>
+    <cellStyle name="40% - Accent6 4 2 2" xfId="556" xr:uid="{FD4FAEB8-28BC-4B2B-B5B4-8BD0B07B3BD5}"/>
+    <cellStyle name="40% - Accent6 4 2 2 2" xfId="938" xr:uid="{E74C2656-055D-4A04-887C-0FA5C48BA827}"/>
+    <cellStyle name="40% - Accent6 4 2 2 2 2" xfId="2294" xr:uid="{BD559CA5-52A6-4001-937F-7812862BE2CD}"/>
+    <cellStyle name="40% - Accent6 4 2 2 3" xfId="1323" xr:uid="{814F896F-9054-44E9-B786-FD6D5D79BB1F}"/>
+    <cellStyle name="40% - Accent6 4 2 2 4" xfId="1914" xr:uid="{47807632-6435-4979-9D9B-B38A366B5D25}"/>
+    <cellStyle name="40% - Accent6 4 2 3" xfId="668" xr:uid="{2EBAB581-2A91-460B-BC4C-BBA5EED51A85}"/>
+    <cellStyle name="40% - Accent6 4 2 3 2" xfId="2026" xr:uid="{C69E8A50-F02A-4829-AE2B-916D5C5E61B2}"/>
+    <cellStyle name="40% - Accent6 4 2 4" xfId="809" xr:uid="{DC1DE150-BF2A-448B-BFC4-BDC4710EBB10}"/>
+    <cellStyle name="40% - Accent6 4 2 4 2" xfId="2167" xr:uid="{2F6B20D7-19C3-42D8-A73E-912AE1E41F99}"/>
+    <cellStyle name="40% - Accent6 4 2 5" xfId="420" xr:uid="{DDD5A22B-7B4C-4CDE-87BC-C9D38ECDDF1E}"/>
+    <cellStyle name="40% - Accent6 4 2 5 2" xfId="1787" xr:uid="{59DE3112-2361-462E-93FB-14E0B49D9FC0}"/>
+    <cellStyle name="40% - Accent6 4 2 6" xfId="1179" xr:uid="{ADE300F5-53F1-4566-A08A-91DCDA8B1FB9}"/>
+    <cellStyle name="40% - Accent6 4 2 7" xfId="1659" xr:uid="{E65FAD38-076F-45E8-ABD8-3CD8982554B2}"/>
+    <cellStyle name="40% - Accent6 4 3" xfId="233" xr:uid="{477B866E-4EC3-41D0-9D69-B63EC673ABDC}"/>
+    <cellStyle name="40% - Accent6 4 3 2" xfId="881" xr:uid="{39D69BCE-8319-411B-BDBE-C01795A028AD}"/>
+    <cellStyle name="40% - Accent6 4 3 2 2" xfId="2238" xr:uid="{E2B22CC7-CA2B-4331-A642-B43087AE4CCB}"/>
+    <cellStyle name="40% - Accent6 4 3 3" xfId="493" xr:uid="{BC39B580-97FD-486F-B008-E8078FE477E2}"/>
+    <cellStyle name="40% - Accent6 4 3 3 2" xfId="1858" xr:uid="{9BB392F1-D941-4F68-A07C-6DE76EC246A0}"/>
+    <cellStyle name="40% - Accent6 4 3 4" xfId="1123" xr:uid="{3CEA8633-77AA-4E1A-96A3-269BD67997B8}"/>
+    <cellStyle name="40% - Accent6 4 3 5" xfId="1602" xr:uid="{7AFB76BE-B62B-4E30-8CA8-383608B2CA53}"/>
+    <cellStyle name="40% - Accent6 4 4" xfId="612" xr:uid="{22DDEDBC-1CAB-4017-B8FB-37215E4A5313}"/>
+    <cellStyle name="40% - Accent6 4 4 2" xfId="1252" xr:uid="{32946E57-F5E8-4267-A272-09F3A82C8896}"/>
+    <cellStyle name="40% - Accent6 4 4 3" xfId="1970" xr:uid="{831CDDEE-42E9-42D1-AA7E-B2A32E5E6CF2}"/>
+    <cellStyle name="40% - Accent6 4 5" xfId="752" xr:uid="{9E56412D-82E2-4F8D-9523-1E9B2D6C00C3}"/>
+    <cellStyle name="40% - Accent6 4 5 2" xfId="2110" xr:uid="{17212B02-399C-4C6F-A20E-A2CF83443C69}"/>
+    <cellStyle name="40% - Accent6 4 6" xfId="363" xr:uid="{60206648-181D-4AEB-A3EC-E3C6094B2FBE}"/>
+    <cellStyle name="40% - Accent6 4 6 2" xfId="1730" xr:uid="{7C9128A9-5019-4E40-BE29-56032C43C740}"/>
+    <cellStyle name="40% - Accent6 4 7" xfId="163" xr:uid="{AD04101F-E087-46AD-99F4-44284A502E63}"/>
+    <cellStyle name="40% - Accent6 4 7 2" xfId="1532" xr:uid="{EFF514B0-A3DF-4EF5-8581-6FC2C7434166}"/>
+    <cellStyle name="40% - Accent6 4 8" xfId="1053" xr:uid="{4376FA72-21ED-4705-8330-F71FAD4048F7}"/>
+    <cellStyle name="40% - Accent6 4 9" xfId="1462" xr:uid="{1663ADA7-1109-4A3C-A825-B34D4B21BC6F}"/>
+    <cellStyle name="40% - Accent6 5" xfId="106" xr:uid="{EE17AFA9-625C-4E3D-8E77-A425034419CA}"/>
+    <cellStyle name="40% - Accent6 5 2" xfId="249" xr:uid="{ECDB6F91-BDB7-4883-BA14-925A2CADE504}"/>
+    <cellStyle name="40% - Accent6 5 2 2" xfId="894" xr:uid="{8363DE5D-BE4E-47B8-9248-7C946A966914}"/>
+    <cellStyle name="40% - Accent6 5 2 2 2" xfId="2250" xr:uid="{1E7CD972-1235-4B3B-8926-D28A9551EEFA}"/>
+    <cellStyle name="40% - Accent6 5 2 3" xfId="509" xr:uid="{4F4F203E-5256-4486-B1C1-ED92C6CAAB6E}"/>
+    <cellStyle name="40% - Accent6 5 2 3 2" xfId="1870" xr:uid="{3B155537-039C-4C42-BDE2-A196978E9225}"/>
+    <cellStyle name="40% - Accent6 5 2 4" xfId="1135" xr:uid="{AAF52483-63B8-42CE-A179-4D9F2F10832C}"/>
+    <cellStyle name="40% - Accent6 5 2 5" xfId="1616" xr:uid="{C5DA3299-2759-4C85-8936-FA34B62FCFF1}"/>
+    <cellStyle name="40% - Accent6 5 3" xfId="682" xr:uid="{60ADE548-F8B2-44B5-A3F7-60F1CA4A3376}"/>
+    <cellStyle name="40% - Accent6 5 3 2" xfId="1266" xr:uid="{B4DD3B49-2CE1-466E-9CE3-C1E1454739FD}"/>
+    <cellStyle name="40% - Accent6 5 3 3" xfId="2040" xr:uid="{EE8BC021-9C9D-416C-90B1-0C5F0F769708}"/>
+    <cellStyle name="40% - Accent6 5 4" xfId="766" xr:uid="{EAA30BD0-5A62-4D02-BF05-265FF779AE62}"/>
+    <cellStyle name="40% - Accent6 5 4 2" xfId="2124" xr:uid="{59A6EC10-21C6-4A3E-A4BA-DC913E704ECA}"/>
+    <cellStyle name="40% - Accent6 5 5" xfId="377" xr:uid="{72255A8F-3F9A-41AF-BECF-D09759F7D0C0}"/>
+    <cellStyle name="40% - Accent6 5 5 2" xfId="1744" xr:uid="{5D7B0C1F-B492-4660-8CA0-260FA2CE600A}"/>
+    <cellStyle name="40% - Accent6 5 6" xfId="177" xr:uid="{7441691F-0C7D-4197-974A-D283D7083F99}"/>
+    <cellStyle name="40% - Accent6 5 6 2" xfId="1546" xr:uid="{F8A72074-AB67-4170-9494-D50E20D91E45}"/>
+    <cellStyle name="40% - Accent6 5 7" xfId="1067" xr:uid="{FA4D26BF-2752-4E2E-B4D5-3373E7FC20C6}"/>
+    <cellStyle name="40% - Accent6 5 8" xfId="1476" xr:uid="{1FB29F36-AB49-4DC2-B76F-60985D1FE3E2}"/>
+    <cellStyle name="40% - Accent6 6" xfId="189" xr:uid="{A130DB87-EB44-4472-BD63-6BBDF4C0A174}"/>
+    <cellStyle name="40% - Accent6 6 2" xfId="624" xr:uid="{9A365833-00CB-4E19-AE5C-B6E4786802BE}"/>
+    <cellStyle name="40% - Accent6 6 2 2" xfId="1279" xr:uid="{B7158676-9177-42D3-B2AB-AE97166B1BB4}"/>
+    <cellStyle name="40% - Accent6 6 2 3" xfId="1982" xr:uid="{B0981B34-AD0C-45F1-B636-FDD0CAE3554A}"/>
+    <cellStyle name="40% - Accent6 6 3" xfId="824" xr:uid="{789D3526-147D-4E1E-8893-385FA4A7B1F4}"/>
+    <cellStyle name="40% - Accent6 6 3 2" xfId="2182" xr:uid="{AFF51C34-4C95-477E-BDB7-17D6850A0621}"/>
+    <cellStyle name="40% - Accent6 6 4" xfId="435" xr:uid="{5B708099-A8FF-4790-9C65-1A441CD5F13C}"/>
+    <cellStyle name="40% - Accent6 6 4 2" xfId="1802" xr:uid="{3B6158DD-4832-4946-8869-1EDEEA4FBB19}"/>
+    <cellStyle name="40% - Accent6 6 5" xfId="1079" xr:uid="{42A52319-A91E-4A65-A1FE-18ACB491CF83}"/>
+    <cellStyle name="40% - Accent6 6 6" xfId="1558" xr:uid="{94E67A58-DCD5-4AC6-B325-B73DCA28C634}"/>
+    <cellStyle name="40% - Accent6 7" xfId="307" xr:uid="{7DB84CF0-4516-49C2-9891-74FAB5D73DB6}"/>
+    <cellStyle name="40% - Accent6 7 2" xfId="696" xr:uid="{8F35C50D-820D-4884-9A70-A87B5DBD2DCA}"/>
+    <cellStyle name="40% - Accent6 7 2 2" xfId="1337" xr:uid="{03E6092C-36E5-469F-8553-D0D36D5E53BE}"/>
+    <cellStyle name="40% - Accent6 7 2 3" xfId="2054" xr:uid="{F62BBF54-9E34-4CDE-9279-6E46C1FD6577}"/>
+    <cellStyle name="40% - Accent6 7 3" xfId="837" xr:uid="{4390A7A2-72D0-4D79-BCDF-6C7E9DBD9DD0}"/>
+    <cellStyle name="40% - Accent6 7 3 2" xfId="2194" xr:uid="{81D7CE91-B2B4-4443-9653-DBDF30BB44F0}"/>
+    <cellStyle name="40% - Accent6 7 4" xfId="449" xr:uid="{B88328F8-AA99-4F81-BF1D-F9C8A817A6F1}"/>
+    <cellStyle name="40% - Accent6 7 4 2" xfId="1814" xr:uid="{E7F03153-1B21-4318-BD32-9BFA06B6FBF4}"/>
+    <cellStyle name="40% - Accent6 7 5" xfId="1193" xr:uid="{D9EBA40C-92AE-4B35-8BA7-E424C3658C50}"/>
+    <cellStyle name="40% - Accent6 7 6" xfId="1674" xr:uid="{CEBED54E-D664-47B5-8949-CAC98F6FB9D6}"/>
+    <cellStyle name="40% - Accent6 8" xfId="568" xr:uid="{24E26940-7D75-4964-A6B9-F07D17D9114C}"/>
+    <cellStyle name="40% - Accent6 8 2" xfId="1207" xr:uid="{34367136-D23D-4095-9EB0-51A6F0F912DB}"/>
+    <cellStyle name="40% - Accent6 8 3" xfId="1926" xr:uid="{E6705456-6016-4A17-8C27-541FC5D6458E}"/>
+    <cellStyle name="40% - Accent6 9" xfId="708" xr:uid="{2E27149C-37FF-40B4-A2F6-25890DE9B6F8}"/>
+    <cellStyle name="40% - Accent6 9 2" xfId="1351" xr:uid="{A9A4B473-B466-42F3-BB88-A046D198C8EE}"/>
+    <cellStyle name="40% - Accent6 9 3" xfId="2066" xr:uid="{DD0C3B56-EC54-4C34-B6BA-04CF1AD94C17}"/>
+    <cellStyle name="60% - Accent1 2" xfId="36" xr:uid="{1C369D64-2B8F-45E9-8E2B-0F48E26F5F6A}"/>
+    <cellStyle name="60% - Accent2 2" xfId="37" xr:uid="{E248696C-9425-47AB-BA6C-E822EE5BA43E}"/>
+    <cellStyle name="60% - Accent3 2" xfId="38" xr:uid="{29FD35DA-5AAD-420F-87B9-B4F8996F592E}"/>
+    <cellStyle name="60% - Accent4 2" xfId="39" xr:uid="{02145D59-12C4-4E17-9BF3-ADA3967B7C28}"/>
+    <cellStyle name="60% - Accent5 2" xfId="40" xr:uid="{70B9FFEB-D1F6-4EAD-A0A4-F9D54492BD52}"/>
+    <cellStyle name="60% - Accent6 2" xfId="41" xr:uid="{C8D69B08-58E2-49B8-9684-6DCA5F2D8B9F}"/>
+    <cellStyle name="Accent1" xfId="16" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="19" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="22" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="25" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="28" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="31" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="6" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="9" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="CAPAD_STATS_TOTALS" xfId="64" xr:uid="{85F7A8BA-0D88-41C2-BE50-4C8A082F0755}"/>
+    <cellStyle name="Check Cell" xfId="11" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma 2" xfId="437" xr:uid="{5C957782-A795-4B7E-98D2-A831B63FAE82}"/>
+    <cellStyle name="Comma 2 2" xfId="496" xr:uid="{3AC268A4-C326-4F2E-AF91-491432B5251B}"/>
+    <cellStyle name="Comma 2 3" xfId="511" xr:uid="{B5F4CC0B-E068-4A49-88FA-C19B08F6F736}"/>
+    <cellStyle name="Comma 3" xfId="495" xr:uid="{E7611C8D-FD11-40E0-97B6-F25013A73453}"/>
+    <cellStyle name="Comma 4" xfId="825" xr:uid="{69C75C8B-C44D-413D-A9B4-1EBB815A6F55}"/>
+    <cellStyle name="Comma 5" xfId="436" xr:uid="{5EF07817-6B4A-44E4-9E39-919739CDD565}"/>
+    <cellStyle name="Comma 6" xfId="981" xr:uid="{DC3EB59B-1F45-473C-80F9-BB9985C2ED13}"/>
+    <cellStyle name="Explanatory Text" xfId="14" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="5" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="1" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="2" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="3" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="4" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="7" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="10" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral 2" xfId="35" xr:uid="{1CE55BB3-B3C4-460F-9672-51AB4C3B0C78}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 10" xfId="939" xr:uid="{60CE125D-92DB-4C98-A7E5-5AD445CFB151}"/>
+    <cellStyle name="Normal 10 2" xfId="1208" xr:uid="{606341B9-0078-48B5-8367-B45CCFAEC34B}"/>
+    <cellStyle name="Normal 10 3" xfId="2295" xr:uid="{5E1C5A90-68D7-4535-9BC6-3A7199A9D916}"/>
+    <cellStyle name="Normal 10 4" xfId="2344" xr:uid="{7BF9C3A3-D350-411B-9F39-76FEF58209BA}"/>
+    <cellStyle name="Normal 11" xfId="953" xr:uid="{0265ABC3-3080-4280-A4C4-03A3C1C89D8F}"/>
+    <cellStyle name="Normal 11 2" xfId="1194" xr:uid="{8383CEF9-9513-4693-8E66-7AC8E7A58289}"/>
+    <cellStyle name="Normal 11 3" xfId="2309" xr:uid="{B9E8A3F2-980D-4E9F-AD48-627EC56DC813}"/>
+    <cellStyle name="Normal 12" xfId="967" xr:uid="{5C3C335A-235A-4007-9C21-AF0CB72B78A2}"/>
+    <cellStyle name="Normal 12 2" xfId="1338" xr:uid="{9C10DC51-6AAB-4BA2-B303-45BC25E87274}"/>
+    <cellStyle name="Normal 12 3" xfId="2323" xr:uid="{2FDEAF7D-8FE6-4EE5-A471-7D10C87C02EF}"/>
+    <cellStyle name="Normal 13" xfId="983" xr:uid="{069A7CA3-422F-40C1-9160-E7560C69BACA}"/>
+    <cellStyle name="Normal 13 2" xfId="982" xr:uid="{9647151E-FA97-412D-BE78-3B98E6E26630}"/>
+    <cellStyle name="Normal 13 3" xfId="1352" xr:uid="{06AD4D28-9FBE-437A-83D8-6B71CD651C5F}"/>
+    <cellStyle name="Normal 14" xfId="43" xr:uid="{602EE813-AE39-4330-A4A7-22BB103DDCEF}"/>
+    <cellStyle name="Normal 15" xfId="1379" xr:uid="{30EB8C37-C2E7-4752-8AB3-226E9DAC8F56}"/>
+    <cellStyle name="Normal 16" xfId="1392" xr:uid="{95FDB035-6096-487C-8508-8210904B6A95}"/>
+    <cellStyle name="Normal 16 2" xfId="2345" xr:uid="{9337058C-020A-4BED-973A-36924CC97CB4}"/>
+    <cellStyle name="Normal 16 3" xfId="2338" xr:uid="{09414F5E-569A-4BEA-AA38-5961230F39B6}"/>
+    <cellStyle name="Normal 17" xfId="44" xr:uid="{38F8AB20-B6C5-47BD-AD22-30BB68D8414C}"/>
+    <cellStyle name="Normal 17 2" xfId="2337" xr:uid="{2CB5C5D0-4C50-4FE8-BD57-9D15BB8FBA47}"/>
+    <cellStyle name="Normal 2" xfId="45" xr:uid="{6DB1E396-7E8C-424E-A959-CAB7373639A5}"/>
+    <cellStyle name="Normal 2 2" xfId="42" xr:uid="{7826608F-13EA-4539-8F13-1ABD5E340307}"/>
+    <cellStyle name="Normal 2 2 2" xfId="513" xr:uid="{E15A3D61-59BD-4D34-92AF-17BEBA8AB984}"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="895" xr:uid="{F3D2D80C-1936-4765-80A8-1C7C337A975F}"/>
+    <cellStyle name="Normal 2 2 2 2 2" xfId="2251" xr:uid="{411A7DA5-B503-4189-B863-A07EFD58D5BE}"/>
+    <cellStyle name="Normal 2 2 2 3" xfId="1280" xr:uid="{499810D5-1B74-43AB-9A81-81949C59D65A}"/>
+    <cellStyle name="Normal 2 2 2 4" xfId="1871" xr:uid="{D39FDD6B-F1AD-444B-8159-F7EF59C9D946}"/>
+    <cellStyle name="Normal 2 2 3" xfId="1136" xr:uid="{6AFBAB65-08C5-49C0-8B3A-6119E2A4794B}"/>
+    <cellStyle name="Normal 2 2 4" xfId="2340" xr:uid="{C48E6223-7A98-4E40-899B-D2A5D8E87F2D}"/>
+    <cellStyle name="Normal 2 3" xfId="190" xr:uid="{D8615742-18BD-4E13-82B5-B137EE3A99DA}"/>
+    <cellStyle name="Normal 2 3 2" xfId="838" xr:uid="{F6DB0623-E41B-4A1E-B754-C083B82F2BA1}"/>
+    <cellStyle name="Normal 2 3 2 2" xfId="2195" xr:uid="{2DC246BB-4AF0-4E24-9091-E4F257C2667A}"/>
+    <cellStyle name="Normal 2 3 3" xfId="450" xr:uid="{9383E3E2-D3AA-4FD6-8633-7DB7EC417DDD}"/>
+    <cellStyle name="Normal 2 3 3 2" xfId="1815" xr:uid="{14893741-303E-49EF-9F0D-303DE518C56D}"/>
+    <cellStyle name="Normal 2 3 4" xfId="1080" xr:uid="{2CBC9A97-46C6-4BB1-9DB9-49EC8AC494D2}"/>
+    <cellStyle name="Normal 2 3 5" xfId="1559" xr:uid="{54D87FD8-6C89-4FA6-9332-376922318E4F}"/>
+    <cellStyle name="Normal 2 4" xfId="709" xr:uid="{69D57324-D758-4C4E-8A90-8B746284F8AD}"/>
+    <cellStyle name="Normal 2 4 2" xfId="1209" xr:uid="{F9C92833-5E83-4A21-B256-71A2C43A6BDD}"/>
+    <cellStyle name="Normal 2 4 3" xfId="2067" xr:uid="{E9B84445-CA34-485A-A24A-06F88421DE76}"/>
+    <cellStyle name="Normal 2 5" xfId="320" xr:uid="{6C8DD537-D4EC-4419-AE06-721157E21ECB}"/>
+    <cellStyle name="Normal 2 5 2" xfId="1406" xr:uid="{F1B15532-6AB4-45E4-948D-BEB010211924}"/>
+    <cellStyle name="Normal 2 5 3" xfId="1687" xr:uid="{8DC4BD85-9C16-4B3B-B9BE-D54C30B05CB3}"/>
+    <cellStyle name="Normal 2 6" xfId="107" xr:uid="{FD0B13DB-1D35-4A4B-8989-9065FB590F9B}"/>
+    <cellStyle name="Normal 2 7" xfId="62" xr:uid="{CFE40854-BA74-4C8B-9537-CED4B7C9DFB9}"/>
+    <cellStyle name="Normal 2 8" xfId="1419" xr:uid="{C9BEF48B-9973-40DB-9CCC-73D24DD52DEC}"/>
+    <cellStyle name="Normal 3" xfId="47" xr:uid="{73442FE4-F4C7-4AF8-BA3B-480717D75175}"/>
+    <cellStyle name="Normal 3 2" xfId="250" xr:uid="{D2BCEAAA-2466-4F1E-B578-21B500331597}"/>
+    <cellStyle name="Normal 3 2 2" xfId="515" xr:uid="{19D26968-9F7A-4369-A616-5E1D9B9A67EB}"/>
+    <cellStyle name="Normal 3 2 2 2" xfId="897" xr:uid="{D7F1F9AB-B520-47E8-A1DC-8B4A5F1BD187}"/>
+    <cellStyle name="Normal 3 2 2 2 2" xfId="2253" xr:uid="{3EC535C8-699A-4B53-A9CD-2D2BC462F65E}"/>
+    <cellStyle name="Normal 3 2 2 3" xfId="1282" xr:uid="{D71CF6D8-3839-4B1E-9CC9-12592D6BDA0F}"/>
+    <cellStyle name="Normal 3 2 2 4" xfId="1873" xr:uid="{073CE855-4F29-44C0-802B-6AAD3C3EC9EB}"/>
+    <cellStyle name="Normal 3 2 3" xfId="625" xr:uid="{613B4B4F-6F4C-48DC-9F64-B51EC49A46AF}"/>
+    <cellStyle name="Normal 3 2 3 2" xfId="1983" xr:uid="{4015626F-39E9-481A-9C07-F17AEFB31817}"/>
+    <cellStyle name="Normal 3 2 4" xfId="767" xr:uid="{C73B3A36-D354-4FF7-97C4-6574BDF37326}"/>
+    <cellStyle name="Normal 3 2 4 2" xfId="2125" xr:uid="{1DFB050B-EFF3-4068-B9CD-9BF9F4E1F13A}"/>
+    <cellStyle name="Normal 3 2 5" xfId="378" xr:uid="{068B92F8-172E-4388-8017-F2BA22827726}"/>
+    <cellStyle name="Normal 3 2 5 2" xfId="1745" xr:uid="{EFDCE998-7E3E-4011-A213-700B7E6BAFD9}"/>
+    <cellStyle name="Normal 3 2 6" xfId="1138" xr:uid="{747F584B-E683-4DB9-8514-ACCEB65338BA}"/>
+    <cellStyle name="Normal 3 2 7" xfId="1617" xr:uid="{92659E68-A114-4FF7-9071-C2218C489B85}"/>
+    <cellStyle name="Normal 3 3" xfId="192" xr:uid="{EB6AAE17-ADD6-48B9-BF5E-6E923FB67DB2}"/>
+    <cellStyle name="Normal 3 3 2" xfId="840" xr:uid="{BCBB0ED5-CFC9-419E-A6E4-BA88CFDA1557}"/>
+    <cellStyle name="Normal 3 3 2 2" xfId="2197" xr:uid="{6540B86E-24D3-4E21-A5BA-8F6805792133}"/>
+    <cellStyle name="Normal 3 3 3" xfId="452" xr:uid="{2B0BAAD3-775E-4F7B-8F9C-8B658AED385E}"/>
+    <cellStyle name="Normal 3 3 3 2" xfId="1817" xr:uid="{7FC6B4F0-614E-4451-8C5F-F6FFE1BA9615}"/>
+    <cellStyle name="Normal 3 3 4" xfId="1082" xr:uid="{1FE86382-8A4F-4708-BA61-AB41109AA98F}"/>
+    <cellStyle name="Normal 3 3 5" xfId="1561" xr:uid="{9A2CFF0B-503D-40C6-B9BD-8C6FB618FC2E}"/>
+    <cellStyle name="Normal 3 4" xfId="569" xr:uid="{D23C16F3-7FD0-4FB9-9717-5085EC5BA6C1}"/>
+    <cellStyle name="Normal 3 4 2" xfId="1211" xr:uid="{974A5A39-7EC6-4F3F-BF1C-C929EEC1DBF5}"/>
+    <cellStyle name="Normal 3 4 3" xfId="1927" xr:uid="{62942845-C211-48C2-9C99-947B5DEF649A}"/>
+    <cellStyle name="Normal 3 5" xfId="711" xr:uid="{6EA71082-4EEE-4FB6-8EF5-9FE872E0C18D}"/>
+    <cellStyle name="Normal 3 5 2" xfId="2069" xr:uid="{8C38986A-AD00-4189-8C82-BD823D269742}"/>
+    <cellStyle name="Normal 3 6" xfId="322" xr:uid="{CB4CDD68-AB2B-426A-B70F-273814B60C47}"/>
+    <cellStyle name="Normal 3 6 2" xfId="1689" xr:uid="{8B69C702-1125-4A0E-AC89-803691977F0A}"/>
+    <cellStyle name="Normal 3 7" xfId="120" xr:uid="{3264F666-3AC6-45BB-9D38-8042722153E4}"/>
+    <cellStyle name="Normal 3 7 2" xfId="1489" xr:uid="{96609597-19E9-4CE8-82E0-44A3D18E63E3}"/>
+    <cellStyle name="Normal 3 8" xfId="1010" xr:uid="{F006ECAE-AABD-4F6F-B45E-B8ACCC2452F4}"/>
+    <cellStyle name="Normal 3 9" xfId="1421" xr:uid="{FAF37699-3ABE-487C-BD8F-1AEF66781F22}"/>
+    <cellStyle name="Normal 4" xfId="61" xr:uid="{914F1F41-6A55-4116-9DB1-ADD70E466C8A}"/>
+    <cellStyle name="Normal 4 10" xfId="1435" xr:uid="{39CEDBD5-B502-4B50-ADC1-747F7D54D566}"/>
+    <cellStyle name="Normal 4 11" xfId="2341" xr:uid="{4C30037C-6C0D-404A-947E-04BDF72875B8}"/>
+    <cellStyle name="Normal 4 2" xfId="252" xr:uid="{7CAAD342-0BCF-4C44-8F47-4DE565A98AF3}"/>
+    <cellStyle name="Normal 4 2 2" xfId="529" xr:uid="{4D632829-F440-42D7-AE8A-09FD76D105BC}"/>
+    <cellStyle name="Normal 4 2 2 2" xfId="911" xr:uid="{583B6DB5-4A3E-40E0-BFE9-4658AE1D568D}"/>
+    <cellStyle name="Normal 4 2 2 2 2" xfId="2267" xr:uid="{5366787F-0944-4780-A9F1-2BADB479D166}"/>
+    <cellStyle name="Normal 4 2 2 3" xfId="1296" xr:uid="{6EE3E87F-AE33-408D-958B-D54DC1FF535C}"/>
+    <cellStyle name="Normal 4 2 2 4" xfId="1887" xr:uid="{8D15E1D6-E56C-43BD-877F-48C49E1C3F29}"/>
+    <cellStyle name="Normal 4 2 3" xfId="627" xr:uid="{862E0887-5FB1-4AFC-B46C-224239595CD6}"/>
+    <cellStyle name="Normal 4 2 3 2" xfId="1985" xr:uid="{6B166E64-8F7A-42A5-ACCC-FD65AEFAA54C}"/>
+    <cellStyle name="Normal 4 2 4" xfId="769" xr:uid="{500BF709-8B90-45FA-ADDB-04861FB832C0}"/>
+    <cellStyle name="Normal 4 2 4 2" xfId="2127" xr:uid="{3C7230D9-EF6E-4644-851C-69BB166A7DD5}"/>
+    <cellStyle name="Normal 4 2 5" xfId="380" xr:uid="{6D826424-F246-4263-A144-B147DF1B1191}"/>
+    <cellStyle name="Normal 4 2 5 2" xfId="1747" xr:uid="{33563E5C-320E-457B-B9A2-66001ECEF83B}"/>
+    <cellStyle name="Normal 4 2 6" xfId="1152" xr:uid="{F9365238-4696-44EE-ADEE-30B9922C8862}"/>
+    <cellStyle name="Normal 4 2 7" xfId="1619" xr:uid="{41C46DAB-6055-4251-84E8-D19BDE2BFDB0}"/>
+    <cellStyle name="Normal 4 3" xfId="206" xr:uid="{DD45D009-F732-4A51-B031-FE6BA81538A7}"/>
+    <cellStyle name="Normal 4 3 2" xfId="854" xr:uid="{2B6D85BA-A4EA-4DFD-A268-6948067F58B8}"/>
+    <cellStyle name="Normal 4 3 2 2" xfId="2211" xr:uid="{E0638409-387B-4D8E-9DAF-524466403CA1}"/>
+    <cellStyle name="Normal 4 3 3" xfId="466" xr:uid="{F734329F-8F87-422B-A4E0-95EAE3AEDFF3}"/>
+    <cellStyle name="Normal 4 3 3 2" xfId="1831" xr:uid="{B51BF7DB-0673-4B11-98DD-298429B8B03B}"/>
+    <cellStyle name="Normal 4 3 4" xfId="1096" xr:uid="{02B00CD8-DF0B-4DA2-990F-89734D14633E}"/>
+    <cellStyle name="Normal 4 3 5" xfId="1575" xr:uid="{501100B8-433E-4183-8AC9-75DB96633BC9}"/>
+    <cellStyle name="Normal 4 4" xfId="571" xr:uid="{0350FA68-8467-4DDF-A521-25BFC6812009}"/>
+    <cellStyle name="Normal 4 4 2" xfId="1225" xr:uid="{333B9C67-A41B-478E-9A87-FF89F22B09F1}"/>
+    <cellStyle name="Normal 4 4 3" xfId="1929" xr:uid="{5778EBE7-1F29-44E3-A11D-3EC90C4FD8D2}"/>
+    <cellStyle name="Normal 4 5" xfId="725" xr:uid="{31495AB2-DA2A-4182-B963-8ED44CDEED7F}"/>
+    <cellStyle name="Normal 4 5 2" xfId="2083" xr:uid="{A59412A1-84A8-4845-AD6C-0618941DA7BF}"/>
+    <cellStyle name="Normal 4 6" xfId="336" xr:uid="{1DCF4E50-068B-4836-8CC7-76B091F3DF0F}"/>
+    <cellStyle name="Normal 4 6 2" xfId="1703" xr:uid="{ECA8D356-C896-4CDA-B6D3-F5E728C74F36}"/>
+    <cellStyle name="Normal 4 7" xfId="122" xr:uid="{30FC1A9C-64ED-439C-8FBF-F09738A43A57}"/>
+    <cellStyle name="Normal 4 7 2" xfId="1491" xr:uid="{1F637986-EE47-40D5-B47E-82CB1E2F44BE}"/>
+    <cellStyle name="Normal 4 8" xfId="65" xr:uid="{DC119B60-0624-4301-B76A-9295E621629B}"/>
+    <cellStyle name="Normal 4 9" xfId="1012" xr:uid="{8F35A796-1AEF-45C9-9A79-CB5347D14C4E}"/>
+    <cellStyle name="Normal 5" xfId="79" xr:uid="{DD2C7A1D-BE81-480D-9065-C297FEF8C9EF}"/>
+    <cellStyle name="Normal 5 2" xfId="266" xr:uid="{353983E8-184E-4716-8382-21F8A09A3848}"/>
+    <cellStyle name="Normal 5 2 2" xfId="543" xr:uid="{3B720788-2765-4642-98D3-12F025E59E40}"/>
+    <cellStyle name="Normal 5 2 2 2" xfId="925" xr:uid="{BAC7C882-B882-42A9-A0B3-1123A7A587D3}"/>
+    <cellStyle name="Normal 5 2 2 2 2" xfId="2281" xr:uid="{1229CEBA-3575-4FED-8737-EE70F941BEDF}"/>
+    <cellStyle name="Normal 5 2 2 3" xfId="1310" xr:uid="{2AD8BB40-77A5-456C-AC3E-509A90C7CEB1}"/>
+    <cellStyle name="Normal 5 2 2 4" xfId="1901" xr:uid="{3389E577-382C-4536-9748-F01CAF58D7CC}"/>
+    <cellStyle name="Normal 5 2 3" xfId="641" xr:uid="{08AE72E9-4080-4735-B131-93775D2F61B7}"/>
+    <cellStyle name="Normal 5 2 3 2" xfId="1999" xr:uid="{1C5A0916-FA75-4B73-A721-82C077B9AE53}"/>
+    <cellStyle name="Normal 5 2 4" xfId="783" xr:uid="{DCABE3E6-D099-4D46-8C82-3D43625CE427}"/>
+    <cellStyle name="Normal 5 2 4 2" xfId="2141" xr:uid="{D1B77F91-3BDB-4EF8-972A-C7DB7EF7B4B2}"/>
+    <cellStyle name="Normal 5 2 5" xfId="394" xr:uid="{3FE78661-2D13-42E4-9EDE-FCD5A9E22280}"/>
+    <cellStyle name="Normal 5 2 5 2" xfId="1761" xr:uid="{7820618C-98C5-4F24-BCF7-85CC987A8506}"/>
+    <cellStyle name="Normal 5 2 6" xfId="1166" xr:uid="{76868472-77B9-42BC-820B-3D12AE6F9C4C}"/>
+    <cellStyle name="Normal 5 2 7" xfId="1633" xr:uid="{9C8C58D7-A593-4F69-BCDA-5B2BD235057F}"/>
+    <cellStyle name="Normal 5 3" xfId="220" xr:uid="{632E516B-8024-430B-A764-265947E10590}"/>
+    <cellStyle name="Normal 5 3 2" xfId="868" xr:uid="{69B3F3F5-81D8-46F2-83A1-F0F11A599D38}"/>
+    <cellStyle name="Normal 5 3 2 2" xfId="2225" xr:uid="{41AE094E-530F-4464-A0CF-4596E1C01D92}"/>
+    <cellStyle name="Normal 5 3 3" xfId="480" xr:uid="{F10B04BD-F6C8-4C05-BC38-1692B2F558C0}"/>
+    <cellStyle name="Normal 5 3 3 2" xfId="1845" xr:uid="{B608A114-AD43-43B8-BB9B-5BB6E2194C42}"/>
+    <cellStyle name="Normal 5 3 4" xfId="1110" xr:uid="{E2442559-6AB3-4FC2-AC15-23B6F5072004}"/>
+    <cellStyle name="Normal 5 3 5" xfId="1589" xr:uid="{8FFC5649-1111-4EA8-9EFB-859CCDBCD838}"/>
+    <cellStyle name="Normal 5 4" xfId="585" xr:uid="{D2CE9D20-3B18-466E-84F6-DB5E3CD9A348}"/>
+    <cellStyle name="Normal 5 4 2" xfId="1239" xr:uid="{E39395F3-31F2-4A70-992D-4A41EDA2E7EB}"/>
+    <cellStyle name="Normal 5 4 3" xfId="1943" xr:uid="{B5A89D91-B8EB-4857-A7F5-AA54DC0F9355}"/>
+    <cellStyle name="Normal 5 5" xfId="739" xr:uid="{05AE7399-CBDD-45FD-BF08-3234EA9A43F3}"/>
+    <cellStyle name="Normal 5 5 2" xfId="2097" xr:uid="{5C344481-E58B-4D7D-93F5-483664C529E0}"/>
+    <cellStyle name="Normal 5 6" xfId="350" xr:uid="{A8455228-BE14-4263-85CE-57A2DDD39725}"/>
+    <cellStyle name="Normal 5 6 2" xfId="1717" xr:uid="{2A707284-8BCA-48C8-AD37-AF3415C3C879}"/>
+    <cellStyle name="Normal 5 7" xfId="136" xr:uid="{3420D154-F72C-4A87-9D0A-55C1E2C64A96}"/>
+    <cellStyle name="Normal 5 7 2" xfId="1505" xr:uid="{DF272C17-F160-48EE-92A4-1011ED2684C2}"/>
+    <cellStyle name="Normal 5 8" xfId="1026" xr:uid="{2E4F58EA-4920-4A8D-9452-2431661EB8FB}"/>
+    <cellStyle name="Normal 5 9" xfId="1449" xr:uid="{8D6AB7D3-59BB-482F-8F59-5A8CDC1A4D8C}"/>
+    <cellStyle name="Normal 6" xfId="93" xr:uid="{8A6D01CD-757C-45BC-9CE1-293C41DD86C3}"/>
+    <cellStyle name="Normal 6 2" xfId="234" xr:uid="{450B582B-E974-41B8-B558-F848CEC727C1}"/>
+    <cellStyle name="Normal 6 2 2" xfId="655" xr:uid="{055D9939-E6EB-4535-8E01-89992B974EA8}"/>
+    <cellStyle name="Normal 6 2 2 2" xfId="2013" xr:uid="{FEFCCA76-2D31-44EE-BBC8-93D2281B332E}"/>
+    <cellStyle name="Normal 6 2 3" xfId="882" xr:uid="{19542ED4-5AF0-4384-AEBE-4D5A8FA3E925}"/>
+    <cellStyle name="Normal 6 2 4" xfId="494" xr:uid="{97AF7393-4E81-4111-AE08-BEB3525C2075}"/>
+    <cellStyle name="Normal 6 2 5" xfId="1603" xr:uid="{76827F1C-8402-470A-9FD2-25046AA6B75D}"/>
+    <cellStyle name="Normal 6 2 6" xfId="2343" xr:uid="{723D632E-502F-4635-8EF5-8BACDE06DF2A}"/>
+    <cellStyle name="Normal 6 3" xfId="599" xr:uid="{0A1370C8-A548-4556-9EB4-0BF0C25A323B}"/>
+    <cellStyle name="Normal 6 3 2" xfId="1253" xr:uid="{D6440B4F-DA3D-42A9-AC2B-7FD274B91435}"/>
+    <cellStyle name="Normal 6 3 3" xfId="1957" xr:uid="{DF840DF9-55C9-4F48-923B-EDF083024AD7}"/>
+    <cellStyle name="Normal 6 4" xfId="753" xr:uid="{EAA4367E-EE47-4B03-869A-899DCD526B60}"/>
+    <cellStyle name="Normal 6 4 2" xfId="2111" xr:uid="{23B5555C-407E-4692-A59C-F620DE40C804}"/>
+    <cellStyle name="Normal 6 5" xfId="364" xr:uid="{84C58B0C-80F8-4690-99A4-BCE886262574}"/>
+    <cellStyle name="Normal 6 5 2" xfId="1731" xr:uid="{7B1D1FAF-DB7A-4879-951A-816E74CF3F38}"/>
+    <cellStyle name="Normal 6 6" xfId="150" xr:uid="{BD7C51BF-2CAF-4F97-8984-7F0E9259F1A9}"/>
+    <cellStyle name="Normal 6 6 2" xfId="1519" xr:uid="{BB997B24-30BA-4DE2-AC96-A9EFBE192C2B}"/>
+    <cellStyle name="Normal 6 7" xfId="1040" xr:uid="{9552C1F2-D24B-46EE-9DD3-C4E0783CDF61}"/>
+    <cellStyle name="Normal 6 8" xfId="1463" xr:uid="{8D131188-A857-42C9-99D9-CDB83514FACF}"/>
+    <cellStyle name="Normal 7" xfId="164" xr:uid="{4BA79920-0D3A-44CC-9542-BBDAA591B3C1}"/>
+    <cellStyle name="Normal 7 2" xfId="293" xr:uid="{283F6D47-EADC-42AA-A0EE-024E5F8826E4}"/>
+    <cellStyle name="Normal 7 2 2" xfId="510" xr:uid="{DA6FC034-7FD7-4A6C-A5B6-66221E628BCA}"/>
+    <cellStyle name="Normal 7 2 3" xfId="1660" xr:uid="{CEF7E030-7F84-419A-A3A5-281DA1EC5D53}"/>
+    <cellStyle name="Normal 7 3" xfId="669" xr:uid="{F616AA93-B56C-40D2-B5C6-6E46C6FB988E}"/>
+    <cellStyle name="Normal 7 3 2" xfId="2027" xr:uid="{718C57F8-3433-4099-A2DC-CE5495C9D469}"/>
+    <cellStyle name="Normal 7 4" xfId="810" xr:uid="{265E8014-9653-405A-A6BB-4E5ED29A6176}"/>
+    <cellStyle name="Normal 7 4 2" xfId="2168" xr:uid="{8E65E41D-9672-4E11-8E84-A8937B455A9B}"/>
+    <cellStyle name="Normal 7 5" xfId="421" xr:uid="{A3837456-6B85-4CEF-8DC9-31E8E33C181D}"/>
+    <cellStyle name="Normal 7 5 2" xfId="1788" xr:uid="{B74A8DFF-1A96-4792-BB03-850D9DA43F5C}"/>
+    <cellStyle name="Normal 7 6" xfId="1054" xr:uid="{C3E617BC-5DB8-4AB8-9A30-FF4FE6EA0119}"/>
+    <cellStyle name="Normal 7 7" xfId="1533" xr:uid="{F1AA894A-02EE-4905-9A95-83533F624EA2}"/>
+    <cellStyle name="Normal 7 8" xfId="2342" xr:uid="{6A37F746-5B2A-4742-876D-9BCF820A2B1C}"/>
+    <cellStyle name="Normal 8" xfId="236" xr:uid="{E12C7BDC-724F-47B2-BD6F-B85038B32904}"/>
+    <cellStyle name="Normal 8 2" xfId="1267" xr:uid="{B0D7B484-1F37-48F8-86D6-3F2464072AC4}"/>
+    <cellStyle name="Normal 8 3" xfId="1180" xr:uid="{15AE45EF-FDC7-49CC-AF4E-653E2AB7E39E}"/>
+    <cellStyle name="Normal 9" xfId="294" xr:uid="{E116F996-DBAE-4C8F-8EE7-4D7D389E2599}"/>
+    <cellStyle name="Normal 9 2" xfId="683" xr:uid="{C62ADF0A-8E61-4F5F-927E-16C20EA94C43}"/>
+    <cellStyle name="Normal 9 2 2" xfId="2041" xr:uid="{3D20F9B0-807F-42B5-8137-A1A314670548}"/>
+    <cellStyle name="Normal 9 3" xfId="811" xr:uid="{4087B3F3-6497-4B19-9E38-A986BEBFD572}"/>
+    <cellStyle name="Normal 9 3 2" xfId="2169" xr:uid="{310A5359-3DEF-43CC-AC2D-1C8AB4497B65}"/>
+    <cellStyle name="Normal 9 4" xfId="422" xr:uid="{4BCD53C1-7B93-440F-9BEA-CDCC1788472B}"/>
+    <cellStyle name="Normal 9 4 2" xfId="1789" xr:uid="{6A0B4C0A-D5D4-4CD5-800D-A3FDFCDA6E45}"/>
+    <cellStyle name="Normal 9 5" xfId="1324" xr:uid="{463A5F16-1BE2-4AC5-80BF-F51C58902EA5}"/>
+    <cellStyle name="Normal 9 6" xfId="1661" xr:uid="{E4A535C8-4A03-4150-BCE9-857AD1CB8351}"/>
+    <cellStyle name="Note" xfId="13" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Note 10" xfId="968" xr:uid="{7B3EB9F0-A9CD-463D-954A-81D6E1AA5E49}"/>
+    <cellStyle name="Note 10 2" xfId="1353" xr:uid="{EC94591C-3887-4359-8F7B-182846FC960E}"/>
+    <cellStyle name="Note 10 3" xfId="2324" xr:uid="{C7DE3E25-2B0A-4CEC-B6FB-A9963E4969E3}"/>
+    <cellStyle name="Note 11" xfId="984" xr:uid="{3D55D56A-5344-45FC-B511-22CEABA8548E}"/>
+    <cellStyle name="Note 11 2" xfId="1366" xr:uid="{4F5803E0-38BE-4128-B78F-1CB76124031A}"/>
+    <cellStyle name="Note 12" xfId="997" xr:uid="{207B6D7F-B730-4591-BC02-F9B67D4567DF}"/>
+    <cellStyle name="Note 13" xfId="1393" xr:uid="{56B4118A-3540-47BE-B83E-6A352431D1F8}"/>
+    <cellStyle name="Note 2" xfId="46" xr:uid="{FBE6E1B6-F9A7-44B2-B0D4-15CBB5F1E734}"/>
+    <cellStyle name="Note 2 10" xfId="1420" xr:uid="{FF1BB032-4F4D-452D-9BF2-BC2090DFB4BF}"/>
+    <cellStyle name="Note 2 2" xfId="251" xr:uid="{A4ADA102-07D3-407C-A362-92C77F1F010E}"/>
+    <cellStyle name="Note 2 2 2" xfId="514" xr:uid="{1B06AC5C-ED3B-4FD5-81DA-621E57487C5D}"/>
+    <cellStyle name="Note 2 2 2 2" xfId="896" xr:uid="{F09FFC67-5D80-421D-B76D-509B9EAF9FCB}"/>
+    <cellStyle name="Note 2 2 2 2 2" xfId="2252" xr:uid="{E17F3985-DB77-4A1C-B075-16CF0B5FB601}"/>
+    <cellStyle name="Note 2 2 2 3" xfId="1281" xr:uid="{E7F2F67A-D837-4389-9C6A-7EA8CF3AE0B7}"/>
+    <cellStyle name="Note 2 2 2 4" xfId="1872" xr:uid="{902F1C32-E2A2-4474-88AC-4B57460F4497}"/>
+    <cellStyle name="Note 2 2 3" xfId="626" xr:uid="{0B63044B-A581-4AFA-8122-91C9E31C9A07}"/>
+    <cellStyle name="Note 2 2 3 2" xfId="1984" xr:uid="{DBEA24EF-0980-4875-AC09-33D1CC2570EB}"/>
+    <cellStyle name="Note 2 2 4" xfId="768" xr:uid="{4F61C104-23F8-4D00-B70E-C97767ACAF7C}"/>
+    <cellStyle name="Note 2 2 4 2" xfId="2126" xr:uid="{B24DE345-853E-4D25-A049-0FC425EC4AC9}"/>
+    <cellStyle name="Note 2 2 5" xfId="379" xr:uid="{A9C8BB96-3E2F-4A71-A3AE-687B850E0FD5}"/>
+    <cellStyle name="Note 2 2 5 2" xfId="1746" xr:uid="{9FBC4A52-8461-49E6-AAF3-30CB4EFFB091}"/>
+    <cellStyle name="Note 2 2 6" xfId="1137" xr:uid="{B015DCFA-1309-4D93-8C7A-4603F8320D24}"/>
+    <cellStyle name="Note 2 2 7" xfId="1618" xr:uid="{66E03FCB-06CE-426F-ABF9-41B432A0C964}"/>
+    <cellStyle name="Note 2 3" xfId="191" xr:uid="{DE69B409-C9C5-432B-A36E-CA0AE72B29FF}"/>
+    <cellStyle name="Note 2 3 2" xfId="839" xr:uid="{EDA5F310-74AC-41A6-BA1C-6C4B5F99EF8A}"/>
+    <cellStyle name="Note 2 3 2 2" xfId="2196" xr:uid="{FF2D257D-A5F0-4E32-90DA-3C0EF687813C}"/>
+    <cellStyle name="Note 2 3 3" xfId="451" xr:uid="{F7806E85-E429-4D1E-A06A-DF5AFD1D5550}"/>
+    <cellStyle name="Note 2 3 3 2" xfId="1816" xr:uid="{76E94441-E83E-4BC1-BAD9-4380B777211D}"/>
+    <cellStyle name="Note 2 3 4" xfId="1081" xr:uid="{A891223B-A779-4965-A9A5-6C449898A496}"/>
+    <cellStyle name="Note 2 3 5" xfId="1560" xr:uid="{05676976-765B-4562-B303-AADA520E64D4}"/>
+    <cellStyle name="Note 2 4" xfId="570" xr:uid="{89268B5D-834C-437D-A1D9-0C095C8E412D}"/>
+    <cellStyle name="Note 2 4 2" xfId="1210" xr:uid="{021C617C-8739-4C0E-9F7E-F6A7646E397A}"/>
+    <cellStyle name="Note 2 4 3" xfId="1928" xr:uid="{D238EC44-3BE1-4C1E-ACC6-31890F076C8E}"/>
+    <cellStyle name="Note 2 5" xfId="710" xr:uid="{98986D82-9407-4BDC-9F4F-59D59AAB9515}"/>
+    <cellStyle name="Note 2 5 2" xfId="2068" xr:uid="{A28109BB-CD26-4872-B918-0D2697D41ADA}"/>
+    <cellStyle name="Note 2 6" xfId="321" xr:uid="{57343154-94D9-4F44-91F8-321EF0F0ACFA}"/>
+    <cellStyle name="Note 2 6 2" xfId="1688" xr:uid="{9CFA0AA7-857F-4B32-BA3B-CCB8674DA3E2}"/>
+    <cellStyle name="Note 2 7" xfId="121" xr:uid="{71712658-628C-4E3B-8F57-0D36CE85558F}"/>
+    <cellStyle name="Note 2 7 2" xfId="1490" xr:uid="{BF0611CC-93E7-4A0A-B928-CEF9B7E4C717}"/>
+    <cellStyle name="Note 2 8" xfId="63" xr:uid="{B68B84AC-6AC1-40BC-A9B7-01A6C744D16A}"/>
+    <cellStyle name="Note 2 9" xfId="1011" xr:uid="{BFF333A9-DD03-43BD-9536-449F307E5ADF}"/>
+    <cellStyle name="Note 3" xfId="48" xr:uid="{F6D8F0B1-9C94-4A17-884A-3827A7CD5256}"/>
+    <cellStyle name="Note 3 2" xfId="253" xr:uid="{F7042367-3EE9-4968-AB45-610E9E9C18C7}"/>
+    <cellStyle name="Note 3 2 2" xfId="516" xr:uid="{D513E21B-19CB-458B-B3CD-699A7941BAAC}"/>
+    <cellStyle name="Note 3 2 2 2" xfId="898" xr:uid="{822FCE50-7CAE-4735-80BC-6D088EEB52BC}"/>
+    <cellStyle name="Note 3 2 2 2 2" xfId="2254" xr:uid="{E0ED3885-D3E4-4CC3-8555-FEDBF875C096}"/>
+    <cellStyle name="Note 3 2 2 3" xfId="1283" xr:uid="{ADFBFA15-E6B9-49B1-BDDC-F0ACC3D3BADC}"/>
+    <cellStyle name="Note 3 2 2 4" xfId="1874" xr:uid="{DD9BF97E-2A0B-4E9C-BD41-048101B3A94F}"/>
+    <cellStyle name="Note 3 2 3" xfId="628" xr:uid="{2E81B982-1657-40CD-8A47-DAFBB3E93BC9}"/>
+    <cellStyle name="Note 3 2 3 2" xfId="1986" xr:uid="{A29980FA-B46F-4ECB-AC56-9AC2D540021A}"/>
+    <cellStyle name="Note 3 2 4" xfId="770" xr:uid="{B12F6913-57EC-493B-89E6-40F656890F9F}"/>
+    <cellStyle name="Note 3 2 4 2" xfId="2128" xr:uid="{B2A87A8E-0D41-4F7B-B4DC-C6539D7620E7}"/>
+    <cellStyle name="Note 3 2 5" xfId="381" xr:uid="{D3A4AC91-189A-4413-8F2D-0D1064F165A8}"/>
+    <cellStyle name="Note 3 2 5 2" xfId="1748" xr:uid="{A986601F-A26A-4E5C-8C16-91C5CC423CA4}"/>
+    <cellStyle name="Note 3 2 6" xfId="1139" xr:uid="{36F2D24A-4CCA-4C4B-B78B-3D00B37BCA85}"/>
+    <cellStyle name="Note 3 2 7" xfId="1620" xr:uid="{DA21E6A8-D34E-49D6-B133-6BA87E1FC365}"/>
+    <cellStyle name="Note 3 3" xfId="193" xr:uid="{8B2CBA3B-A748-4719-8384-648023B82FD0}"/>
+    <cellStyle name="Note 3 3 2" xfId="841" xr:uid="{FE542177-6165-43EC-87AE-C203E86FB4E0}"/>
+    <cellStyle name="Note 3 3 2 2" xfId="2198" xr:uid="{4693454D-A9A4-4A21-A662-B2C874932C46}"/>
+    <cellStyle name="Note 3 3 3" xfId="453" xr:uid="{B58466DF-0371-4F04-88B7-5037459CD3D3}"/>
+    <cellStyle name="Note 3 3 3 2" xfId="1818" xr:uid="{31F9F656-C87C-4E7A-9319-A1A02FCF15B2}"/>
+    <cellStyle name="Note 3 3 4" xfId="1083" xr:uid="{30621C31-2787-48BF-BCB5-5AE331D2FBE8}"/>
+    <cellStyle name="Note 3 3 5" xfId="1562" xr:uid="{8EF383A0-F0CA-47D1-8BF5-2519CA4225C1}"/>
+    <cellStyle name="Note 3 4" xfId="572" xr:uid="{3989AE22-EE8B-4BF2-86AA-B8B2E6C84820}"/>
+    <cellStyle name="Note 3 4 2" xfId="1212" xr:uid="{DF0EF205-2FBB-49A3-9ADD-396174627DF3}"/>
+    <cellStyle name="Note 3 4 3" xfId="1930" xr:uid="{D754F1E6-3ED9-4711-B284-F7EBD5B5BFBB}"/>
+    <cellStyle name="Note 3 5" xfId="712" xr:uid="{3BCA2234-C36B-4CB2-ABC1-331000FC5AF5}"/>
+    <cellStyle name="Note 3 5 2" xfId="2070" xr:uid="{86A58136-A703-49BF-BCA6-7303B4FE7014}"/>
+    <cellStyle name="Note 3 6" xfId="323" xr:uid="{DEA5C624-015C-43A1-BA6E-0F22F5CCF7EC}"/>
+    <cellStyle name="Note 3 6 2" xfId="1690" xr:uid="{A9EFA6F7-55B7-4C19-9B1C-227EFE822879}"/>
+    <cellStyle name="Note 3 7" xfId="123" xr:uid="{C474EE7A-2D7F-45A4-B6E4-8A14D39112F9}"/>
+    <cellStyle name="Note 3 7 2" xfId="1492" xr:uid="{A9136EB7-245E-4D52-8E9E-4BFB30983551}"/>
+    <cellStyle name="Note 3 8" xfId="1013" xr:uid="{D1BF42D2-47DE-4031-A0E1-B5C167CA86E1}"/>
+    <cellStyle name="Note 3 9" xfId="1422" xr:uid="{1B325E45-9D99-4412-8DE7-8C8BAF98593F}"/>
+    <cellStyle name="Note 4" xfId="66" xr:uid="{052B2D18-261B-4A1E-A210-4F7BCD440C41}"/>
+    <cellStyle name="Note 4 2" xfId="267" xr:uid="{CABEFC60-BD3B-4AE2-B170-CBEC8F02E06B}"/>
+    <cellStyle name="Note 4 2 2" xfId="530" xr:uid="{307FF9B0-71C0-4F97-9903-C07B99580774}"/>
+    <cellStyle name="Note 4 2 2 2" xfId="912" xr:uid="{51756C7A-CF5C-460D-A516-54C1117F1AAA}"/>
+    <cellStyle name="Note 4 2 2 2 2" xfId="2268" xr:uid="{F0ED9FFD-F656-419F-966D-68769C3594B2}"/>
+    <cellStyle name="Note 4 2 2 3" xfId="1297" xr:uid="{CD5B8D2F-3F9B-4F98-A3DE-D4593926535C}"/>
+    <cellStyle name="Note 4 2 2 4" xfId="1888" xr:uid="{C50DD882-E5A4-41F9-96FC-60BDBC66F051}"/>
+    <cellStyle name="Note 4 2 3" xfId="642" xr:uid="{03306B28-9E42-4E17-A768-D7FFB2DF60B0}"/>
+    <cellStyle name="Note 4 2 3 2" xfId="2000" xr:uid="{E1A93FD4-1E52-4951-B42C-66B13B9EDD59}"/>
+    <cellStyle name="Note 4 2 4" xfId="784" xr:uid="{EE349F01-B895-4ABB-A610-1BA82841272A}"/>
+    <cellStyle name="Note 4 2 4 2" xfId="2142" xr:uid="{C9356512-2B16-4EDC-A79B-C28D98B5AD26}"/>
+    <cellStyle name="Note 4 2 5" xfId="395" xr:uid="{90F8673E-140C-40CD-9A7A-39DDA5C0F3B3}"/>
+    <cellStyle name="Note 4 2 5 2" xfId="1762" xr:uid="{0CDCC185-9422-4A11-8CA6-B05E88EA3D92}"/>
+    <cellStyle name="Note 4 2 6" xfId="1153" xr:uid="{6C2635F4-BA02-4369-99C3-1B4BE2BCC805}"/>
+    <cellStyle name="Note 4 2 7" xfId="1634" xr:uid="{0003B427-D870-4686-B575-C1BF74E41DA4}"/>
+    <cellStyle name="Note 4 3" xfId="207" xr:uid="{210678A5-0DBD-4E4B-950F-FDBCE153B920}"/>
+    <cellStyle name="Note 4 3 2" xfId="855" xr:uid="{24843EA3-F434-498A-865C-3DAFF8219989}"/>
+    <cellStyle name="Note 4 3 2 2" xfId="2212" xr:uid="{F40CA8A0-821A-4FD3-A881-50231C29EF6C}"/>
+    <cellStyle name="Note 4 3 3" xfId="467" xr:uid="{2C4FE29C-582B-4D84-B24F-C9F6EFE5A996}"/>
+    <cellStyle name="Note 4 3 3 2" xfId="1832" xr:uid="{8702F993-D9D5-4E59-A5C1-26EA39503B0D}"/>
+    <cellStyle name="Note 4 3 4" xfId="1097" xr:uid="{140699AA-D246-49D4-B4DE-328297EB0821}"/>
+    <cellStyle name="Note 4 3 5" xfId="1576" xr:uid="{E33CE35D-B557-43F8-8848-8B1F4F773809}"/>
+    <cellStyle name="Note 4 4" xfId="586" xr:uid="{BFB0CB72-5AC4-4DB3-BD51-CAF6C21DB014}"/>
+    <cellStyle name="Note 4 4 2" xfId="1226" xr:uid="{BE0B9E7C-4A6E-4B49-B6D0-81EEC3F6DEB0}"/>
+    <cellStyle name="Note 4 4 3" xfId="1944" xr:uid="{F789C657-15CA-4774-99D4-8DF55C52A943}"/>
+    <cellStyle name="Note 4 5" xfId="726" xr:uid="{53E9BC0F-0E49-4F94-B75E-942C0F363CDC}"/>
+    <cellStyle name="Note 4 5 2" xfId="2084" xr:uid="{DE8D4C79-AF8F-478C-A34E-90319C70831D}"/>
+    <cellStyle name="Note 4 6" xfId="337" xr:uid="{03CA3E22-6CD1-4894-86BF-6D10A9F7617D}"/>
+    <cellStyle name="Note 4 6 2" xfId="1704" xr:uid="{CCC22675-912F-4744-AFE1-C0E40480A553}"/>
+    <cellStyle name="Note 4 7" xfId="137" xr:uid="{B3881A9B-8C46-4F1A-9BBA-E87DFA740089}"/>
+    <cellStyle name="Note 4 7 2" xfId="1506" xr:uid="{83D0832A-3D7E-4C5B-B9EB-ACE176B7A883}"/>
+    <cellStyle name="Note 4 8" xfId="1027" xr:uid="{F7A7B4E2-384D-4833-BBF3-7273F531289F}"/>
+    <cellStyle name="Note 4 9" xfId="1436" xr:uid="{2C1192F4-47B4-4A15-A4A8-E3EB6CEA119D}"/>
+    <cellStyle name="Note 5" xfId="80" xr:uid="{EFFB2324-089B-4DAA-BCE3-6422073D656C}"/>
+    <cellStyle name="Note 5 2" xfId="280" xr:uid="{41DC36F8-CCEC-45A5-96A2-5393526EF55D}"/>
+    <cellStyle name="Note 5 2 2" xfId="544" xr:uid="{7BE0C75D-A255-4FF4-B95C-D6C1674CDA92}"/>
+    <cellStyle name="Note 5 2 2 2" xfId="926" xr:uid="{E8D6B129-A888-4910-977E-59BBD2F2AC1C}"/>
+    <cellStyle name="Note 5 2 2 2 2" xfId="2282" xr:uid="{68487192-5B4D-437A-AF15-189F56981D69}"/>
+    <cellStyle name="Note 5 2 2 3" xfId="1311" xr:uid="{92984ED9-52EF-4B19-81C3-5B79DFB999A6}"/>
+    <cellStyle name="Note 5 2 2 4" xfId="1902" xr:uid="{14E8416F-A6AD-441D-83AC-3BA593B4223F}"/>
+    <cellStyle name="Note 5 2 3" xfId="656" xr:uid="{545B8BA8-0B42-48D3-8C17-00421DB587F4}"/>
+    <cellStyle name="Note 5 2 3 2" xfId="2014" xr:uid="{297E8579-66D8-4BC2-B934-89DF6A35706B}"/>
+    <cellStyle name="Note 5 2 4" xfId="797" xr:uid="{914F7C69-B5DA-4DE6-BD63-CBEB69D2B8AB}"/>
+    <cellStyle name="Note 5 2 4 2" xfId="2155" xr:uid="{2CBEADF5-DB4A-4FA5-821E-E38EE6E04777}"/>
+    <cellStyle name="Note 5 2 5" xfId="408" xr:uid="{094AB9D7-9E87-4818-B474-6BDCE460DFF1}"/>
+    <cellStyle name="Note 5 2 5 2" xfId="1775" xr:uid="{825B452D-6E1E-4FFF-ADBE-E235E1F6052F}"/>
+    <cellStyle name="Note 5 2 6" xfId="1167" xr:uid="{61F55F6E-8682-45BE-9314-66140CC0DF2D}"/>
+    <cellStyle name="Note 5 2 7" xfId="1647" xr:uid="{1BC38690-7CBC-4736-B509-B242312B0067}"/>
+    <cellStyle name="Note 5 3" xfId="221" xr:uid="{2CD1E748-A8D5-4683-9A55-E0B9FA05C2A0}"/>
+    <cellStyle name="Note 5 3 2" xfId="869" xr:uid="{F1C17448-5E6B-49D7-B311-B96002AF0C54}"/>
+    <cellStyle name="Note 5 3 2 2" xfId="2226" xr:uid="{8D50C78C-8659-4801-9A69-EE4CE2E3EB4C}"/>
+    <cellStyle name="Note 5 3 3" xfId="481" xr:uid="{2D15ED9B-D5C6-42E3-A21E-488E2BF9A3F9}"/>
+    <cellStyle name="Note 5 3 3 2" xfId="1846" xr:uid="{A72AB4B1-80C0-4A1D-82E0-9C54605A5F5E}"/>
+    <cellStyle name="Note 5 3 4" xfId="1111" xr:uid="{75FBEFF3-FC66-4090-B47B-ADC049A5EEB1}"/>
+    <cellStyle name="Note 5 3 5" xfId="1590" xr:uid="{C809BACF-07C4-421B-850E-EBCC82A70A1E}"/>
+    <cellStyle name="Note 5 4" xfId="600" xr:uid="{3088909F-4153-49E8-A252-36020C36ED4B}"/>
+    <cellStyle name="Note 5 4 2" xfId="1240" xr:uid="{67AFC4AD-4756-434D-89BD-B338883AF131}"/>
+    <cellStyle name="Note 5 4 3" xfId="1958" xr:uid="{1373FF79-6A84-4E6E-BB05-49569C3376D0}"/>
+    <cellStyle name="Note 5 5" xfId="740" xr:uid="{CF873007-7E02-47CF-B8CF-B90331E779AA}"/>
+    <cellStyle name="Note 5 5 2" xfId="2098" xr:uid="{822387C9-3512-496F-ACBF-B3BF854D96F7}"/>
+    <cellStyle name="Note 5 6" xfId="351" xr:uid="{29C90D94-2638-4276-A3BD-3E94630644E0}"/>
+    <cellStyle name="Note 5 6 2" xfId="1718" xr:uid="{C90ACA42-7FA7-4C13-AAF2-B779E9B8C349}"/>
+    <cellStyle name="Note 5 7" xfId="151" xr:uid="{71D0F71C-401C-4C8B-B2F1-4ACB5A353651}"/>
+    <cellStyle name="Note 5 7 2" xfId="1520" xr:uid="{52057838-1E97-48E2-B60B-BC8A3F645EFF}"/>
+    <cellStyle name="Note 5 8" xfId="1041" xr:uid="{46431B20-46CF-4C62-A3D4-AB918D3B7F7A}"/>
+    <cellStyle name="Note 5 9" xfId="1450" xr:uid="{88C963C4-E01E-4365-AF86-F81489C65ECF}"/>
+    <cellStyle name="Note 6" xfId="94" xr:uid="{06696849-6F4E-4777-9083-33AB116599AC}"/>
+    <cellStyle name="Note 6 2" xfId="237" xr:uid="{55ABF390-BD6C-4BFB-AED0-9134D78F23AB}"/>
+    <cellStyle name="Note 6 2 2" xfId="670" xr:uid="{4181B09C-DA2A-4023-AAB7-42E4E3989D81}"/>
+    <cellStyle name="Note 6 2 2 2" xfId="2028" xr:uid="{E587BCE4-9D6D-4C73-A7A6-30F99AEF08C2}"/>
+    <cellStyle name="Note 6 2 3" xfId="1254" xr:uid="{AE2F2EB7-A421-4B85-85D7-50B55174790D}"/>
+    <cellStyle name="Note 6 2 4" xfId="1604" xr:uid="{E1E7F2AD-468B-417B-9CA6-1F41F9310911}"/>
+    <cellStyle name="Note 6 3" xfId="754" xr:uid="{25A7DB65-96B6-4E72-91C9-A618C5629F0D}"/>
+    <cellStyle name="Note 6 3 2" xfId="2112" xr:uid="{0C18EB1A-D6E1-4D58-BC72-EC41C5801F57}"/>
+    <cellStyle name="Note 6 4" xfId="365" xr:uid="{EA0E6840-0076-4C59-85A3-9C314FE65241}"/>
+    <cellStyle name="Note 6 4 2" xfId="1732" xr:uid="{FACB9C45-D7AD-4D67-A8AC-9485730B54D4}"/>
+    <cellStyle name="Note 6 5" xfId="165" xr:uid="{C20ED99C-F6AE-404E-B180-FBA881AE54BB}"/>
+    <cellStyle name="Note 6 5 2" xfId="1534" xr:uid="{9D29D67F-B8B5-44DE-9764-B6A543D436F4}"/>
+    <cellStyle name="Note 6 6" xfId="1055" xr:uid="{688995A7-F652-41D4-86A0-55054DFCDB45}"/>
+    <cellStyle name="Note 6 7" xfId="1464" xr:uid="{84794E29-B8D6-45D0-BEBA-E6E8F5F35BC4}"/>
+    <cellStyle name="Note 7" xfId="295" xr:uid="{AB17DC34-3061-4C9C-AB2A-BDB997314936}"/>
+    <cellStyle name="Note 7 2" xfId="684" xr:uid="{8AE5573D-3675-4350-8226-3A84E86BFF4C}"/>
+    <cellStyle name="Note 7 2 2" xfId="1325" xr:uid="{595F5F9C-D107-4695-8943-8CF40CED9D47}"/>
+    <cellStyle name="Note 7 2 3" xfId="2042" xr:uid="{8933ABA8-C1BE-4D21-9B48-7B6F8464114F}"/>
+    <cellStyle name="Note 7 3" xfId="812" xr:uid="{988609AF-BEC9-4119-8C28-9F2860874525}"/>
+    <cellStyle name="Note 7 3 2" xfId="2170" xr:uid="{99CF826E-1EE2-4632-8D01-F6E5FD801051}"/>
+    <cellStyle name="Note 7 4" xfId="423" xr:uid="{5493AA3B-E8F4-456A-A008-EF8F0A91B83A}"/>
+    <cellStyle name="Note 7 4 2" xfId="1790" xr:uid="{2D17706F-F45A-4A35-A576-88D0634E9681}"/>
+    <cellStyle name="Note 7 5" xfId="1181" xr:uid="{2E90A41D-3A70-49F6-A340-3AF786856C6C}"/>
+    <cellStyle name="Note 7 6" xfId="1662" xr:uid="{1088D2DF-6878-4E56-98CC-6EECE09DE6DC}"/>
+    <cellStyle name="Note 8" xfId="940" xr:uid="{7CD145B8-BF55-4E1D-88D2-E4AF6B0709ED}"/>
+    <cellStyle name="Note 8 2" xfId="1195" xr:uid="{0E756EFB-2E94-4CA6-9014-4CD52B907FC2}"/>
+    <cellStyle name="Note 8 3" xfId="2296" xr:uid="{0084C19D-1B0D-4111-8675-9F96FD311276}"/>
+    <cellStyle name="Note 9" xfId="954" xr:uid="{D3620995-D11A-4F1A-A930-0572776CB3C1}"/>
+    <cellStyle name="Note 9 2" xfId="1339" xr:uid="{D4243E55-5EF8-4DE1-A242-5FFD048942C1}"/>
+    <cellStyle name="Note 9 3" xfId="2310" xr:uid="{191944C4-B937-4E31-9A1D-245659A65E94}"/>
+    <cellStyle name="Output" xfId="8" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Percent 2" xfId="235" xr:uid="{022198AA-F5CA-4B97-B0A5-47445C6D531B}"/>
+    <cellStyle name="Percent 2 2" xfId="497" xr:uid="{36E065EA-F918-44C2-B48C-85B8A28598F1}"/>
+    <cellStyle name="Percent 2 3" xfId="512" xr:uid="{E13671CC-33F7-46E5-A629-D016FA466C21}"/>
+    <cellStyle name="Percent 3" xfId="2339" xr:uid="{FED0F976-7C83-463C-916D-6954FC557426}"/>
+    <cellStyle name="Title 2" xfId="34" xr:uid="{BC54CB54-02C0-4070-BFC5-10AA3F4B01DB}"/>
+    <cellStyle name="Total" xfId="15" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="12" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -440,7 +5590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1C875C-CB7D-4A19-8DE8-50CDE760ECA2}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" customWidth="1"/>
@@ -479,7 +5629,7 @@
       <c r="C2">
         <v>85858982.425728291</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>11.1675025489292</v>
       </c>
       <c r="E2">
@@ -499,7 +5649,7 @@
       <c r="C3">
         <v>66509385.460622221</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>8.6560281841141009</v>
       </c>
       <c r="E3">
@@ -519,7 +5669,7 @@
       <c r="C4">
         <v>10521598.33745534</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>1.368522814185275</v>
       </c>
       <c r="E4">
@@ -539,7 +5689,7 @@
       <c r="C5">
         <v>10603501.62759142</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>1.379175807914284</v>
       </c>
       <c r="E5">
@@ -547,6 +5697,406 @@
       </c>
       <c r="F5">
         <v>2024</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>80</v>
+      </c>
+      <c r="C6" s="1">
+        <v>84085730.401156649</v>
+      </c>
+      <c r="D6" s="5">
+        <v>10.93685927847782</v>
+      </c>
+      <c r="E6" s="6">
+        <v>49.479290240914771</v>
+      </c>
+      <c r="F6">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
+        <v>7295</v>
+      </c>
+      <c r="C7" s="1">
+        <v>65864604.887095042</v>
+      </c>
+      <c r="D7" s="5">
+        <v>8.5668746842780834</v>
+      </c>
+      <c r="E7" s="6">
+        <v>38.757276487508747</v>
+      </c>
+      <c r="F7">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1">
+        <v>255</v>
+      </c>
+      <c r="C8" s="1">
+        <v>9954950.8854382019</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.2948201370050549</v>
+      </c>
+      <c r="E8" s="6">
+        <v>5.85787745250855</v>
+      </c>
+      <c r="F8">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6276</v>
+      </c>
+      <c r="C9" s="1">
+        <v>10035976.1034023</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1.3053589216793819</v>
+      </c>
+      <c r="E9" s="6">
+        <v>5.9055558190679216</v>
+      </c>
+      <c r="F9">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1">
+        <v>75</v>
+      </c>
+      <c r="C10" s="1">
+        <v>66678668.680909157</v>
+      </c>
+      <c r="D10" s="5">
+        <v>8.6727582998948218</v>
+      </c>
+      <c r="E10" s="6">
+        <v>43.901780129389479</v>
+      </c>
+      <c r="F10">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1">
+        <v>7254</v>
+      </c>
+      <c r="C11" s="1">
+        <v>65505876.649254672</v>
+      </c>
+      <c r="D11" s="5">
+        <v>8.5202156347846802</v>
+      </c>
+      <c r="E11" s="6">
+        <v>43.129604275705461</v>
+      </c>
+      <c r="F11">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1810</v>
+      </c>
+      <c r="C12" s="1">
+        <v>10775812.920727581</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.401587986010757</v>
+      </c>
+      <c r="E12" s="6">
+        <v>7.0948832500710051</v>
+      </c>
+      <c r="F12">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1">
+        <v>4253</v>
+      </c>
+      <c r="C13" s="1">
+        <v>8921110.9842751995</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1.160350691814392</v>
+      </c>
+      <c r="E13" s="6">
+        <v>5.8737323448340781</v>
+      </c>
+      <c r="F13">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="1">
+        <v>75</v>
+      </c>
+      <c r="C14" s="1">
+        <v>66880818.999995738</v>
+      </c>
+      <c r="D14" s="5">
+        <v>8.6990515830709683</v>
+      </c>
+      <c r="E14" s="6">
+        <v>44.062138573522283</v>
+      </c>
+      <c r="F14">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="1">
+        <v>6686</v>
+      </c>
+      <c r="C15" s="1">
+        <v>63889747.00310646</v>
+      </c>
+      <c r="D15" s="5">
+        <v>8.3060437603354309</v>
+      </c>
+      <c r="E15" s="6">
+        <v>42.091573159089698</v>
+      </c>
+      <c r="F15">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2323</v>
+      </c>
+      <c r="C16" s="1">
+        <v>12274083.82762666</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1.5964650246204113</v>
+      </c>
+      <c r="E16" s="6">
+        <v>8.0863600440650885</v>
+      </c>
+      <c r="F16">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2970</v>
+      </c>
+      <c r="C17" s="1">
+        <v>8742851.1059269998</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1.1371647938936407</v>
+      </c>
+      <c r="E17" s="6">
+        <v>5.7599282233229321</v>
+      </c>
+      <c r="F17">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="1">
+        <v>74</v>
+      </c>
+      <c r="C18" s="1">
+        <v>66786266.178993002</v>
+      </c>
+      <c r="D18" s="5">
+        <v>8.6867532906827165</v>
+      </c>
+      <c r="E18" s="4">
+        <v>44.253232741337655</v>
+      </c>
+      <c r="F18">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="1">
+        <v>7204</v>
+      </c>
+      <c r="C19" s="1">
+        <v>66985502.981183998</v>
+      </c>
+      <c r="D19" s="5">
+        <v>8.7126676147807167</v>
+      </c>
+      <c r="E19" s="4">
+        <v>44.385248993816397</v>
+      </c>
+      <c r="F19">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1778</v>
+      </c>
+      <c r="C20" s="1">
+        <v>8444020.1159259994</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1.0982964571192504</v>
+      </c>
+      <c r="E20" s="4">
+        <v>5.5950902609397</v>
+      </c>
+      <c r="F20">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1536</v>
+      </c>
+      <c r="C21" s="1">
+        <v>8702600.2783100009</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1.131929450921815</v>
+      </c>
+      <c r="E21" s="4">
+        <v>5.7664280039062534</v>
+      </c>
+      <c r="F21">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="1">
+        <v>67</v>
+      </c>
+      <c r="C22" s="1">
+        <v>55028856.235243097</v>
+      </c>
+      <c r="D22" s="5">
+        <v>7.1575086963057908</v>
+      </c>
+      <c r="E22" s="6">
+        <v>40.018914014776257</v>
+      </c>
+      <c r="F22">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="1">
+        <v>7295</v>
+      </c>
+      <c r="C23" s="1">
+        <v>65685097.931883499</v>
+      </c>
+      <c r="D23" s="5">
+        <v>8.5435477280382326</v>
+      </c>
+      <c r="E23" s="6">
+        <v>47.768506671317901</v>
+      </c>
+      <c r="F23">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1754</v>
+      </c>
+      <c r="C24" s="1">
+        <v>9546680.7427750006</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1.2417203465970827</v>
+      </c>
+      <c r="E24" s="6">
+        <v>6.942681020634252</v>
+      </c>
+      <c r="F24">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1223</v>
+      </c>
+      <c r="C25" s="1">
+        <v>7240916.1551781502</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0.94181351195731877</v>
+      </c>
+      <c r="E25" s="6">
+        <v>5.2658481536218789</v>
+      </c>
+      <c r="F25">
+        <v>2014</v>
       </c>
     </row>
   </sheetData>
